--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F2530D-7A0D-491E-9721-AF28616147ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4660B7E-39BC-482D-8956-1F6582096710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="264">
   <si>
     <t>STT</t>
   </si>
@@ -654,13 +654,172 @@
     <t>VNET860879084178025</t>
   </si>
   <si>
-    <t>Còn 54 tb chưa bắn ID</t>
-  </si>
-  <si>
     <t>VNET860879084178041</t>
   </si>
   <si>
     <t>A. Vũ mượn test ngày 14/10/26</t>
+  </si>
+  <si>
+    <t>VNET860879084182639</t>
+  </si>
+  <si>
+    <t>VNET860879084178785</t>
+  </si>
+  <si>
+    <t>VNET860879084181300</t>
+  </si>
+  <si>
+    <t>VNET860879084182043</t>
+  </si>
+  <si>
+    <t>VNET860879084173976</t>
+  </si>
+  <si>
+    <t>VNET860879084182688</t>
+  </si>
+  <si>
+    <t>VNET860879084182431</t>
+  </si>
+  <si>
+    <t>VNET860879084175492</t>
+  </si>
+  <si>
+    <t>VNET860879084180153</t>
+  </si>
+  <si>
+    <t>VNET860879084176078</t>
+  </si>
+  <si>
+    <t>VNET860879084180823</t>
+  </si>
+  <si>
+    <t>VNET860879084180815</t>
+  </si>
+  <si>
+    <t>VNET860879084180294</t>
+  </si>
+  <si>
+    <t>VNET860879084183215</t>
+  </si>
+  <si>
+    <t>VNET860879084183421</t>
+  </si>
+  <si>
+    <t>VNET860879084173950</t>
+  </si>
+  <si>
+    <t>VNET860879084180443</t>
+  </si>
+  <si>
+    <t>VNET860879084175989</t>
+  </si>
+  <si>
+    <t>VNET860879084177464</t>
+  </si>
+  <si>
+    <t>VNET860879084176086</t>
+  </si>
+  <si>
+    <t>VNET860879084183447</t>
+  </si>
+  <si>
+    <t>VNET860879084180203</t>
+  </si>
+  <si>
+    <t>VNET860879084180724</t>
+  </si>
+  <si>
+    <t>VNET860879084175898</t>
+  </si>
+  <si>
+    <t>VNET860879084177316</t>
+  </si>
+  <si>
+    <t>VNET860879084181573</t>
+  </si>
+  <si>
+    <t>VNET860879084180336</t>
+  </si>
+  <si>
+    <t>VNET860879084180492</t>
+  </si>
+  <si>
+    <t>VNET860879084180682</t>
+  </si>
+  <si>
+    <t>VNET860879084180112</t>
+  </si>
+  <si>
+    <t>VNET860879084181904</t>
+  </si>
+  <si>
+    <t>VNET860879084180500</t>
+  </si>
+  <si>
+    <t>VNET860879084174248</t>
+  </si>
+  <si>
+    <t>VNET860879084181094</t>
+  </si>
+  <si>
+    <t>VNET860879084179544</t>
+  </si>
+  <si>
+    <t>VNET860879084179320</t>
+  </si>
+  <si>
+    <t>VNET860879084181581</t>
+  </si>
+  <si>
+    <t>VNET860879084175484</t>
+  </si>
+  <si>
+    <t>VNET860879084178066</t>
+  </si>
+  <si>
+    <t>VNET860879084177605</t>
+  </si>
+  <si>
+    <t>VNET860879084175062</t>
+  </si>
+  <si>
+    <t>VNET860879084175286</t>
+  </si>
+  <si>
+    <t>VNET860879084183306</t>
+  </si>
+  <si>
+    <t>VNET860879084181078</t>
+  </si>
+  <si>
+    <t>VNET860879084178058</t>
+  </si>
+  <si>
+    <t>VNET860879084178769</t>
+  </si>
+  <si>
+    <t>VNET860879084174909</t>
+  </si>
+  <si>
+    <t>VNET860879084181854</t>
+  </si>
+  <si>
+    <t>VNET860879084179007</t>
+  </si>
+  <si>
+    <t>VNET860879084181623</t>
+  </si>
+  <si>
+    <t>VNET860879084179890</t>
+  </si>
+  <si>
+    <t>VNET860879084183728</t>
+  </si>
+  <si>
+    <t>VNET860879084182324</t>
+  </si>
+  <si>
+    <t>VNET860879084180674</t>
   </si>
 </sst>
 </file>
@@ -4448,14 +4607,14 @@
         <v>200</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D201" s="3"/>
       <c r="E201" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F201" s="10"/>
     </row>
@@ -4464,7 +4623,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>166</v>
@@ -4477,8 +4636,12 @@
       <c r="A203" s="3">
         <v>202</v>
       </c>
-      <c r="B203" s="4"/>
-      <c r="C203" s="4"/>
+      <c r="B203" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D203" s="3"/>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
@@ -4487,8 +4650,12 @@
       <c r="A204" s="3">
         <v>203</v>
       </c>
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
+      <c r="B204" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D204" s="3"/>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
@@ -4497,8 +4664,12 @@
       <c r="A205" s="3">
         <v>204</v>
       </c>
-      <c r="B205" s="4"/>
-      <c r="C205" s="4"/>
+      <c r="B205" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D205" s="3"/>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
@@ -4507,8 +4678,12 @@
       <c r="A206" s="3">
         <v>205</v>
       </c>
-      <c r="B206" s="4"/>
-      <c r="C206" s="4"/>
+      <c r="B206" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D206" s="3"/>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
@@ -4517,8 +4692,12 @@
       <c r="A207" s="3">
         <v>206</v>
       </c>
-      <c r="B207" s="4"/>
-      <c r="C207" s="4"/>
+      <c r="B207" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D207" s="3"/>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -4527,8 +4706,12 @@
       <c r="A208" s="3">
         <v>207</v>
       </c>
-      <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
+      <c r="B208" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D208" s="3"/>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
@@ -4537,8 +4720,12 @@
       <c r="A209" s="3">
         <v>208</v>
       </c>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
+      <c r="B209" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D209" s="3"/>
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
@@ -4547,8 +4734,12 @@
       <c r="A210" s="3">
         <v>209</v>
       </c>
-      <c r="B210" s="4"/>
-      <c r="C210" s="4"/>
+      <c r="B210" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D210" s="3"/>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -4557,8 +4748,12 @@
       <c r="A211" s="3">
         <v>210</v>
       </c>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
+      <c r="B211" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D211" s="3"/>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -4567,8 +4762,12 @@
       <c r="A212" s="3">
         <v>211</v>
       </c>
-      <c r="B212" s="4"/>
-      <c r="C212" s="4"/>
+      <c r="B212" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D212" s="3"/>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
@@ -4577,8 +4776,12 @@
       <c r="A213" s="3">
         <v>212</v>
       </c>
-      <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
+      <c r="B213" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D213" s="3"/>
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
@@ -4587,8 +4790,12 @@
       <c r="A214" s="3">
         <v>213</v>
       </c>
-      <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
+      <c r="B214" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D214" s="3"/>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
@@ -4597,8 +4804,12 @@
       <c r="A215" s="3">
         <v>214</v>
       </c>
-      <c r="B215" s="4"/>
-      <c r="C215" s="4"/>
+      <c r="B215" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D215" s="3"/>
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
@@ -4607,8 +4818,12 @@
       <c r="A216" s="3">
         <v>215</v>
       </c>
-      <c r="B216" s="4"/>
-      <c r="C216" s="4"/>
+      <c r="B216" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D216" s="3"/>
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
@@ -4617,8 +4832,12 @@
       <c r="A217" s="3">
         <v>216</v>
       </c>
-      <c r="B217" s="4"/>
-      <c r="C217" s="4"/>
+      <c r="B217" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D217" s="3"/>
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
@@ -4627,8 +4846,12 @@
       <c r="A218" s="3">
         <v>217</v>
       </c>
-      <c r="B218" s="4"/>
-      <c r="C218" s="4"/>
+      <c r="B218" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D218" s="3"/>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -4637,8 +4860,12 @@
       <c r="A219" s="3">
         <v>218</v>
       </c>
-      <c r="B219" s="4"/>
-      <c r="C219" s="4"/>
+      <c r="B219" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D219" s="3"/>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
@@ -4647,8 +4874,12 @@
       <c r="A220" s="3">
         <v>219</v>
       </c>
-      <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
+      <c r="B220" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D220" s="3"/>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
@@ -4657,8 +4888,12 @@
       <c r="A221" s="3">
         <v>220</v>
       </c>
-      <c r="B221" s="4"/>
-      <c r="C221" s="4"/>
+      <c r="B221" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D221" s="3"/>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
@@ -4667,8 +4902,12 @@
       <c r="A222" s="3">
         <v>221</v>
       </c>
-      <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
+      <c r="B222" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D222" s="3"/>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
@@ -4677,8 +4916,12 @@
       <c r="A223" s="3">
         <v>222</v>
       </c>
-      <c r="B223" s="4"/>
-      <c r="C223" s="4"/>
+      <c r="B223" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D223" s="3"/>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
@@ -4687,8 +4930,12 @@
       <c r="A224" s="3">
         <v>223</v>
       </c>
-      <c r="B224" s="4"/>
-      <c r="C224" s="4"/>
+      <c r="B224" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D224" s="3"/>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
@@ -4697,8 +4944,12 @@
       <c r="A225" s="3">
         <v>224</v>
       </c>
-      <c r="B225" s="4"/>
-      <c r="C225" s="4"/>
+      <c r="B225" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D225" s="3"/>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
@@ -4707,8 +4958,12 @@
       <c r="A226" s="3">
         <v>225</v>
       </c>
-      <c r="B226" s="4"/>
-      <c r="C226" s="4"/>
+      <c r="B226" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D226" s="3"/>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -4717,8 +4972,12 @@
       <c r="A227" s="3">
         <v>226</v>
       </c>
-      <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
+      <c r="B227" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D227" s="3"/>
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
@@ -4727,8 +4986,12 @@
       <c r="A228" s="3">
         <v>227</v>
       </c>
-      <c r="B228" s="4"/>
-      <c r="C228" s="4"/>
+      <c r="B228" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D228" s="3"/>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
@@ -4737,8 +5000,12 @@
       <c r="A229" s="3">
         <v>228</v>
       </c>
-      <c r="B229" s="4"/>
-      <c r="C229" s="4"/>
+      <c r="B229" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D229" s="3"/>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -4747,8 +5014,12 @@
       <c r="A230" s="3">
         <v>229</v>
       </c>
-      <c r="B230" s="4"/>
-      <c r="C230" s="4"/>
+      <c r="B230" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D230" s="3"/>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -4757,8 +5028,12 @@
       <c r="A231" s="3">
         <v>230</v>
       </c>
-      <c r="B231" s="4"/>
-      <c r="C231" s="4"/>
+      <c r="B231" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D231" s="3"/>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
@@ -4767,8 +5042,12 @@
       <c r="A232" s="3">
         <v>231</v>
       </c>
-      <c r="B232" s="4"/>
-      <c r="C232" s="4"/>
+      <c r="B232" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D232" s="3"/>
       <c r="E232" s="10"/>
       <c r="F232" s="10"/>
@@ -4777,8 +5056,12 @@
       <c r="A233" s="3">
         <v>232</v>
       </c>
-      <c r="B233" s="4"/>
-      <c r="C233" s="4"/>
+      <c r="B233" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D233" s="3"/>
       <c r="E233" s="10"/>
       <c r="F233" s="10"/>
@@ -4787,8 +5070,12 @@
       <c r="A234" s="3">
         <v>233</v>
       </c>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
+      <c r="B234" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D234" s="3"/>
       <c r="E234" s="10"/>
       <c r="F234" s="10"/>
@@ -4797,8 +5084,12 @@
       <c r="A235" s="3">
         <v>234</v>
       </c>
-      <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
+      <c r="B235" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D235" s="3"/>
       <c r="E235" s="10"/>
       <c r="F235" s="10"/>
@@ -4807,8 +5098,12 @@
       <c r="A236" s="3">
         <v>235</v>
       </c>
-      <c r="B236" s="4"/>
-      <c r="C236" s="4"/>
+      <c r="B236" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D236" s="3"/>
       <c r="E236" s="10"/>
       <c r="F236" s="10"/>
@@ -4817,8 +5112,12 @@
       <c r="A237" s="3">
         <v>236</v>
       </c>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
+      <c r="B237" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D237" s="3"/>
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
@@ -4827,8 +5126,12 @@
       <c r="A238" s="3">
         <v>237</v>
       </c>
-      <c r="B238" s="4"/>
-      <c r="C238" s="4"/>
+      <c r="B238" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D238" s="3"/>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -4837,8 +5140,12 @@
       <c r="A239" s="3">
         <v>238</v>
       </c>
-      <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
+      <c r="B239" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D239" s="3"/>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -4847,8 +5154,12 @@
       <c r="A240" s="3">
         <v>239</v>
       </c>
-      <c r="B240" s="4"/>
-      <c r="C240" s="4"/>
+      <c r="B240" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D240" s="3"/>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -4857,8 +5168,12 @@
       <c r="A241" s="3">
         <v>240</v>
       </c>
-      <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
+      <c r="B241" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D241" s="3"/>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -4867,8 +5182,12 @@
       <c r="A242" s="3">
         <v>241</v>
       </c>
-      <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
+      <c r="B242" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D242" s="3"/>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -4877,8 +5196,12 @@
       <c r="A243" s="3">
         <v>242</v>
       </c>
-      <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
+      <c r="B243" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D243" s="3"/>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -4887,8 +5210,12 @@
       <c r="A244" s="3">
         <v>243</v>
       </c>
-      <c r="B244" s="4"/>
-      <c r="C244" s="4"/>
+      <c r="B244" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D244" s="3"/>
       <c r="E244" s="10"/>
       <c r="F244" s="10"/>
@@ -4897,8 +5224,12 @@
       <c r="A245" s="3">
         <v>244</v>
       </c>
-      <c r="B245" s="4"/>
-      <c r="C245" s="4"/>
+      <c r="B245" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D245" s="3"/>
       <c r="E245" s="10"/>
       <c r="F245" s="10"/>
@@ -4907,8 +5238,12 @@
       <c r="A246" s="3">
         <v>245</v>
       </c>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
+      <c r="B246" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D246" s="3"/>
       <c r="E246" s="10"/>
       <c r="F246" s="10"/>
@@ -4917,8 +5252,12 @@
       <c r="A247" s="3">
         <v>246</v>
       </c>
-      <c r="B247" s="4"/>
-      <c r="C247" s="4"/>
+      <c r="B247" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D247" s="3"/>
       <c r="E247" s="10"/>
       <c r="F247" s="10"/>
@@ -4927,8 +5266,12 @@
       <c r="A248" s="3">
         <v>247</v>
       </c>
-      <c r="B248" s="4"/>
-      <c r="C248" s="4"/>
+      <c r="B248" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D248" s="3"/>
       <c r="E248" s="10"/>
       <c r="F248" s="10"/>
@@ -4937,8 +5280,12 @@
       <c r="A249" s="3">
         <v>248</v>
       </c>
-      <c r="B249" s="4"/>
-      <c r="C249" s="4"/>
+      <c r="B249" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D249" s="3"/>
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
@@ -4947,8 +5294,12 @@
       <c r="A250" s="3">
         <v>249</v>
       </c>
-      <c r="B250" s="4"/>
-      <c r="C250" s="4"/>
+      <c r="B250" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D250" s="3"/>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
@@ -4957,8 +5308,12 @@
       <c r="A251" s="3">
         <v>250</v>
       </c>
-      <c r="B251" s="4"/>
-      <c r="C251" s="4"/>
+      <c r="B251" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D251" s="3"/>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -4967,8 +5322,12 @@
       <c r="A252" s="3">
         <v>251</v>
       </c>
-      <c r="B252" s="4"/>
-      <c r="C252" s="4"/>
+      <c r="B252" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D252" s="3"/>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
@@ -4977,8 +5336,12 @@
       <c r="A253" s="3">
         <v>252</v>
       </c>
-      <c r="B253" s="4"/>
-      <c r="C253" s="4"/>
+      <c r="B253" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D253" s="3"/>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
@@ -4987,8 +5350,12 @@
       <c r="A254" s="3">
         <v>253</v>
       </c>
-      <c r="B254" s="4"/>
-      <c r="C254" s="4"/>
+      <c r="B254" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D254" s="3"/>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
@@ -4997,8 +5364,12 @@
       <c r="A255" s="3">
         <v>254</v>
       </c>
-      <c r="B255" s="4"/>
-      <c r="C255" s="4"/>
+      <c r="B255" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="D255" s="3"/>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
@@ -12465,44 +12836,44 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:B70">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71:B72">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74:B75">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76:B77">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78:B80">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:B86">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87:B99">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B100:B102">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576 B1:B62 B150:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B64:B70">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71:B72">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B74:B75">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B76:B77">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B78:B80">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B81">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B82:B86">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B87:B99">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B100:B102">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4660B7E-39BC-482D-8956-1F6582096710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B8E0EC-5C7A-413F-9B23-95FE6C8ACD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$1001</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="272">
   <si>
     <t>STT</t>
   </si>
@@ -820,13 +820,37 @@
   </si>
   <si>
     <t>VNET860879084180674</t>
+  </si>
+  <si>
+    <t>SL nhận</t>
+  </si>
+  <si>
+    <t>SL nhập kho</t>
+  </si>
+  <si>
+    <t>SL lỗi</t>
+  </si>
+  <si>
+    <t>Tồn SX</t>
+  </si>
+  <si>
+    <t>Đã cho mượn</t>
+  </si>
+  <si>
+    <t>Cho mượn</t>
+  </si>
+  <si>
+    <t>Nhận 180 chưa bắn ID</t>
+  </si>
+  <si>
+    <t>16/10/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -864,6 +888,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -879,7 +909,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -903,23 +933,34 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -965,10 +1006,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1414,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:G1001"/>
+  <dimension ref="A1:K1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="8" customWidth="1"/>
@@ -1423,10 +1493,13 @@
     <col min="4" max="4" width="22.7109375" style="8" customWidth="1"/>
     <col min="5" max="5" width="30.42578125" style="9" customWidth="1"/>
     <col min="6" max="6" width="29.7109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1442,8 +1515,24 @@
       <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F1" s="21"/>
+      <c r="G1" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1457,10 +1546,29 @@
         <v>3</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2" s="20"/>
+      <c r="G2" s="3">
+        <f>COUNTIFS(B2:B1001,"*VNET*")</f>
+        <v>254</v>
+      </c>
+      <c r="H2" s="23">
+        <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
+        <v>181</v>
+      </c>
+      <c r="I2" s="25">
+        <f>COUNTIFS(D2:D1001,"Lỗi")</f>
+        <v>19</v>
+      </c>
+      <c r="J2" s="30">
+        <f>COUNTIFS(D2:D1001,"Đã cho mượn")</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="31">
+        <f>G2-H2</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1476,8 +1584,9 @@
       <c r="E3" s="10"/>
       <c r="F3" s="15"/>
       <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1494,7 +1603,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1511,7 +1620,7 @@
       <c r="F5" s="15"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1528,7 +1637,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1545,7 +1654,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1562,7 +1671,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1579,7 +1688,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1596,7 +1705,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1613,7 +1722,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1630,7 +1739,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1647,7 +1756,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1664,7 +1773,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1681,7 +1790,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1730,7 +1839,7 @@
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="19"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -2454,7 +2563,7 @@
       <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="19" t="s">
         <v>67</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -2470,7 +2579,7 @@
       <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="19" t="s">
         <v>68</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -2486,7 +2595,7 @@
       <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="19" t="s">
         <v>69</v>
       </c>
       <c r="C65" s="1" t="s">
@@ -2502,7 +2611,7 @@
       <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -2518,7 +2627,7 @@
       <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="19" t="s">
         <v>71</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -2534,7 +2643,7 @@
       <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="19" t="s">
         <v>72</v>
       </c>
       <c r="C68" s="1" t="s">
@@ -2550,7 +2659,7 @@
       <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -2566,7 +2675,7 @@
       <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="19" t="s">
         <v>74</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -2582,7 +2691,7 @@
       <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="19" t="s">
         <v>75</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -2598,7 +2707,7 @@
       <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -2614,7 +2723,7 @@
       <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="19" t="s">
         <v>77</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -2630,7 +2739,7 @@
       <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" s="20" t="s">
+      <c r="B74" s="19" t="s">
         <v>78</v>
       </c>
       <c r="C74" s="1" t="s">
@@ -2646,7 +2755,7 @@
       <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="19" t="s">
         <v>79</v>
       </c>
       <c r="C75" s="1" t="s">
@@ -2662,7 +2771,7 @@
       <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="B76" s="19" t="s">
         <v>80</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -2678,7 +2787,7 @@
       <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" s="20" t="s">
+      <c r="B77" s="19" t="s">
         <v>81</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -2694,7 +2803,7 @@
       <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="19" t="s">
         <v>82</v>
       </c>
       <c r="C78" s="1" t="s">
@@ -2710,7 +2819,7 @@
       <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" s="20" t="s">
+      <c r="B79" s="19" t="s">
         <v>83</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -2726,7 +2835,7 @@
       <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="19" t="s">
         <v>84</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -2742,7 +2851,7 @@
       <c r="A81" s="3">
         <v>80</v>
       </c>
-      <c r="B81" s="20" t="s">
+      <c r="B81" s="19" t="s">
         <v>85</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -2758,7 +2867,7 @@
       <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" s="20" t="s">
+      <c r="B82" s="19" t="s">
         <v>86</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -2774,7 +2883,7 @@
       <c r="A83" s="3">
         <v>82</v>
       </c>
-      <c r="B83" s="20" t="s">
+      <c r="B83" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -2790,7 +2899,7 @@
       <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" s="20" t="s">
+      <c r="B84" s="19" t="s">
         <v>88</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -2806,7 +2915,7 @@
       <c r="A85" s="3">
         <v>84</v>
       </c>
-      <c r="B85" s="20" t="s">
+      <c r="B85" s="19" t="s">
         <v>89</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -2822,7 +2931,7 @@
       <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" s="20" t="s">
+      <c r="B86" s="19" t="s">
         <v>90</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -2838,7 +2947,7 @@
       <c r="A87" s="3">
         <v>86</v>
       </c>
-      <c r="B87" s="20" t="s">
+      <c r="B87" s="19" t="s">
         <v>91</v>
       </c>
       <c r="C87" s="1" t="s">
@@ -2854,7 +2963,7 @@
       <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" s="20" t="s">
+      <c r="B88" s="19" t="s">
         <v>92</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -2870,7 +2979,7 @@
       <c r="A89" s="3">
         <v>88</v>
       </c>
-      <c r="B89" s="20" t="s">
+      <c r="B89" s="19" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="1" t="s">
@@ -2886,7 +2995,7 @@
       <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" s="20" t="s">
+      <c r="B90" s="19" t="s">
         <v>94</v>
       </c>
       <c r="C90" s="1" t="s">
@@ -2902,7 +3011,7 @@
       <c r="A91" s="3">
         <v>90</v>
       </c>
-      <c r="B91" s="20" t="s">
+      <c r="B91" s="19" t="s">
         <v>95</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -2918,7 +3027,7 @@
       <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" s="20" t="s">
+      <c r="B92" s="19" t="s">
         <v>96</v>
       </c>
       <c r="C92" s="1" t="s">
@@ -2934,7 +3043,7 @@
       <c r="A93" s="3">
         <v>92</v>
       </c>
-      <c r="B93" s="20" t="s">
+      <c r="B93" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -2950,7 +3059,7 @@
       <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" s="20" t="s">
+      <c r="B94" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -2966,7 +3075,7 @@
       <c r="A95" s="3">
         <v>94</v>
       </c>
-      <c r="B95" s="20" t="s">
+      <c r="B95" s="19" t="s">
         <v>99</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -2982,7 +3091,7 @@
       <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" s="20" t="s">
+      <c r="B96" s="19" t="s">
         <v>100</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -2998,7 +3107,7 @@
       <c r="A97" s="3">
         <v>96</v>
       </c>
-      <c r="B97" s="20" t="s">
+      <c r="B97" s="19" t="s">
         <v>101</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -3014,7 +3123,7 @@
       <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" s="20" t="s">
+      <c r="B98" s="19" t="s">
         <v>102</v>
       </c>
       <c r="C98" s="1" t="s">
@@ -3030,7 +3139,7 @@
       <c r="A99" s="3">
         <v>98</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B99" s="19" t="s">
         <v>103</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -3046,7 +3155,7 @@
       <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" s="20" t="s">
+      <c r="B100" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C100" s="1" t="s">
@@ -3062,7 +3171,7 @@
       <c r="A101" s="3">
         <v>100</v>
       </c>
-      <c r="B101" s="20" t="s">
+      <c r="B101" s="19" t="s">
         <v>105</v>
       </c>
       <c r="C101" s="1" t="s">
@@ -3078,7 +3187,7 @@
       <c r="A102" s="3">
         <v>101</v>
       </c>
-      <c r="B102" s="20" t="s">
+      <c r="B102" s="19" t="s">
         <v>106</v>
       </c>
       <c r="C102" s="1" t="s">
@@ -3094,7 +3203,7 @@
       <c r="A103" s="3">
         <v>102</v>
       </c>
-      <c r="B103" s="20" t="s">
+      <c r="B103" s="19" t="s">
         <v>107</v>
       </c>
       <c r="C103" s="1" t="s">
@@ -3110,7 +3219,7 @@
       <c r="A104" s="3">
         <v>103</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B104" s="19" t="s">
         <v>108</v>
       </c>
       <c r="C104" s="1" t="s">
@@ -3126,7 +3235,7 @@
       <c r="A105" s="3">
         <v>104</v>
       </c>
-      <c r="B105" s="20" t="s">
+      <c r="B105" s="19" t="s">
         <v>109</v>
       </c>
       <c r="C105" s="1" t="s">
@@ -3142,7 +3251,7 @@
       <c r="A106" s="3">
         <v>105</v>
       </c>
-      <c r="B106" s="20" t="s">
+      <c r="B106" s="19" t="s">
         <v>110</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -3158,7 +3267,7 @@
       <c r="A107" s="3">
         <v>106</v>
       </c>
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="19" t="s">
         <v>111</v>
       </c>
       <c r="C107" s="1" t="s">
@@ -3174,7 +3283,7 @@
       <c r="A108" s="3">
         <v>107</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C108" s="1" t="s">
@@ -3190,7 +3299,7 @@
       <c r="A109" s="3">
         <v>108</v>
       </c>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="19" t="s">
         <v>113</v>
       </c>
       <c r="C109" s="1" t="s">
@@ -3206,7 +3315,7 @@
       <c r="A110" s="3">
         <v>109</v>
       </c>
-      <c r="B110" s="20" t="s">
+      <c r="B110" s="19" t="s">
         <v>114</v>
       </c>
       <c r="C110" s="1" t="s">
@@ -3222,7 +3331,7 @@
       <c r="A111" s="3">
         <v>110</v>
       </c>
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C111" s="1" t="s">
@@ -3238,7 +3347,7 @@
       <c r="A112" s="3">
         <v>111</v>
       </c>
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="19" t="s">
         <v>116</v>
       </c>
       <c r="C112" s="1" t="s">
@@ -3254,7 +3363,7 @@
       <c r="A113" s="3">
         <v>112</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="19" t="s">
         <v>117</v>
       </c>
       <c r="C113" s="1" t="s">
@@ -3270,7 +3379,7 @@
       <c r="A114" s="3">
         <v>113</v>
       </c>
-      <c r="B114" s="20" t="s">
+      <c r="B114" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C114" s="1" t="s">
@@ -3286,7 +3395,7 @@
       <c r="A115" s="3">
         <v>114</v>
       </c>
-      <c r="B115" s="20" t="s">
+      <c r="B115" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C115" s="1" t="s">
@@ -3302,7 +3411,7 @@
       <c r="A116" s="3">
         <v>115</v>
       </c>
-      <c r="B116" s="20" t="s">
+      <c r="B116" s="19" t="s">
         <v>120</v>
       </c>
       <c r="C116" s="1" t="s">
@@ -3318,7 +3427,7 @@
       <c r="A117" s="3">
         <v>116</v>
       </c>
-      <c r="B117" s="20" t="s">
+      <c r="B117" s="19" t="s">
         <v>121</v>
       </c>
       <c r="C117" s="1" t="s">
@@ -3334,7 +3443,7 @@
       <c r="A118" s="3">
         <v>117</v>
       </c>
-      <c r="B118" s="20" t="s">
+      <c r="B118" s="19" t="s">
         <v>122</v>
       </c>
       <c r="C118" s="1" t="s">
@@ -3350,7 +3459,7 @@
       <c r="A119" s="3">
         <v>118</v>
       </c>
-      <c r="B119" s="20" t="s">
+      <c r="B119" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C119" s="1" t="s">
@@ -3366,7 +3475,7 @@
       <c r="A120" s="3">
         <v>119</v>
       </c>
-      <c r="B120" s="20" t="s">
+      <c r="B120" s="19" t="s">
         <v>124</v>
       </c>
       <c r="C120" s="1" t="s">
@@ -3382,7 +3491,7 @@
       <c r="A121" s="3">
         <v>120</v>
       </c>
-      <c r="B121" s="20" t="s">
+      <c r="B121" s="19" t="s">
         <v>125</v>
       </c>
       <c r="C121" s="1" t="s">
@@ -3398,7 +3507,7 @@
       <c r="A122" s="3">
         <v>121</v>
       </c>
-      <c r="B122" s="20" t="s">
+      <c r="B122" s="19" t="s">
         <v>126</v>
       </c>
       <c r="C122" s="1" t="s">
@@ -3414,7 +3523,7 @@
       <c r="A123" s="3">
         <v>122</v>
       </c>
-      <c r="B123" s="20" t="s">
+      <c r="B123" s="19" t="s">
         <v>127</v>
       </c>
       <c r="C123" s="1" t="s">
@@ -3430,7 +3539,7 @@
       <c r="A124" s="3">
         <v>123</v>
       </c>
-      <c r="B124" s="20" t="s">
+      <c r="B124" s="19" t="s">
         <v>128</v>
       </c>
       <c r="C124" s="1" t="s">
@@ -3446,7 +3555,7 @@
       <c r="A125" s="3">
         <v>124</v>
       </c>
-      <c r="B125" s="20" t="s">
+      <c r="B125" s="19" t="s">
         <v>129</v>
       </c>
       <c r="C125" s="1" t="s">
@@ -3462,7 +3571,7 @@
       <c r="A126" s="3">
         <v>125</v>
       </c>
-      <c r="B126" s="20" t="s">
+      <c r="B126" s="19" t="s">
         <v>130</v>
       </c>
       <c r="C126" s="1" t="s">
@@ -3478,7 +3587,7 @@
       <c r="A127" s="3">
         <v>126</v>
       </c>
-      <c r="B127" s="20" t="s">
+      <c r="B127" s="19" t="s">
         <v>131</v>
       </c>
       <c r="C127" s="1" t="s">
@@ -3494,7 +3603,7 @@
       <c r="A128" s="3">
         <v>127</v>
       </c>
-      <c r="B128" s="20" t="s">
+      <c r="B128" s="19" t="s">
         <v>132</v>
       </c>
       <c r="C128" s="1" t="s">
@@ -3510,7 +3619,7 @@
       <c r="A129" s="3">
         <v>128</v>
       </c>
-      <c r="B129" s="20" t="s">
+      <c r="B129" s="19" t="s">
         <v>133</v>
       </c>
       <c r="C129" s="1" t="s">
@@ -3526,7 +3635,7 @@
       <c r="A130" s="3">
         <v>129</v>
       </c>
-      <c r="B130" s="20" t="s">
+      <c r="B130" s="19" t="s">
         <v>134</v>
       </c>
       <c r="C130" s="1" t="s">
@@ -3542,7 +3651,7 @@
       <c r="A131" s="3">
         <v>130</v>
       </c>
-      <c r="B131" s="20" t="s">
+      <c r="B131" s="19" t="s">
         <v>135</v>
       </c>
       <c r="C131" s="1" t="s">
@@ -3558,7 +3667,7 @@
       <c r="A132" s="3">
         <v>131</v>
       </c>
-      <c r="B132" s="20" t="s">
+      <c r="B132" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C132" s="1" t="s">
@@ -3574,7 +3683,7 @@
       <c r="A133" s="3">
         <v>132</v>
       </c>
-      <c r="B133" s="20" t="s">
+      <c r="B133" s="19" t="s">
         <v>137</v>
       </c>
       <c r="C133" s="1" t="s">
@@ -3590,7 +3699,7 @@
       <c r="A134" s="3">
         <v>133</v>
       </c>
-      <c r="B134" s="20" t="s">
+      <c r="B134" s="19" t="s">
         <v>138</v>
       </c>
       <c r="C134" s="1" t="s">
@@ -3606,7 +3715,7 @@
       <c r="A135" s="3">
         <v>134</v>
       </c>
-      <c r="B135" s="20" t="s">
+      <c r="B135" s="19" t="s">
         <v>139</v>
       </c>
       <c r="C135" s="1" t="s">
@@ -3622,7 +3731,7 @@
       <c r="A136" s="3">
         <v>135</v>
       </c>
-      <c r="B136" s="20" t="s">
+      <c r="B136" s="19" t="s">
         <v>140</v>
       </c>
       <c r="C136" s="1" t="s">
@@ -3638,7 +3747,7 @@
       <c r="A137" s="3">
         <v>136</v>
       </c>
-      <c r="B137" s="20" t="s">
+      <c r="B137" s="19" t="s">
         <v>141</v>
       </c>
       <c r="C137" s="1" t="s">
@@ -3654,7 +3763,7 @@
       <c r="A138" s="3">
         <v>137</v>
       </c>
-      <c r="B138" s="20" t="s">
+      <c r="B138" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C138" s="1" t="s">
@@ -3670,7 +3779,7 @@
       <c r="A139" s="3">
         <v>138</v>
       </c>
-      <c r="B139" s="20" t="s">
+      <c r="B139" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C139" s="1" t="s">
@@ -3686,7 +3795,7 @@
       <c r="A140" s="3">
         <v>139</v>
       </c>
-      <c r="B140" s="20" t="s">
+      <c r="B140" s="19" t="s">
         <v>144</v>
       </c>
       <c r="C140" s="1" t="s">
@@ -3702,7 +3811,7 @@
       <c r="A141" s="3">
         <v>140</v>
       </c>
-      <c r="B141" s="20" t="s">
+      <c r="B141" s="19" t="s">
         <v>145</v>
       </c>
       <c r="C141" s="1" t="s">
@@ -3718,7 +3827,7 @@
       <c r="A142" s="3">
         <v>141</v>
       </c>
-      <c r="B142" s="20" t="s">
+      <c r="B142" s="19" t="s">
         <v>146</v>
       </c>
       <c r="C142" s="1" t="s">
@@ -3734,7 +3843,7 @@
       <c r="A143" s="3">
         <v>142</v>
       </c>
-      <c r="B143" s="20" t="s">
+      <c r="B143" s="19" t="s">
         <v>147</v>
       </c>
       <c r="C143" s="1" t="s">
@@ -3750,7 +3859,7 @@
       <c r="A144" s="3">
         <v>143</v>
       </c>
-      <c r="B144" s="20" t="s">
+      <c r="B144" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C144" s="1" t="s">
@@ -3766,7 +3875,7 @@
       <c r="A145" s="3">
         <v>144</v>
       </c>
-      <c r="B145" s="20" t="s">
+      <c r="B145" s="19" t="s">
         <v>149</v>
       </c>
       <c r="C145" s="1" t="s">
@@ -3782,7 +3891,7 @@
       <c r="A146" s="3">
         <v>145</v>
       </c>
-      <c r="B146" s="20" t="s">
+      <c r="B146" s="19" t="s">
         <v>150</v>
       </c>
       <c r="C146" s="1" t="s">
@@ -3798,7 +3907,7 @@
       <c r="A147" s="3">
         <v>146</v>
       </c>
-      <c r="B147" s="20" t="s">
+      <c r="B147" s="19" t="s">
         <v>151</v>
       </c>
       <c r="C147" s="1" t="s">
@@ -3814,7 +3923,7 @@
       <c r="A148" s="3">
         <v>147</v>
       </c>
-      <c r="B148" s="20" t="s">
+      <c r="B148" s="19" t="s">
         <v>152</v>
       </c>
       <c r="C148" s="1" t="s">
@@ -3830,7 +3939,7 @@
       <c r="A149" s="3">
         <v>148</v>
       </c>
-      <c r="B149" s="20" t="s">
+      <c r="B149" s="19" t="s">
         <v>153</v>
       </c>
       <c r="C149" s="1" t="s">
@@ -3846,16 +3955,16 @@
       <c r="A150" s="3">
         <v>149</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D150" s="3" t="s">
+      <c r="C150" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D150" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E150" s="10" t="s">
+      <c r="E150" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F150" s="10"/>
@@ -3864,16 +3973,16 @@
       <c r="A151" s="3">
         <v>150</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D151" s="3" t="s">
+      <c r="C151" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D151" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E151" s="10" t="s">
+      <c r="E151" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F151" s="10"/>
@@ -3882,16 +3991,16 @@
       <c r="A152" s="3">
         <v>151</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D152" s="3" t="s">
+      <c r="C152" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D152" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E152" s="10" t="s">
+      <c r="E152" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F152" s="10"/>
@@ -3900,16 +4009,16 @@
       <c r="A153" s="3">
         <v>152</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D153" s="3" t="s">
+      <c r="C153" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D153" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E153" s="10" t="s">
+      <c r="E153" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F153" s="10"/>
@@ -3918,16 +4027,16 @@
       <c r="A154" s="3">
         <v>153</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D154" s="3" t="s">
+      <c r="C154" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D154" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E154" s="10" t="s">
+      <c r="E154" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F154" s="10"/>
@@ -3936,16 +4045,16 @@
       <c r="A155" s="3">
         <v>154</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D155" s="3" t="s">
+      <c r="C155" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D155" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E155" s="10" t="s">
+      <c r="E155" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F155" s="10"/>
@@ -3954,16 +4063,16 @@
       <c r="A156" s="3">
         <v>155</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D156" s="3" t="s">
+      <c r="C156" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D156" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E156" s="10" t="s">
+      <c r="E156" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F156" s="10"/>
@@ -3972,16 +4081,16 @@
       <c r="A157" s="3">
         <v>156</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D157" s="3" t="s">
+      <c r="C157" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D157" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E157" s="10" t="s">
+      <c r="E157" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F157" s="10"/>
@@ -3990,16 +4099,16 @@
       <c r="A158" s="3">
         <v>157</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D158" s="3" t="s">
+      <c r="C158" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D158" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E158" s="10" t="s">
+      <c r="E158" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F158" s="10"/>
@@ -4008,16 +4117,16 @@
       <c r="A159" s="3">
         <v>158</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D159" s="3" t="s">
+      <c r="C159" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D159" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E159" s="10" t="s">
+      <c r="E159" s="14" t="s">
         <v>165</v>
       </c>
       <c r="F159" s="10"/>
@@ -4026,48 +4135,48 @@
       <c r="A160" s="3">
         <v>159</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D160" s="3" t="s">
+      <c r="C160" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D160" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E160" s="10"/>
+      <c r="E160" s="14"/>
       <c r="F160" s="10"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>160</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D161" s="3" t="s">
+      <c r="C161" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D161" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E161" s="10"/>
+      <c r="E161" s="14"/>
       <c r="F161" s="10"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>161</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D162" s="3" t="s">
+      <c r="C162" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D162" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E162" s="10"/>
+      <c r="E162" s="14"/>
       <c r="F162" s="10"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,7 +4189,9 @@
       <c r="C163" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D163" s="3"/>
+      <c r="D163" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E163" s="10"/>
       <c r="F163" s="10"/>
     </row>
@@ -4094,7 +4205,9 @@
       <c r="C164" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D164" s="3"/>
+      <c r="D164" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
     </row>
@@ -4108,7 +4221,9 @@
       <c r="C165" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D165" s="3"/>
+      <c r="D165" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E165" s="10"/>
       <c r="F165" s="10"/>
     </row>
@@ -4122,7 +4237,9 @@
       <c r="C166" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D166" s="3"/>
+      <c r="D166" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E166" s="10"/>
       <c r="F166" s="10"/>
     </row>
@@ -4136,7 +4253,9 @@
       <c r="C167" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D167" s="3"/>
+      <c r="D167" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E167" s="10"/>
       <c r="F167" s="10"/>
     </row>
@@ -4150,7 +4269,9 @@
       <c r="C168" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D168" s="3"/>
+      <c r="D168" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
     </row>
@@ -4164,7 +4285,9 @@
       <c r="C169" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D169" s="3"/>
+      <c r="D169" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E169" s="10"/>
       <c r="F169" s="10"/>
     </row>
@@ -4178,7 +4301,9 @@
       <c r="C170" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D170" s="3"/>
+      <c r="D170" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
     </row>
@@ -4192,7 +4317,9 @@
       <c r="C171" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D171" s="3"/>
+      <c r="D171" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E171" s="10"/>
       <c r="F171" s="10"/>
     </row>
@@ -4206,7 +4333,9 @@
       <c r="C172" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D172" s="3"/>
+      <c r="D172" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
     </row>
@@ -4220,7 +4349,9 @@
       <c r="C173" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D173" s="3"/>
+      <c r="D173" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E173" s="10"/>
       <c r="F173" s="10"/>
     </row>
@@ -4234,7 +4365,9 @@
       <c r="C174" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D174" s="3"/>
+      <c r="D174" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
     </row>
@@ -4253,18 +4386,20 @@
       <c r="F175" s="10"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="3">
+      <c r="A176" s="25">
         <v>175</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D176" s="3"/>
-      <c r="E176" s="10"/>
-      <c r="F176" s="10"/>
+      <c r="C176" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D176" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" s="14"/>
+      <c r="F176" s="14"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
@@ -4276,7 +4411,9 @@
       <c r="C177" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D177" s="3"/>
+      <c r="D177" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E177" s="10"/>
       <c r="F177" s="10"/>
     </row>
@@ -4290,7 +4427,9 @@
       <c r="C178" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D178" s="3"/>
+      <c r="D178" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
     </row>
@@ -4304,7 +4443,9 @@
       <c r="C179" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D179" s="3"/>
+      <c r="D179" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
     </row>
@@ -4318,7 +4459,9 @@
       <c r="C180" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D180" s="3"/>
+      <c r="D180" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
     </row>
@@ -4332,7 +4475,9 @@
       <c r="C181" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D181" s="3"/>
+      <c r="D181" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E181" s="14"/>
       <c r="F181" s="10"/>
     </row>
@@ -4346,7 +4491,9 @@
       <c r="C182" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D182" s="3"/>
+      <c r="D182" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
     </row>
@@ -4360,7 +4507,9 @@
       <c r="C183" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D183" s="3"/>
+      <c r="D183" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E183" s="10"/>
       <c r="F183" s="10"/>
     </row>
@@ -4374,7 +4523,9 @@
       <c r="C184" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D184" s="3"/>
+      <c r="D184" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E184" s="10"/>
       <c r="F184" s="10"/>
     </row>
@@ -4388,7 +4539,9 @@
       <c r="C185" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D185" s="3"/>
+      <c r="D185" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E185" s="10"/>
       <c r="F185" s="10"/>
     </row>
@@ -4402,7 +4555,9 @@
       <c r="C186" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D186" s="3"/>
+      <c r="D186" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E186" s="10"/>
       <c r="F186" s="10"/>
     </row>
@@ -4416,7 +4571,9 @@
       <c r="C187" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D187" s="3"/>
+      <c r="D187" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E187" s="10"/>
       <c r="F187" s="10"/>
     </row>
@@ -4430,7 +4587,9 @@
       <c r="C188" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D188" s="3"/>
+      <c r="D188" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
     </row>
@@ -4570,7 +4729,9 @@
       <c r="C198" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D198" s="3"/>
+      <c r="D198" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
     </row>
@@ -4606,14 +4767,16 @@
       <c r="A201" s="3">
         <v>200</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D201" s="3"/>
-      <c r="E201" s="10" t="s">
+      <c r="C201" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="D201" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="E201" s="29" t="s">
         <v>209</v>
       </c>
       <c r="F201" s="10"/>
@@ -4754,7 +4917,9 @@
       <c r="C211" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D211" s="3"/>
+      <c r="D211" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
     </row>
@@ -4818,14 +4983,16 @@
       <c r="A216" s="3">
         <v>215</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D216" s="3"/>
-      <c r="E216" s="10"/>
+      <c r="C216" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D216" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E216" s="14"/>
       <c r="F216" s="10"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -4852,7 +5019,9 @@
       <c r="C218" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D218" s="3"/>
+      <c r="D218" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
     </row>
@@ -4950,7 +5119,9 @@
       <c r="C225" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D225" s="3"/>
+      <c r="D225" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
     </row>
@@ -4986,14 +5157,16 @@
       <c r="A228" s="3">
         <v>227</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C228" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D228" s="3"/>
-      <c r="E228" s="10"/>
+      <c r="C228" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D228" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E228" s="14"/>
       <c r="F228" s="10"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -5006,7 +5179,9 @@
       <c r="C229" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D229" s="3"/>
+      <c r="D229" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
     </row>
@@ -5020,7 +5195,9 @@
       <c r="C230" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D230" s="3"/>
+      <c r="D230" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
     </row>
@@ -5056,14 +5233,16 @@
       <c r="A233" s="3">
         <v>232</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C233" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D233" s="3"/>
-      <c r="E233" s="10"/>
+      <c r="C233" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D233" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E233" s="14"/>
       <c r="F233" s="10"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -5146,7 +5325,9 @@
       <c r="C239" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D239" s="3"/>
+      <c r="D239" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
     </row>
@@ -5154,14 +5335,16 @@
       <c r="A240" s="3">
         <v>239</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="C240" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D240" s="3"/>
-      <c r="E240" s="10"/>
+      <c r="C240" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D240" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" s="14"/>
       <c r="F240" s="10"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -5210,14 +5393,16 @@
       <c r="A244" s="3">
         <v>243</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D244" s="3"/>
-      <c r="E244" s="10"/>
+      <c r="C244" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D244" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" s="14"/>
       <c r="F244" s="10"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -5230,7 +5415,9 @@
       <c r="C245" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D245" s="3"/>
+      <c r="D245" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E245" s="10"/>
       <c r="F245" s="10"/>
     </row>
@@ -5244,7 +5431,9 @@
       <c r="C246" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D246" s="3"/>
+      <c r="D246" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E246" s="10"/>
       <c r="F246" s="10"/>
     </row>
@@ -5378,8 +5567,12 @@
       <c r="A256" s="3">
         <v>255</v>
       </c>
-      <c r="B256" s="4"/>
-      <c r="C256" s="4"/>
+      <c r="B256" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="D256" s="3"/>
       <c r="E256" s="10"/>
       <c r="F256" s="10"/>
@@ -12835,7 +13028,7 @@
       <c r="F1001" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <autoFilter ref="A1:E1001" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="B63">
     <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B8E0EC-5C7A-413F-9B23-95FE6C8ACD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B4EC81-2075-442E-9594-0BF604CF78E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="275">
   <si>
     <t>STT</t>
   </si>
@@ -831,9 +831,6 @@
     <t>SL lỗi</t>
   </si>
   <si>
-    <t>Tồn SX</t>
-  </si>
-  <si>
     <t>Đã cho mượn</t>
   </si>
   <si>
@@ -844,6 +841,18 @@
   </si>
   <si>
     <t>16/10/26</t>
+  </si>
+  <si>
+    <t>Trả lại lỗi</t>
+  </si>
+  <si>
+    <t>Tồn thực tế</t>
+  </si>
+  <si>
+    <t>Tồn lỗi</t>
+  </si>
+  <si>
+    <t>180 chưa nhập ID</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1045,7 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1484,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:K1001"/>
+  <dimension ref="A1:N1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="8" customWidth="1"/>
@@ -1495,11 +1504,12 @@
     <col min="6" max="6" width="29.7109375" style="9" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1526,13 +1536,19 @@
         <v>266</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1553,22 +1569,33 @@
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="I2" s="25">
         <f>COUNTIFS(D2:D1001,"Lỗi")</f>
         <v>19</v>
       </c>
-      <c r="J2" s="30">
+      <c r="J2" s="25">
+        <f>COUNTIFS(E2:E1001,"*Trả lại X-Force*")</f>
+        <v>10</v>
+      </c>
+      <c r="K2" s="25">
+        <f>SUM(I2-J2)</f>
+        <v>9</v>
+      </c>
+      <c r="L2" s="30">
         <f>COUNTIFS(D2:D1001,"Đã cho mượn")</f>
         <v>1</v>
       </c>
-      <c r="K2" s="31">
-        <f>G2-H2</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M2" s="31">
+        <f>SUM(G2-(H2+J2+L2))</f>
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1584,9 +1611,9 @@
       <c r="E3" s="10"/>
       <c r="F3" s="15"/>
       <c r="G3" s="7"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="7"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1603,7 +1630,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1620,7 +1647,7 @@
       <c r="F5" s="15"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1637,7 +1664,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1654,7 +1681,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1671,7 +1698,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1688,7 +1715,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1705,7 +1732,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1722,7 +1749,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1739,7 +1766,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1756,7 +1783,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1773,7 +1800,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1790,7 +1817,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -4774,7 +4801,7 @@
         <v>166</v>
       </c>
       <c r="D201" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E201" s="29" t="s">
         <v>209</v>
@@ -4791,7 +4818,9 @@
       <c r="C202" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D202" s="3"/>
+      <c r="D202" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
     </row>
@@ -4805,7 +4834,9 @@
       <c r="C203" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D203" s="3"/>
+      <c r="D203" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
     </row>
@@ -4819,7 +4850,9 @@
       <c r="C204" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D204" s="3"/>
+      <c r="D204" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
     </row>
@@ -4833,7 +4866,9 @@
       <c r="C205" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D205" s="3"/>
+      <c r="D205" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
     </row>
@@ -4861,7 +4896,9 @@
       <c r="C207" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D207" s="3"/>
+      <c r="D207" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
     </row>
@@ -4875,7 +4912,9 @@
       <c r="C208" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D208" s="3"/>
+      <c r="D208" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
     </row>
@@ -4889,7 +4928,9 @@
       <c r="C209" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D209" s="3"/>
+      <c r="D209" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
     </row>
@@ -4903,7 +4944,9 @@
       <c r="C210" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D210" s="3"/>
+      <c r="D210" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
     </row>
@@ -4933,7 +4976,9 @@
       <c r="C212" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D212" s="3"/>
+      <c r="D212" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
     </row>
@@ -4961,7 +5006,9 @@
       <c r="C214" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D214" s="3"/>
+      <c r="D214" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
     </row>
@@ -4975,7 +5022,9 @@
       <c r="C215" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D215" s="3"/>
+      <c r="D215" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
     </row>
@@ -5049,7 +5098,9 @@
       <c r="C220" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D220" s="3"/>
+      <c r="D220" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
     </row>
@@ -5063,7 +5114,9 @@
       <c r="C221" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D221" s="3"/>
+      <c r="D221" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
     </row>
@@ -5077,7 +5130,9 @@
       <c r="C222" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D222" s="3"/>
+      <c r="D222" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
     </row>
@@ -5091,7 +5146,9 @@
       <c r="C223" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D223" s="3"/>
+      <c r="D223" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
     </row>
@@ -5105,7 +5162,9 @@
       <c r="C224" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D224" s="3"/>
+      <c r="D224" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
     </row>
@@ -5135,7 +5194,9 @@
       <c r="C226" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D226" s="3"/>
+      <c r="D226" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
     </row>
@@ -5149,7 +5210,9 @@
       <c r="C227" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D227" s="3"/>
+      <c r="D227" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
     </row>
@@ -5225,7 +5288,9 @@
       <c r="C232" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D232" s="3"/>
+      <c r="D232" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E232" s="10"/>
       <c r="F232" s="10"/>
     </row>
@@ -5269,7 +5334,9 @@
       <c r="C235" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D235" s="3"/>
+      <c r="D235" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E235" s="10"/>
       <c r="F235" s="10"/>
     </row>
@@ -5297,7 +5364,9 @@
       <c r="C237" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D237" s="3"/>
+      <c r="D237" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
     </row>
@@ -5371,7 +5440,9 @@
       <c r="C242" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D242" s="3"/>
+      <c r="D242" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
     </row>
@@ -5385,7 +5456,9 @@
       <c r="C243" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D243" s="3"/>
+      <c r="D243" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
     </row>
@@ -5461,7 +5534,9 @@
       <c r="C248" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D248" s="3"/>
+      <c r="D248" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E248" s="10"/>
       <c r="F248" s="10"/>
     </row>
@@ -5475,7 +5550,9 @@
       <c r="C249" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D249" s="3"/>
+      <c r="D249" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
     </row>
@@ -5489,7 +5566,9 @@
       <c r="C250" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D250" s="3"/>
+      <c r="D250" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
     </row>
@@ -5517,7 +5596,9 @@
       <c r="C252" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D252" s="3"/>
+      <c r="D252" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
     </row>
@@ -5545,7 +5626,9 @@
       <c r="C254" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D254" s="3"/>
+      <c r="D254" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
     </row>
@@ -5559,7 +5642,9 @@
       <c r="C255" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D255" s="3"/>
+      <c r="D255" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
     </row>
@@ -5568,10 +5653,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C256" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="10"/>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B4EC81-2075-442E-9594-0BF604CF78E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994E2518-3845-44F6-BAA7-EB9944141150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="275">
   <si>
     <t>STT</t>
   </si>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="I2" s="25">
         <f>COUNTIFS(D2:D1001,"Lỗi")</f>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="N2" t="s">
         <v>274</v>
@@ -4408,7 +4408,9 @@
       <c r="C175" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D175" s="3"/>
+      <c r="D175" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E175" s="10"/>
       <c r="F175" s="10"/>
     </row>
@@ -4630,7 +4632,9 @@
       <c r="C189" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D189" s="3"/>
+      <c r="D189" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E189" s="10"/>
       <c r="F189" s="10"/>
     </row>
@@ -4644,7 +4648,9 @@
       <c r="C190" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D190" s="3"/>
+      <c r="D190" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E190" s="12"/>
       <c r="F190" s="17"/>
     </row>
@@ -4658,7 +4664,9 @@
       <c r="C191" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D191" s="3"/>
+      <c r="D191" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E191" s="10"/>
       <c r="F191" s="10"/>
     </row>
@@ -4672,7 +4680,9 @@
       <c r="C192" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D192" s="3"/>
+      <c r="D192" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
     </row>
@@ -4686,7 +4696,9 @@
       <c r="C193" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D193" s="3"/>
+      <c r="D193" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E193" s="10"/>
       <c r="F193" s="10"/>
     </row>
@@ -4700,7 +4712,9 @@
       <c r="C194" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D194" s="3"/>
+      <c r="D194" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
     </row>
@@ -4714,7 +4728,9 @@
       <c r="C195" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D195" s="3"/>
+      <c r="D195" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
     </row>
@@ -4728,7 +4744,9 @@
       <c r="C196" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D196" s="3"/>
+      <c r="D196" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E196" s="10"/>
       <c r="F196" s="10"/>
     </row>
@@ -4742,7 +4760,9 @@
       <c r="C197" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D197" s="3"/>
+      <c r="D197" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E197" s="10"/>
       <c r="F197" s="10"/>
     </row>
@@ -4772,7 +4792,9 @@
       <c r="C199" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D199" s="3"/>
+      <c r="D199" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
     </row>
@@ -4786,7 +4808,9 @@
       <c r="C200" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D200" s="3"/>
+      <c r="D200" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
     </row>
@@ -4882,7 +4906,9 @@
       <c r="C206" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D206" s="3"/>
+      <c r="D206" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
     </row>
@@ -4992,7 +5018,9 @@
       <c r="C213" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D213" s="3"/>
+      <c r="D213" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
     </row>
@@ -5054,7 +5082,9 @@
       <c r="C217" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D217" s="3"/>
+      <c r="D217" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
     </row>
@@ -5084,7 +5114,9 @@
       <c r="C219" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D219" s="3"/>
+      <c r="D219" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
     </row>
@@ -5274,7 +5306,9 @@
       <c r="C231" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D231" s="3"/>
+      <c r="D231" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
     </row>
@@ -5320,7 +5354,9 @@
       <c r="C234" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D234" s="3"/>
+      <c r="D234" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E234" s="10"/>
       <c r="F234" s="10"/>
     </row>
@@ -5350,7 +5386,9 @@
       <c r="C236" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D236" s="3"/>
+      <c r="D236" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E236" s="10"/>
       <c r="F236" s="10"/>
     </row>
@@ -5380,7 +5418,9 @@
       <c r="C238" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D238" s="3"/>
+      <c r="D238" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
     </row>
@@ -5426,7 +5466,9 @@
       <c r="C241" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D241" s="3"/>
+      <c r="D241" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
     </row>
@@ -5520,7 +5562,9 @@
       <c r="C247" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D247" s="3"/>
+      <c r="D247" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E247" s="10"/>
       <c r="F247" s="10"/>
     </row>
@@ -5582,7 +5626,9 @@
       <c r="C251" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D251" s="3"/>
+      <c r="D251" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
     </row>
@@ -5612,7 +5658,9 @@
       <c r="C253" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D253" s="3"/>
+      <c r="D253" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
     </row>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994E2518-3845-44F6-BAA7-EB9944141150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E96C116-8923-422B-BA71-4A5E24190475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E96C116-8923-422B-BA71-4A5E24190475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145D58F0-4F27-4B40-AE12-F55476977381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="374">
   <si>
     <t>STT</t>
   </si>
@@ -837,9 +837,6 @@
     <t>Cho mượn</t>
   </si>
   <si>
-    <t>Nhận 180 chưa bắn ID</t>
-  </si>
-  <si>
     <t>16/10/26</t>
   </si>
   <si>
@@ -852,7 +849,307 @@
     <t>Tồn lỗi</t>
   </si>
   <si>
-    <t>180 chưa nhập ID</t>
+    <t>VNET860879084181813</t>
+  </si>
+  <si>
+    <t>VNET860879084180195</t>
+  </si>
+  <si>
+    <t>VNET860879084177613</t>
+  </si>
+  <si>
+    <t>VNET860879084179932</t>
+  </si>
+  <si>
+    <t>VNET860879084182522</t>
+  </si>
+  <si>
+    <t>VNET860879084181987</t>
+  </si>
+  <si>
+    <t>VNET860879084179981</t>
+  </si>
+  <si>
+    <t>VNET860879084180211</t>
+  </si>
+  <si>
+    <t>VNET860879084180120</t>
+  </si>
+  <si>
+    <t>VNET860879084182407</t>
+  </si>
+  <si>
+    <t>VNET860879084180880</t>
+  </si>
+  <si>
+    <t>VNET860879084174362</t>
+  </si>
+  <si>
+    <t>VNET860879084180054</t>
+  </si>
+  <si>
+    <t>VNET860879084175237</t>
+  </si>
+  <si>
+    <t>VNET860879084176003</t>
+  </si>
+  <si>
+    <t>VNET860879084181482</t>
+  </si>
+  <si>
+    <t>VNET860879084180088</t>
+  </si>
+  <si>
+    <t>VNET860879084176011</t>
+  </si>
+  <si>
+    <t>VNET860879084179502</t>
+  </si>
+  <si>
+    <t>VNET860879084179072</t>
+  </si>
+  <si>
+    <t>VNET860879084177787</t>
+  </si>
+  <si>
+    <t>VNET860879084178496</t>
+  </si>
+  <si>
+    <t>VNET860879084179254</t>
+  </si>
+  <si>
+    <t>VNET860879084179676</t>
+  </si>
+  <si>
+    <t>VNET860879084183736</t>
+  </si>
+  <si>
+    <t>VNET860879084180435</t>
+  </si>
+  <si>
+    <t>VNET860879084183280</t>
+  </si>
+  <si>
+    <t>VNET860879084175351</t>
+  </si>
+  <si>
+    <t>VNET860879084175526</t>
+  </si>
+  <si>
+    <t>VNET860879084179593</t>
+  </si>
+  <si>
+    <t>VNET860879084179585</t>
+  </si>
+  <si>
+    <t>VNET860879084181136</t>
+  </si>
+  <si>
+    <t>VNET860879084174669</t>
+  </si>
+  <si>
+    <t>VNET860879084183470</t>
+  </si>
+  <si>
+    <t>VNET860879084180567</t>
+  </si>
+  <si>
+    <t>VNET860879084181862</t>
+  </si>
+  <si>
+    <t>VNET860879084182001</t>
+  </si>
+  <si>
+    <t>VNET860879084174198</t>
+  </si>
+  <si>
+    <t>VNET860879084180369</t>
+  </si>
+  <si>
+    <t>VNET860879084178942</t>
+  </si>
+  <si>
+    <t>VNET860879084175096</t>
+  </si>
+  <si>
+    <t>VNET860879084181706</t>
+  </si>
+  <si>
+    <t>VNET860879084173737</t>
+  </si>
+  <si>
+    <t>VNET860879084173802</t>
+  </si>
+  <si>
+    <t>VNET860879084180930</t>
+  </si>
+  <si>
+    <t>VNET860879084174370</t>
+  </si>
+  <si>
+    <t>VNET860879084174073</t>
+  </si>
+  <si>
+    <t>VNET860879084179114</t>
+  </si>
+  <si>
+    <t>VNET860879084175930</t>
+  </si>
+  <si>
+    <t>VNET860879084180013</t>
+  </si>
+  <si>
+    <t>VNET860879084180245</t>
+  </si>
+  <si>
+    <t>VNET860879084174032</t>
+  </si>
+  <si>
+    <t>VNET860879084182571</t>
+  </si>
+  <si>
+    <t>VNET860879084179734</t>
+  </si>
+  <si>
+    <t>VNET860879084175765</t>
+  </si>
+  <si>
+    <t>VNET860879084183314</t>
+  </si>
+  <si>
+    <t>VNET860879084179528</t>
+  </si>
+  <si>
+    <t>VNET860879084183199</t>
+  </si>
+  <si>
+    <t>VNET860879084180096</t>
+  </si>
+  <si>
+    <t>VNET860879084180021</t>
+  </si>
+  <si>
+    <t>VNET860879084179148</t>
+  </si>
+  <si>
+    <t>VNET860879084174206</t>
+  </si>
+  <si>
+    <t>VNET860879084179874</t>
+  </si>
+  <si>
+    <t>VNET860879084180534</t>
+  </si>
+  <si>
+    <t>VNET860879084183322</t>
+  </si>
+  <si>
+    <t>VNET860879084183504</t>
+  </si>
+  <si>
+    <t>VNET860879084182332</t>
+  </si>
+  <si>
+    <t>VNET860879084181532</t>
+  </si>
+  <si>
+    <t>VNET860879084178314</t>
+  </si>
+  <si>
+    <t>VNET860879084179171</t>
+  </si>
+  <si>
+    <t>VNET860879084183272</t>
+  </si>
+  <si>
+    <t>VNET860879084174057</t>
+  </si>
+  <si>
+    <t>VNET860879084180401</t>
+  </si>
+  <si>
+    <t>VNET860879084182654</t>
+  </si>
+  <si>
+    <t>VNET860879084183348</t>
+  </si>
+  <si>
+    <t>VNET860879084180278</t>
+  </si>
+  <si>
+    <t>VNET860879084179916</t>
+  </si>
+  <si>
+    <t>VNET860879084183207</t>
+  </si>
+  <si>
+    <t>VNET860879084181953</t>
+  </si>
+  <si>
+    <t>VNET860879084180971</t>
+  </si>
+  <si>
+    <t>VNET860879084175856</t>
+  </si>
+  <si>
+    <t>VNET860879084179080</t>
+  </si>
+  <si>
+    <t>VNET860879084179965</t>
+  </si>
+  <si>
+    <t>VNET860879084182704</t>
+  </si>
+  <si>
+    <t>VNET860879084182340</t>
+  </si>
+  <si>
+    <t>VNET860879084181821</t>
+  </si>
+  <si>
+    <t>VNET860879084183355</t>
+  </si>
+  <si>
+    <t>VNET860879084178348</t>
+  </si>
+  <si>
+    <t>VNET860879084180526</t>
+  </si>
+  <si>
+    <t>VNET860879084175633</t>
+  </si>
+  <si>
+    <t>VNET860879084179601</t>
+  </si>
+  <si>
+    <t>VNET860879084182225</t>
+  </si>
+  <si>
+    <t>VNET860879084180187</t>
+  </si>
+  <si>
+    <t>VNET860879084174479</t>
+  </si>
+  <si>
+    <t>VNET860879084177555</t>
+  </si>
+  <si>
+    <t>VNET860879084183371</t>
+  </si>
+  <si>
+    <t>VNET860879084176375</t>
+  </si>
+  <si>
+    <t>VNET860879084180070</t>
+  </si>
+  <si>
+    <t>VNET860879084182274</t>
+  </si>
+  <si>
+    <t>VNET860879084178850</t>
+  </si>
+  <si>
+    <t>80 chưa nhập ID</t>
   </si>
 </sst>
 </file>
@@ -1536,16 +1833,16 @@
         <v>266</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>268</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1565,11 +1862,11 @@
       <c r="F2" s="20"/>
       <c r="G2" s="3">
         <f>COUNTIFS(B2:B1001,"*VNET*")</f>
-        <v>254</v>
+        <v>354</v>
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
-        <v>234</v>
+        <v>334</v>
       </c>
       <c r="I2" s="25">
         <f>COUNTIFS(D2:D1001,"Lỗi")</f>
@@ -1592,7 +1889,7 @@
         <v>9</v>
       </c>
       <c r="N2" t="s">
-        <v>274</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -5701,12 +5998,14 @@
         <v>255</v>
       </c>
       <c r="B256" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C256" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C256" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D256" s="3"/>
+      <c r="D256" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E256" s="10"/>
       <c r="F256" s="10"/>
     </row>
@@ -5714,9 +6013,15 @@
       <c r="A257" s="3">
         <v>256</v>
       </c>
-      <c r="B257" s="4"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="3"/>
+      <c r="B257" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E257" s="10"/>
       <c r="F257" s="10"/>
     </row>
@@ -5724,9 +6029,15 @@
       <c r="A258" s="3">
         <v>257</v>
       </c>
-      <c r="B258" s="4"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="3"/>
+      <c r="B258" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E258" s="10"/>
       <c r="F258" s="10"/>
     </row>
@@ -5734,9 +6045,15 @@
       <c r="A259" s="3">
         <v>258</v>
       </c>
-      <c r="B259" s="4"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="3"/>
+      <c r="B259" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E259" s="10"/>
       <c r="F259" s="10"/>
     </row>
@@ -5744,9 +6061,15 @@
       <c r="A260" s="3">
         <v>259</v>
       </c>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="3"/>
+      <c r="B260" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E260" s="12"/>
       <c r="F260" s="10"/>
     </row>
@@ -5754,9 +6077,15 @@
       <c r="A261" s="3">
         <v>260</v>
       </c>
-      <c r="B261" s="4"/>
-      <c r="C261" s="4"/>
-      <c r="D261" s="3"/>
+      <c r="B261" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E261" s="10"/>
       <c r="F261" s="10"/>
     </row>
@@ -5764,9 +6093,15 @@
       <c r="A262" s="3">
         <v>261</v>
       </c>
-      <c r="B262" s="4"/>
-      <c r="C262" s="4"/>
-      <c r="D262" s="3"/>
+      <c r="B262" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E262" s="10"/>
       <c r="F262" s="10"/>
     </row>
@@ -5774,9 +6109,15 @@
       <c r="A263" s="3">
         <v>262</v>
       </c>
-      <c r="B263" s="4"/>
-      <c r="C263" s="4"/>
-      <c r="D263" s="3"/>
+      <c r="B263" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
     </row>
@@ -5784,9 +6125,15 @@
       <c r="A264" s="3">
         <v>263</v>
       </c>
-      <c r="B264" s="4"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="3"/>
+      <c r="B264" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
     </row>
@@ -5794,9 +6141,15 @@
       <c r="A265" s="3">
         <v>264</v>
       </c>
-      <c r="B265" s="4"/>
-      <c r="C265" s="4"/>
-      <c r="D265" s="3"/>
+      <c r="B265" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
     </row>
@@ -5804,9 +6157,15 @@
       <c r="A266" s="3">
         <v>265</v>
       </c>
-      <c r="B266" s="4"/>
-      <c r="C266" s="4"/>
-      <c r="D266" s="3"/>
+      <c r="B266" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
     </row>
@@ -5814,9 +6173,15 @@
       <c r="A267" s="3">
         <v>266</v>
       </c>
-      <c r="B267" s="4"/>
-      <c r="C267" s="4"/>
-      <c r="D267" s="3"/>
+      <c r="B267" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
     </row>
@@ -5824,9 +6189,15 @@
       <c r="A268" s="3">
         <v>267</v>
       </c>
-      <c r="B268" s="4"/>
-      <c r="C268" s="4"/>
-      <c r="D268" s="3"/>
+      <c r="B268" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
     </row>
@@ -5834,9 +6205,15 @@
       <c r="A269" s="3">
         <v>268</v>
       </c>
-      <c r="B269" s="4"/>
-      <c r="C269" s="4"/>
-      <c r="D269" s="3"/>
+      <c r="B269" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
     </row>
@@ -5844,9 +6221,15 @@
       <c r="A270" s="3">
         <v>269</v>
       </c>
-      <c r="B270" s="4"/>
-      <c r="C270" s="4"/>
-      <c r="D270" s="3"/>
+      <c r="B270" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
     </row>
@@ -5854,9 +6237,15 @@
       <c r="A271" s="3">
         <v>270</v>
       </c>
-      <c r="B271" s="4"/>
-      <c r="C271" s="4"/>
-      <c r="D271" s="3"/>
+      <c r="B271" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
     </row>
@@ -5864,9 +6253,15 @@
       <c r="A272" s="3">
         <v>271</v>
       </c>
-      <c r="B272" s="4"/>
-      <c r="C272" s="4"/>
-      <c r="D272" s="3"/>
+      <c r="B272" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
     </row>
@@ -5874,9 +6269,15 @@
       <c r="A273" s="3">
         <v>272</v>
       </c>
-      <c r="B273" s="4"/>
-      <c r="C273" s="4"/>
-      <c r="D273" s="3"/>
+      <c r="B273" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
     </row>
@@ -5884,9 +6285,15 @@
       <c r="A274" s="3">
         <v>273</v>
       </c>
-      <c r="B274" s="4"/>
-      <c r="C274" s="4"/>
-      <c r="D274" s="3"/>
+      <c r="B274" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
     </row>
@@ -5894,9 +6301,15 @@
       <c r="A275" s="3">
         <v>274</v>
       </c>
-      <c r="B275" s="4"/>
-      <c r="C275" s="4"/>
-      <c r="D275" s="3"/>
+      <c r="B275" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
     </row>
@@ -5904,9 +6317,15 @@
       <c r="A276" s="3">
         <v>275</v>
       </c>
-      <c r="B276" s="4"/>
-      <c r="C276" s="4"/>
-      <c r="D276" s="3"/>
+      <c r="B276" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
     </row>
@@ -5914,9 +6333,15 @@
       <c r="A277" s="3">
         <v>276</v>
       </c>
-      <c r="B277" s="4"/>
-      <c r="C277" s="4"/>
-      <c r="D277" s="3"/>
+      <c r="B277" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
     </row>
@@ -5924,9 +6349,15 @@
       <c r="A278" s="3">
         <v>277</v>
       </c>
-      <c r="B278" s="4"/>
-      <c r="C278" s="4"/>
-      <c r="D278" s="3"/>
+      <c r="B278" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
     </row>
@@ -5934,9 +6365,15 @@
       <c r="A279" s="3">
         <v>278</v>
       </c>
-      <c r="B279" s="4"/>
-      <c r="C279" s="4"/>
-      <c r="D279" s="3"/>
+      <c r="B279" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
     </row>
@@ -5944,9 +6381,15 @@
       <c r="A280" s="3">
         <v>279</v>
       </c>
-      <c r="B280" s="4"/>
-      <c r="C280" s="4"/>
-      <c r="D280" s="3"/>
+      <c r="B280" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
     </row>
@@ -5954,9 +6397,15 @@
       <c r="A281" s="3">
         <v>280</v>
       </c>
-      <c r="B281" s="4"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="3"/>
+      <c r="B281" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
     </row>
@@ -5964,9 +6413,15 @@
       <c r="A282" s="3">
         <v>281</v>
       </c>
-      <c r="B282" s="4"/>
-      <c r="C282" s="4"/>
-      <c r="D282" s="3"/>
+      <c r="B282" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
     </row>
@@ -5974,9 +6429,15 @@
       <c r="A283" s="3">
         <v>282</v>
       </c>
-      <c r="B283" s="4"/>
-      <c r="C283" s="4"/>
-      <c r="D283" s="3"/>
+      <c r="B283" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
     </row>
@@ -5984,9 +6445,15 @@
       <c r="A284" s="3">
         <v>283</v>
       </c>
-      <c r="B284" s="4"/>
-      <c r="C284" s="4"/>
-      <c r="D284" s="3"/>
+      <c r="B284" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
     </row>
@@ -5994,9 +6461,15 @@
       <c r="A285" s="3">
         <v>284</v>
       </c>
-      <c r="B285" s="4"/>
-      <c r="C285" s="4"/>
-      <c r="D285" s="3"/>
+      <c r="B285" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
     </row>
@@ -6004,9 +6477,15 @@
       <c r="A286" s="3">
         <v>285</v>
       </c>
-      <c r="B286" s="4"/>
-      <c r="C286" s="4"/>
-      <c r="D286" s="3"/>
+      <c r="B286" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
     </row>
@@ -6014,9 +6493,15 @@
       <c r="A287" s="3">
         <v>286</v>
       </c>
-      <c r="B287" s="4"/>
-      <c r="C287" s="4"/>
-      <c r="D287" s="3"/>
+      <c r="B287" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
     </row>
@@ -6024,9 +6509,15 @@
       <c r="A288" s="3">
         <v>287</v>
       </c>
-      <c r="B288" s="4"/>
-      <c r="C288" s="4"/>
-      <c r="D288" s="3"/>
+      <c r="B288" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
     </row>
@@ -6034,9 +6525,15 @@
       <c r="A289" s="3">
         <v>288</v>
       </c>
-      <c r="B289" s="4"/>
-      <c r="C289" s="4"/>
-      <c r="D289" s="3"/>
+      <c r="B289" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
     </row>
@@ -6044,9 +6541,15 @@
       <c r="A290" s="3">
         <v>289</v>
       </c>
-      <c r="B290" s="4"/>
-      <c r="C290" s="4"/>
-      <c r="D290" s="3"/>
+      <c r="B290" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
     </row>
@@ -6054,9 +6557,15 @@
       <c r="A291" s="3">
         <v>290</v>
       </c>
-      <c r="B291" s="4"/>
-      <c r="C291" s="4"/>
-      <c r="D291" s="3"/>
+      <c r="B291" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
     </row>
@@ -6064,9 +6573,15 @@
       <c r="A292" s="3">
         <v>291</v>
       </c>
-      <c r="B292" s="4"/>
-      <c r="C292" s="4"/>
-      <c r="D292" s="3"/>
+      <c r="B292" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
     </row>
@@ -6074,9 +6589,15 @@
       <c r="A293" s="3">
         <v>292</v>
       </c>
-      <c r="B293" s="4"/>
-      <c r="C293" s="4"/>
-      <c r="D293" s="3"/>
+      <c r="B293" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
     </row>
@@ -6084,9 +6605,15 @@
       <c r="A294" s="3">
         <v>293</v>
       </c>
-      <c r="B294" s="4"/>
-      <c r="C294" s="4"/>
-      <c r="D294" s="3"/>
+      <c r="B294" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
     </row>
@@ -6094,9 +6621,15 @@
       <c r="A295" s="3">
         <v>294</v>
       </c>
-      <c r="B295" s="4"/>
-      <c r="C295" s="4"/>
-      <c r="D295" s="3"/>
+      <c r="B295" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
     </row>
@@ -6104,9 +6637,15 @@
       <c r="A296" s="3">
         <v>295</v>
       </c>
-      <c r="B296" s="4"/>
-      <c r="C296" s="4"/>
-      <c r="D296" s="3"/>
+      <c r="B296" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
     </row>
@@ -6114,9 +6653,15 @@
       <c r="A297" s="3">
         <v>296</v>
       </c>
-      <c r="B297" s="4"/>
-      <c r="C297" s="4"/>
-      <c r="D297" s="3"/>
+      <c r="B297" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
     </row>
@@ -6124,9 +6669,15 @@
       <c r="A298" s="3">
         <v>297</v>
       </c>
-      <c r="B298" s="4"/>
-      <c r="C298" s="4"/>
-      <c r="D298" s="3"/>
+      <c r="B298" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
     </row>
@@ -6134,9 +6685,15 @@
       <c r="A299" s="3">
         <v>298</v>
       </c>
-      <c r="B299" s="4"/>
-      <c r="C299" s="4"/>
-      <c r="D299" s="3"/>
+      <c r="B299" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
     </row>
@@ -6144,9 +6701,15 @@
       <c r="A300" s="3">
         <v>299</v>
       </c>
-      <c r="B300" s="4"/>
-      <c r="C300" s="4"/>
-      <c r="D300" s="3"/>
+      <c r="B300" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
     </row>
@@ -6154,9 +6717,15 @@
       <c r="A301" s="3">
         <v>300</v>
       </c>
-      <c r="B301" s="4"/>
-      <c r="C301" s="4"/>
-      <c r="D301" s="3"/>
+      <c r="B301" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
     </row>
@@ -6164,9 +6733,15 @@
       <c r="A302" s="3">
         <v>301</v>
       </c>
-      <c r="B302" s="4"/>
-      <c r="C302" s="4"/>
-      <c r="D302" s="3"/>
+      <c r="B302" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
     </row>
@@ -6174,9 +6749,15 @@
       <c r="A303" s="3">
         <v>302</v>
       </c>
-      <c r="B303" s="4"/>
-      <c r="C303" s="4"/>
-      <c r="D303" s="3"/>
+      <c r="B303" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
     </row>
@@ -6184,9 +6765,15 @@
       <c r="A304" s="3">
         <v>303</v>
       </c>
-      <c r="B304" s="4"/>
-      <c r="C304" s="4"/>
-      <c r="D304" s="3"/>
+      <c r="B304" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
     </row>
@@ -6194,9 +6781,15 @@
       <c r="A305" s="3">
         <v>304</v>
       </c>
-      <c r="B305" s="4"/>
-      <c r="C305" s="4"/>
-      <c r="D305" s="3"/>
+      <c r="B305" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
     </row>
@@ -6204,9 +6797,15 @@
       <c r="A306" s="3">
         <v>305</v>
       </c>
-      <c r="B306" s="4"/>
-      <c r="C306" s="4"/>
-      <c r="D306" s="3"/>
+      <c r="B306" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
     </row>
@@ -6214,9 +6813,15 @@
       <c r="A307" s="3">
         <v>306</v>
       </c>
-      <c r="B307" s="4"/>
-      <c r="C307" s="4"/>
-      <c r="D307" s="3"/>
+      <c r="B307" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
     </row>
@@ -6224,9 +6829,15 @@
       <c r="A308" s="3">
         <v>307</v>
       </c>
-      <c r="B308" s="4"/>
-      <c r="C308" s="4"/>
-      <c r="D308" s="3"/>
+      <c r="B308" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
     </row>
@@ -6234,9 +6845,15 @@
       <c r="A309" s="3">
         <v>308</v>
       </c>
-      <c r="B309" s="4"/>
-      <c r="C309" s="4"/>
-      <c r="D309" s="3"/>
+      <c r="B309" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
     </row>
@@ -6244,9 +6861,15 @@
       <c r="A310" s="3">
         <v>309</v>
       </c>
-      <c r="B310" s="4"/>
-      <c r="C310" s="4"/>
-      <c r="D310" s="3"/>
+      <c r="B310" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
     </row>
@@ -6254,9 +6877,15 @@
       <c r="A311" s="3">
         <v>310</v>
       </c>
-      <c r="B311" s="4"/>
-      <c r="C311" s="4"/>
-      <c r="D311" s="3"/>
+      <c r="B311" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
     </row>
@@ -6264,9 +6893,15 @@
       <c r="A312" s="3">
         <v>311</v>
       </c>
-      <c r="B312" s="4"/>
-      <c r="C312" s="4"/>
-      <c r="D312" s="3"/>
+      <c r="B312" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
     </row>
@@ -6274,9 +6909,15 @@
       <c r="A313" s="3">
         <v>312</v>
       </c>
-      <c r="B313" s="4"/>
-      <c r="C313" s="4"/>
-      <c r="D313" s="3"/>
+      <c r="B313" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
     </row>
@@ -6284,9 +6925,15 @@
       <c r="A314" s="3">
         <v>313</v>
       </c>
-      <c r="B314" s="4"/>
-      <c r="C314" s="4"/>
-      <c r="D314" s="3"/>
+      <c r="B314" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
     </row>
@@ -6294,9 +6941,15 @@
       <c r="A315" s="3">
         <v>314</v>
       </c>
-      <c r="B315" s="4"/>
-      <c r="C315" s="4"/>
-      <c r="D315" s="3"/>
+      <c r="B315" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
     </row>
@@ -6304,9 +6957,15 @@
       <c r="A316" s="3">
         <v>315</v>
       </c>
-      <c r="B316" s="4"/>
-      <c r="C316" s="4"/>
-      <c r="D316" s="3"/>
+      <c r="B316" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
     </row>
@@ -6314,9 +6973,15 @@
       <c r="A317" s="3">
         <v>316</v>
       </c>
-      <c r="B317" s="4"/>
-      <c r="C317" s="4"/>
-      <c r="D317" s="3"/>
+      <c r="B317" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
     </row>
@@ -6324,9 +6989,15 @@
       <c r="A318" s="3">
         <v>317</v>
       </c>
-      <c r="B318" s="4"/>
-      <c r="C318" s="4"/>
-      <c r="D318" s="3"/>
+      <c r="B318" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
     </row>
@@ -6334,9 +7005,15 @@
       <c r="A319" s="3">
         <v>318</v>
       </c>
-      <c r="B319" s="4"/>
-      <c r="C319" s="4"/>
-      <c r="D319" s="3"/>
+      <c r="B319" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
     </row>
@@ -6344,9 +7021,15 @@
       <c r="A320" s="3">
         <v>319</v>
       </c>
-      <c r="B320" s="4"/>
-      <c r="C320" s="4"/>
-      <c r="D320" s="3"/>
+      <c r="B320" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
     </row>
@@ -6354,9 +7037,15 @@
       <c r="A321" s="3">
         <v>320</v>
       </c>
-      <c r="B321" s="4"/>
-      <c r="C321" s="4"/>
-      <c r="D321" s="3"/>
+      <c r="B321" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
     </row>
@@ -6364,9 +7053,15 @@
       <c r="A322" s="3">
         <v>321</v>
       </c>
-      <c r="B322" s="4"/>
-      <c r="C322" s="4"/>
-      <c r="D322" s="3"/>
+      <c r="B322" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
     </row>
@@ -6374,9 +7069,15 @@
       <c r="A323" s="3">
         <v>322</v>
       </c>
-      <c r="B323" s="4"/>
-      <c r="C323" s="4"/>
-      <c r="D323" s="3"/>
+      <c r="B323" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
     </row>
@@ -6384,9 +7085,15 @@
       <c r="A324" s="3">
         <v>323</v>
       </c>
-      <c r="B324" s="4"/>
-      <c r="C324" s="4"/>
-      <c r="D324" s="3"/>
+      <c r="B324" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
     </row>
@@ -6394,9 +7101,15 @@
       <c r="A325" s="3">
         <v>324</v>
       </c>
-      <c r="B325" s="4"/>
-      <c r="C325" s="4"/>
-      <c r="D325" s="3"/>
+      <c r="B325" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
     </row>
@@ -6404,9 +7117,15 @@
       <c r="A326" s="3">
         <v>325</v>
       </c>
-      <c r="B326" s="4"/>
-      <c r="C326" s="4"/>
-      <c r="D326" s="3"/>
+      <c r="B326" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
     </row>
@@ -6414,9 +7133,15 @@
       <c r="A327" s="3">
         <v>326</v>
       </c>
-      <c r="B327" s="4"/>
-      <c r="C327" s="4"/>
-      <c r="D327" s="3"/>
+      <c r="B327" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
     </row>
@@ -6424,9 +7149,15 @@
       <c r="A328" s="3">
         <v>327</v>
       </c>
-      <c r="B328" s="4"/>
-      <c r="C328" s="4"/>
-      <c r="D328" s="3"/>
+      <c r="B328" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
     </row>
@@ -6434,9 +7165,15 @@
       <c r="A329" s="3">
         <v>328</v>
       </c>
-      <c r="B329" s="4"/>
-      <c r="C329" s="4"/>
-      <c r="D329" s="3"/>
+      <c r="B329" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
     </row>
@@ -6444,9 +7181,15 @@
       <c r="A330" s="3">
         <v>329</v>
       </c>
-      <c r="B330" s="4"/>
-      <c r="C330" s="4"/>
-      <c r="D330" s="3"/>
+      <c r="B330" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
     </row>
@@ -6454,9 +7197,15 @@
       <c r="A331" s="3">
         <v>330</v>
       </c>
-      <c r="B331" s="4"/>
-      <c r="C331" s="4"/>
-      <c r="D331" s="3"/>
+      <c r="B331" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
     </row>
@@ -6464,9 +7213,15 @@
       <c r="A332" s="3">
         <v>331</v>
       </c>
-      <c r="B332" s="4"/>
-      <c r="C332" s="4"/>
-      <c r="D332" s="3"/>
+      <c r="B332" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
     </row>
@@ -6474,9 +7229,15 @@
       <c r="A333" s="3">
         <v>332</v>
       </c>
-      <c r="B333" s="4"/>
-      <c r="C333" s="4"/>
-      <c r="D333" s="3"/>
+      <c r="B333" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
     </row>
@@ -6484,9 +7245,15 @@
       <c r="A334" s="3">
         <v>333</v>
       </c>
-      <c r="B334" s="4"/>
-      <c r="C334" s="4"/>
-      <c r="D334" s="3"/>
+      <c r="B334" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
     </row>
@@ -6494,9 +7261,15 @@
       <c r="A335" s="3">
         <v>334</v>
       </c>
-      <c r="B335" s="4"/>
-      <c r="C335" s="4"/>
-      <c r="D335" s="3"/>
+      <c r="B335" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
     </row>
@@ -6504,9 +7277,15 @@
       <c r="A336" s="3">
         <v>335</v>
       </c>
-      <c r="B336" s="4"/>
-      <c r="C336" s="4"/>
-      <c r="D336" s="3"/>
+      <c r="B336" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
     </row>
@@ -6514,9 +7293,15 @@
       <c r="A337" s="3">
         <v>336</v>
       </c>
-      <c r="B337" s="4"/>
-      <c r="C337" s="4"/>
-      <c r="D337" s="3"/>
+      <c r="B337" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
     </row>
@@ -6524,9 +7309,15 @@
       <c r="A338" s="3">
         <v>337</v>
       </c>
-      <c r="B338" s="4"/>
-      <c r="C338" s="4"/>
-      <c r="D338" s="3"/>
+      <c r="B338" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
     </row>
@@ -6534,9 +7325,15 @@
       <c r="A339" s="3">
         <v>338</v>
       </c>
-      <c r="B339" s="4"/>
-      <c r="C339" s="4"/>
-      <c r="D339" s="3"/>
+      <c r="B339" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
     </row>
@@ -6544,9 +7341,15 @@
       <c r="A340" s="3">
         <v>339</v>
       </c>
-      <c r="B340" s="4"/>
-      <c r="C340" s="4"/>
-      <c r="D340" s="3"/>
+      <c r="B340" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
     </row>
@@ -6554,9 +7357,15 @@
       <c r="A341" s="3">
         <v>340</v>
       </c>
-      <c r="B341" s="4"/>
-      <c r="C341" s="4"/>
-      <c r="D341" s="3"/>
+      <c r="B341" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
     </row>
@@ -6564,9 +7373,15 @@
       <c r="A342" s="3">
         <v>341</v>
       </c>
-      <c r="B342" s="4"/>
-      <c r="C342" s="4"/>
-      <c r="D342" s="3"/>
+      <c r="B342" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
     </row>
@@ -6574,9 +7389,15 @@
       <c r="A343" s="3">
         <v>342</v>
       </c>
-      <c r="B343" s="4"/>
-      <c r="C343" s="4"/>
-      <c r="D343" s="3"/>
+      <c r="B343" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
     </row>
@@ -6584,9 +7405,15 @@
       <c r="A344" s="3">
         <v>343</v>
       </c>
-      <c r="B344" s="4"/>
-      <c r="C344" s="4"/>
-      <c r="D344" s="3"/>
+      <c r="B344" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
     </row>
@@ -6594,9 +7421,15 @@
       <c r="A345" s="3">
         <v>344</v>
       </c>
-      <c r="B345" s="4"/>
-      <c r="C345" s="4"/>
-      <c r="D345" s="3"/>
+      <c r="B345" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
     </row>
@@ -6604,9 +7437,15 @@
       <c r="A346" s="3">
         <v>345</v>
       </c>
-      <c r="B346" s="4"/>
-      <c r="C346" s="4"/>
-      <c r="D346" s="3"/>
+      <c r="B346" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
     </row>
@@ -6614,9 +7453,15 @@
       <c r="A347" s="3">
         <v>346</v>
       </c>
-      <c r="B347" s="4"/>
-      <c r="C347" s="4"/>
-      <c r="D347" s="3"/>
+      <c r="B347" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
     </row>
@@ -6624,9 +7469,15 @@
       <c r="A348" s="3">
         <v>347</v>
       </c>
-      <c r="B348" s="4"/>
-      <c r="C348" s="4"/>
-      <c r="D348" s="3"/>
+      <c r="B348" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
     </row>
@@ -6634,9 +7485,15 @@
       <c r="A349" s="3">
         <v>348</v>
       </c>
-      <c r="B349" s="4"/>
-      <c r="C349" s="4"/>
-      <c r="D349" s="3"/>
+      <c r="B349" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
     </row>
@@ -6644,9 +7501,15 @@
       <c r="A350" s="3">
         <v>349</v>
       </c>
-      <c r="B350" s="4"/>
-      <c r="C350" s="4"/>
-      <c r="D350" s="3"/>
+      <c r="B350" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
     </row>
@@ -6654,9 +7517,15 @@
       <c r="A351" s="3">
         <v>350</v>
       </c>
-      <c r="B351" s="4"/>
-      <c r="C351" s="4"/>
-      <c r="D351" s="3"/>
+      <c r="B351" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E351" s="3"/>
       <c r="F351" s="3"/>
     </row>
@@ -6664,9 +7533,15 @@
       <c r="A352" s="3">
         <v>351</v>
       </c>
-      <c r="B352" s="4"/>
-      <c r="C352" s="4"/>
-      <c r="D352" s="3"/>
+      <c r="B352" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
     </row>
@@ -6674,9 +7549,15 @@
       <c r="A353" s="3">
         <v>352</v>
       </c>
-      <c r="B353" s="4"/>
-      <c r="C353" s="4"/>
-      <c r="D353" s="3"/>
+      <c r="B353" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
     </row>
@@ -6684,9 +7565,15 @@
       <c r="A354" s="3">
         <v>353</v>
       </c>
-      <c r="B354" s="4"/>
-      <c r="C354" s="4"/>
-      <c r="D354" s="3"/>
+      <c r="B354" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E354" s="3"/>
       <c r="F354" s="3"/>
     </row>
@@ -6694,9 +7581,15 @@
       <c r="A355" s="3">
         <v>354</v>
       </c>
-      <c r="B355" s="4"/>
-      <c r="C355" s="4"/>
-      <c r="D355" s="3"/>
+      <c r="B355" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
     </row>
@@ -6704,8 +7597,12 @@
       <c r="A356" s="3">
         <v>355</v>
       </c>
-      <c r="B356" s="4"/>
-      <c r="C356" s="4"/>
+      <c r="B356" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145D58F0-4F27-4B40-AE12-F55476977381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCFEB52-4DE3-47CC-97BA-26D1D6FDFAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="400">
   <si>
     <t>STT</t>
   </si>
@@ -1149,7 +1149,85 @@
     <t>VNET860879084178850</t>
   </si>
   <si>
-    <t>80 chưa nhập ID</t>
+    <t>VNET860879084177548</t>
+  </si>
+  <si>
+    <t>VNET860879084181235</t>
+  </si>
+  <si>
+    <t>VNET860879084178561</t>
+  </si>
+  <si>
+    <t>VNET860879084173869</t>
+  </si>
+  <si>
+    <t>VNET860879084173927</t>
+  </si>
+  <si>
+    <t>VNET860879084174008</t>
+  </si>
+  <si>
+    <t>VNET860879084181631</t>
+  </si>
+  <si>
+    <t>VNET860879084182365</t>
+  </si>
+  <si>
+    <t>VNET860879084182076</t>
+  </si>
+  <si>
+    <t>VNET860879084178967</t>
+  </si>
+  <si>
+    <t>VNET860879084177043</t>
+  </si>
+  <si>
+    <t>VNET860879084174404</t>
+  </si>
+  <si>
+    <t>VNET860879084181458</t>
+  </si>
+  <si>
+    <t>VNET860879084176987</t>
+  </si>
+  <si>
+    <t>VNET860879084175666</t>
+  </si>
+  <si>
+    <t>VNET860879084179338</t>
+  </si>
+  <si>
+    <t>VNET860879084182241</t>
+  </si>
+  <si>
+    <t>VNET860879084176318</t>
+  </si>
+  <si>
+    <t>VNET860879084181755</t>
+  </si>
+  <si>
+    <t>VNET860879084180005</t>
+  </si>
+  <si>
+    <t>VNET860879084179387</t>
+  </si>
+  <si>
+    <t>VNET860879084178033</t>
+  </si>
+  <si>
+    <t>VNET860879084181680</t>
+  </si>
+  <si>
+    <t>X-Force trả lại</t>
+  </si>
+  <si>
+    <t>Trả lại X-Force ngày 13/10/26, nhận lại ngày 16/10/2026</t>
+  </si>
+  <si>
+    <t>Còn 56 thiết bị chưa nhập ID</t>
+  </si>
+  <si>
+    <t>56 chưa nhập ID</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1344,6 +1422,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1862,7 +1943,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="3">
         <f>COUNTIFS(B2:B1001,"*VNET*")</f>
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
@@ -1886,10 +1967,10 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -4347,7 +4428,7 @@
       </c>
       <c r="F153" s="10"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -4360,8 +4441,8 @@
       <c r="D154" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E154" s="14" t="s">
-        <v>165</v>
+      <c r="E154" s="32" t="s">
+        <v>397</v>
       </c>
       <c r="F154" s="10"/>
     </row>
@@ -7611,8 +7692,12 @@
       <c r="A357" s="3">
         <v>356</v>
       </c>
-      <c r="B357" s="4"/>
-      <c r="C357" s="4"/>
+      <c r="B357" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
@@ -7621,8 +7706,12 @@
       <c r="A358" s="3">
         <v>357</v>
       </c>
-      <c r="B358" s="4"/>
-      <c r="C358" s="4"/>
+      <c r="B358" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
@@ -7631,8 +7720,12 @@
       <c r="A359" s="3">
         <v>358</v>
       </c>
-      <c r="B359" s="4"/>
-      <c r="C359" s="4"/>
+      <c r="B359" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
@@ -7641,8 +7734,12 @@
       <c r="A360" s="3">
         <v>359</v>
       </c>
-      <c r="B360" s="4"/>
-      <c r="C360" s="4"/>
+      <c r="B360" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
@@ -7651,8 +7748,12 @@
       <c r="A361" s="3">
         <v>360</v>
       </c>
-      <c r="B361" s="4"/>
-      <c r="C361" s="4"/>
+      <c r="B361" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
@@ -7661,8 +7762,12 @@
       <c r="A362" s="3">
         <v>361</v>
       </c>
-      <c r="B362" s="4"/>
-      <c r="C362" s="4"/>
+      <c r="B362" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
@@ -7671,8 +7776,12 @@
       <c r="A363" s="3">
         <v>362</v>
       </c>
-      <c r="B363" s="4"/>
-      <c r="C363" s="4"/>
+      <c r="B363" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
@@ -7681,8 +7790,12 @@
       <c r="A364" s="3">
         <v>363</v>
       </c>
-      <c r="B364" s="4"/>
-      <c r="C364" s="4"/>
+      <c r="B364" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
@@ -7691,8 +7804,12 @@
       <c r="A365" s="3">
         <v>364</v>
       </c>
-      <c r="B365" s="4"/>
-      <c r="C365" s="4"/>
+      <c r="B365" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
@@ -7701,8 +7818,12 @@
       <c r="A366" s="3">
         <v>365</v>
       </c>
-      <c r="B366" s="4"/>
-      <c r="C366" s="4"/>
+      <c r="B366" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
@@ -7711,8 +7832,12 @@
       <c r="A367" s="3">
         <v>366</v>
       </c>
-      <c r="B367" s="4"/>
-      <c r="C367" s="4"/>
+      <c r="B367" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
@@ -7721,18 +7846,28 @@
       <c r="A368" s="3">
         <v>367</v>
       </c>
-      <c r="B368" s="4"/>
-      <c r="C368" s="4"/>
+      <c r="B368" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D368" s="3"/>
-      <c r="E368" s="3"/>
+      <c r="E368" s="3" t="s">
+        <v>396</v>
+      </c>
       <c r="F368" s="3"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>368</v>
       </c>
-      <c r="B369" s="4"/>
-      <c r="C369" s="4"/>
+      <c r="B369" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
@@ -7741,8 +7876,12 @@
       <c r="A370" s="3">
         <v>369</v>
       </c>
-      <c r="B370" s="4"/>
-      <c r="C370" s="4"/>
+      <c r="B370" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
@@ -7751,8 +7890,12 @@
       <c r="A371" s="3">
         <v>370</v>
       </c>
-      <c r="B371" s="4"/>
-      <c r="C371" s="4"/>
+      <c r="B371" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
@@ -7761,8 +7904,12 @@
       <c r="A372" s="3">
         <v>371</v>
       </c>
-      <c r="B372" s="4"/>
-      <c r="C372" s="4"/>
+      <c r="B372" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
@@ -7771,8 +7918,12 @@
       <c r="A373" s="3">
         <v>372</v>
       </c>
-      <c r="B373" s="4"/>
-      <c r="C373" s="4"/>
+      <c r="B373" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
@@ -7781,8 +7932,12 @@
       <c r="A374" s="3">
         <v>373</v>
       </c>
-      <c r="B374" s="4"/>
-      <c r="C374" s="4"/>
+      <c r="B374" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
@@ -7791,8 +7946,12 @@
       <c r="A375" s="3">
         <v>374</v>
       </c>
-      <c r="B375" s="4"/>
-      <c r="C375" s="4"/>
+      <c r="B375" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
@@ -7801,8 +7960,12 @@
       <c r="A376" s="3">
         <v>375</v>
       </c>
-      <c r="B376" s="4"/>
-      <c r="C376" s="4"/>
+      <c r="B376" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
@@ -7811,8 +7974,12 @@
       <c r="A377" s="3">
         <v>376</v>
       </c>
-      <c r="B377" s="4"/>
-      <c r="C377" s="4"/>
+      <c r="B377" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
@@ -7821,8 +7988,12 @@
       <c r="A378" s="3">
         <v>377</v>
       </c>
-      <c r="B378" s="4"/>
-      <c r="C378" s="4"/>
+      <c r="B378" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
@@ -7831,8 +8002,12 @@
       <c r="A379" s="3">
         <v>378</v>
       </c>
-      <c r="B379" s="4"/>
-      <c r="C379" s="4"/>
+      <c r="B379" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
@@ -7841,8 +8016,12 @@
       <c r="A380" s="3">
         <v>379</v>
       </c>
-      <c r="B380" s="4"/>
-      <c r="C380" s="4"/>
+      <c r="B380" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCFEB52-4DE3-47CC-97BA-26D1D6FDFAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0036948C-3082-41DE-A179-B43190BB7BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="454">
   <si>
     <t>STT</t>
   </si>
@@ -1224,10 +1224,172 @@
     <t>Trả lại X-Force ngày 13/10/26, nhận lại ngày 16/10/2026</t>
   </si>
   <si>
-    <t>Còn 56 thiết bị chưa nhập ID</t>
-  </si>
-  <si>
-    <t>56 chưa nhập ID</t>
+    <t>VNET860879084179486</t>
+  </si>
+  <si>
+    <t>VNET860879084181748</t>
+  </si>
+  <si>
+    <t>VNET860879084180351</t>
+  </si>
+  <si>
+    <t>VNET860879084182845</t>
+  </si>
+  <si>
+    <t>VNET860879084174107</t>
+  </si>
+  <si>
+    <t>VNET860879084176995</t>
+  </si>
+  <si>
+    <t>VNET860879084181276</t>
+  </si>
+  <si>
+    <t>VNET860879084174065</t>
+  </si>
+  <si>
+    <t>VNET860879084179494</t>
+  </si>
+  <si>
+    <t>VNET860879084180641</t>
+  </si>
+  <si>
+    <t>VNET860879084178678</t>
+  </si>
+  <si>
+    <t>VNET860879084182761</t>
+  </si>
+  <si>
+    <t>VNET860879084181961</t>
+  </si>
+  <si>
+    <t>VNET860879084174347</t>
+  </si>
+  <si>
+    <t>VNET860879084180716</t>
+  </si>
+  <si>
+    <t>VNET860879084173778</t>
+  </si>
+  <si>
+    <t>VNET860879084182118</t>
+  </si>
+  <si>
+    <t>VNET860879084182266</t>
+  </si>
+  <si>
+    <t>VNET860879084175476</t>
+  </si>
+  <si>
+    <t>VNET860879084174461</t>
+  </si>
+  <si>
+    <t>VNET860879084179197</t>
+  </si>
+  <si>
+    <t>VNET860879084177118</t>
+  </si>
+  <si>
+    <t>VNET860879084181714</t>
+  </si>
+  <si>
+    <t>VNET860879084176037</t>
+  </si>
+  <si>
+    <t>VNET860879084175955</t>
+  </si>
+  <si>
+    <t>VNET860879084182670</t>
+  </si>
+  <si>
+    <t>VNET860879084182803</t>
+  </si>
+  <si>
+    <t>VNET860879084178991</t>
+  </si>
+  <si>
+    <t>VNET860879084179957</t>
+  </si>
+  <si>
+    <t>VNET860879084177571</t>
+  </si>
+  <si>
+    <t>VNET860879084180419</t>
+  </si>
+  <si>
+    <t>VNET860879084179130</t>
+  </si>
+  <si>
+    <t>VNET860879084180708</t>
+  </si>
+  <si>
+    <t>VNET860879084179155</t>
+  </si>
+  <si>
+    <t>VNET860879084180260</t>
+  </si>
+  <si>
+    <t>VNET860879084180237</t>
+  </si>
+  <si>
+    <t>VNET860879084183330</t>
+  </si>
+  <si>
+    <t>VNET860879084177381</t>
+  </si>
+  <si>
+    <t>VNET860879084180773</t>
+  </si>
+  <si>
+    <t>VNET860879084183710</t>
+  </si>
+  <si>
+    <t>VNET860879084181367</t>
+  </si>
+  <si>
+    <t>VNET860879084181102</t>
+  </si>
+  <si>
+    <t>VNET860879084180799</t>
+  </si>
+  <si>
+    <t>VNET860879084181995</t>
+  </si>
+  <si>
+    <t>VNET860879084183363</t>
+  </si>
+  <si>
+    <t>VNET860879084180062</t>
+  </si>
+  <si>
+    <t>VNET860879084183629</t>
+  </si>
+  <si>
+    <t>VNET860879084180450</t>
+  </si>
+  <si>
+    <t>VNET860879084182662</t>
+  </si>
+  <si>
+    <t>VNET860879084178827</t>
+  </si>
+  <si>
+    <t>VNET860879084179452</t>
+  </si>
+  <si>
+    <t>VNET860879084180906</t>
+  </si>
+  <si>
+    <t>VNET860879084180591</t>
+  </si>
+  <si>
+    <t>VNET860879084176094</t>
+  </si>
+  <si>
+    <t>VNET860879084181540</t>
+  </si>
+  <si>
+    <t>VNET860879084180302</t>
   </si>
 </sst>
 </file>
@@ -1871,7 +2033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:N1001"/>
+  <dimension ref="A1:M1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="8" customWidth="1"/>
@@ -1887,7 +2049,7 @@
     <col min="13" max="13" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +2088,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1943,7 +2105,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="3">
         <f>COUNTIFS(B2:B1001,"*VNET*")</f>
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
@@ -1967,13 +2129,10 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>33</v>
-      </c>
-      <c r="N2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1991,7 +2150,7 @@
       <c r="G3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2008,7 +2167,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2025,7 +2184,7 @@
       <c r="F5" s="15"/>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2042,7 +2201,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2059,7 +2218,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2076,7 +2235,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2093,7 +2252,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2110,7 +2269,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2127,7 +2286,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2144,7 +2303,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2161,7 +2320,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2178,7 +2337,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2195,7 +2354,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -8030,8 +8189,12 @@
       <c r="A381" s="3">
         <v>380</v>
       </c>
-      <c r="B381" s="4"/>
-      <c r="C381" s="4"/>
+      <c r="B381" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
@@ -8040,8 +8203,12 @@
       <c r="A382" s="3">
         <v>381</v>
       </c>
-      <c r="B382" s="4"/>
-      <c r="C382" s="4"/>
+      <c r="B382" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
@@ -8050,8 +8217,12 @@
       <c r="A383" s="3">
         <v>382</v>
       </c>
-      <c r="B383" s="4"/>
-      <c r="C383" s="4"/>
+      <c r="B383" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
@@ -8060,8 +8231,12 @@
       <c r="A384" s="3">
         <v>383</v>
       </c>
-      <c r="B384" s="4"/>
-      <c r="C384" s="4"/>
+      <c r="B384" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
@@ -8070,8 +8245,12 @@
       <c r="A385" s="3">
         <v>384</v>
       </c>
-      <c r="B385" s="4"/>
-      <c r="C385" s="4"/>
+      <c r="B385" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
@@ -8080,8 +8259,12 @@
       <c r="A386" s="3">
         <v>385</v>
       </c>
-      <c r="B386" s="4"/>
-      <c r="C386" s="4"/>
+      <c r="B386" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
@@ -8090,8 +8273,12 @@
       <c r="A387" s="3">
         <v>386</v>
       </c>
-      <c r="B387" s="4"/>
-      <c r="C387" s="4"/>
+      <c r="B387" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
@@ -8100,8 +8287,12 @@
       <c r="A388" s="3">
         <v>387</v>
       </c>
-      <c r="B388" s="4"/>
-      <c r="C388" s="4"/>
+      <c r="B388" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
@@ -8110,8 +8301,12 @@
       <c r="A389" s="3">
         <v>388</v>
       </c>
-      <c r="B389" s="4"/>
-      <c r="C389" s="4"/>
+      <c r="B389" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
@@ -8120,8 +8315,12 @@
       <c r="A390" s="3">
         <v>389</v>
       </c>
-      <c r="B390" s="4"/>
-      <c r="C390" s="4"/>
+      <c r="B390" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
@@ -8130,8 +8329,12 @@
       <c r="A391" s="3">
         <v>390</v>
       </c>
-      <c r="B391" s="4"/>
-      <c r="C391" s="4"/>
+      <c r="B391" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
@@ -8140,8 +8343,12 @@
       <c r="A392" s="3">
         <v>391</v>
       </c>
-      <c r="B392" s="4"/>
-      <c r="C392" s="4"/>
+      <c r="B392" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
@@ -8150,8 +8357,12 @@
       <c r="A393" s="3">
         <v>392</v>
       </c>
-      <c r="B393" s="4"/>
-      <c r="C393" s="4"/>
+      <c r="B393" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
@@ -8160,8 +8371,12 @@
       <c r="A394" s="3">
         <v>393</v>
       </c>
-      <c r="B394" s="4"/>
-      <c r="C394" s="4"/>
+      <c r="B394" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
@@ -8170,8 +8385,12 @@
       <c r="A395" s="3">
         <v>394</v>
       </c>
-      <c r="B395" s="4"/>
-      <c r="C395" s="4"/>
+      <c r="B395" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
@@ -8180,8 +8399,12 @@
       <c r="A396" s="3">
         <v>395</v>
       </c>
-      <c r="B396" s="4"/>
-      <c r="C396" s="4"/>
+      <c r="B396" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
@@ -8190,8 +8413,12 @@
       <c r="A397" s="3">
         <v>396</v>
       </c>
-      <c r="B397" s="4"/>
-      <c r="C397" s="4"/>
+      <c r="B397" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
@@ -8200,8 +8427,12 @@
       <c r="A398" s="3">
         <v>397</v>
       </c>
-      <c r="B398" s="4"/>
-      <c r="C398" s="4"/>
+      <c r="B398" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
@@ -8210,8 +8441,12 @@
       <c r="A399" s="3">
         <v>398</v>
       </c>
-      <c r="B399" s="4"/>
-      <c r="C399" s="4"/>
+      <c r="B399" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
@@ -8220,8 +8455,12 @@
       <c r="A400" s="3">
         <v>399</v>
       </c>
-      <c r="B400" s="4"/>
-      <c r="C400" s="4"/>
+      <c r="B400" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
@@ -8230,8 +8469,12 @@
       <c r="A401" s="3">
         <v>400</v>
       </c>
-      <c r="B401" s="4"/>
-      <c r="C401" s="4"/>
+      <c r="B401" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
@@ -8240,8 +8483,12 @@
       <c r="A402" s="3">
         <v>401</v>
       </c>
-      <c r="B402" s="4"/>
-      <c r="C402" s="4"/>
+      <c r="B402" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
@@ -8250,8 +8497,12 @@
       <c r="A403" s="3">
         <v>402</v>
       </c>
-      <c r="B403" s="4"/>
-      <c r="C403" s="4"/>
+      <c r="B403" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D403" s="3"/>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
@@ -8260,8 +8511,12 @@
       <c r="A404" s="3">
         <v>403</v>
       </c>
-      <c r="B404" s="4"/>
-      <c r="C404" s="4"/>
+      <c r="B404" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
@@ -8270,8 +8525,12 @@
       <c r="A405" s="3">
         <v>404</v>
       </c>
-      <c r="B405" s="4"/>
-      <c r="C405" s="4"/>
+      <c r="B405" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D405" s="3"/>
       <c r="E405" s="14"/>
       <c r="F405" s="3"/>
@@ -8280,8 +8539,12 @@
       <c r="A406" s="3">
         <v>405</v>
       </c>
-      <c r="B406" s="4"/>
-      <c r="C406" s="4"/>
+      <c r="B406" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
@@ -8290,8 +8553,12 @@
       <c r="A407" s="3">
         <v>406</v>
       </c>
-      <c r="B407" s="4"/>
-      <c r="C407" s="4"/>
+      <c r="B407" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
@@ -8300,8 +8567,12 @@
       <c r="A408" s="3">
         <v>407</v>
       </c>
-      <c r="B408" s="4"/>
-      <c r="C408" s="4"/>
+      <c r="B408" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
@@ -8310,8 +8581,12 @@
       <c r="A409" s="3">
         <v>408</v>
       </c>
-      <c r="B409" s="4"/>
-      <c r="C409" s="4"/>
+      <c r="B409" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D409" s="3"/>
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
@@ -8320,8 +8595,12 @@
       <c r="A410" s="3">
         <v>409</v>
       </c>
-      <c r="B410" s="4"/>
-      <c r="C410" s="4"/>
+      <c r="B410" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
@@ -8330,8 +8609,12 @@
       <c r="A411" s="3">
         <v>410</v>
       </c>
-      <c r="B411" s="4"/>
-      <c r="C411" s="4"/>
+      <c r="B411" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C411" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
@@ -8340,8 +8623,12 @@
       <c r="A412" s="3">
         <v>411</v>
       </c>
-      <c r="B412" s="4"/>
-      <c r="C412" s="4"/>
+      <c r="B412" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
@@ -8350,8 +8637,12 @@
       <c r="A413" s="3">
         <v>412</v>
       </c>
-      <c r="B413" s="4"/>
-      <c r="C413" s="4"/>
+      <c r="B413" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C413" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D413" s="3"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
@@ -8360,8 +8651,12 @@
       <c r="A414" s="3">
         <v>413</v>
       </c>
-      <c r="B414" s="4"/>
-      <c r="C414" s="4"/>
+      <c r="B414" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
@@ -8370,8 +8665,12 @@
       <c r="A415" s="3">
         <v>414</v>
       </c>
-      <c r="B415" s="4"/>
-      <c r="C415" s="4"/>
+      <c r="B415" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D415" s="3"/>
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
@@ -8380,8 +8679,12 @@
       <c r="A416" s="3">
         <v>415</v>
       </c>
-      <c r="B416" s="4"/>
-      <c r="C416" s="4"/>
+      <c r="B416" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
@@ -8390,8 +8693,12 @@
       <c r="A417" s="3">
         <v>416</v>
       </c>
-      <c r="B417" s="4"/>
-      <c r="C417" s="4"/>
+      <c r="B417" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D417" s="3"/>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
@@ -8400,8 +8707,12 @@
       <c r="A418" s="3">
         <v>417</v>
       </c>
-      <c r="B418" s="4"/>
-      <c r="C418" s="4"/>
+      <c r="B418" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D418" s="3"/>
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
@@ -8410,8 +8721,12 @@
       <c r="A419" s="3">
         <v>418</v>
       </c>
-      <c r="B419" s="4"/>
-      <c r="C419" s="4"/>
+      <c r="B419" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D419" s="3"/>
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
@@ -8420,8 +8735,12 @@
       <c r="A420" s="3">
         <v>419</v>
       </c>
-      <c r="B420" s="4"/>
-      <c r="C420" s="4"/>
+      <c r="B420" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D420" s="3"/>
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
@@ -8430,8 +8749,12 @@
       <c r="A421" s="3">
         <v>420</v>
       </c>
-      <c r="B421" s="4"/>
-      <c r="C421" s="4"/>
+      <c r="B421" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D421" s="3"/>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
@@ -8440,8 +8763,12 @@
       <c r="A422" s="3">
         <v>421</v>
       </c>
-      <c r="B422" s="4"/>
-      <c r="C422" s="4"/>
+      <c r="B422" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D422" s="3"/>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
@@ -8450,8 +8777,12 @@
       <c r="A423" s="3">
         <v>422</v>
       </c>
-      <c r="B423" s="4"/>
-      <c r="C423" s="4"/>
+      <c r="B423" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D423" s="3"/>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
@@ -8460,8 +8791,12 @@
       <c r="A424" s="3">
         <v>423</v>
       </c>
-      <c r="B424" s="4"/>
-      <c r="C424" s="4"/>
+      <c r="B424" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
@@ -8470,8 +8805,12 @@
       <c r="A425" s="3">
         <v>424</v>
       </c>
-      <c r="B425" s="4"/>
-      <c r="C425" s="4"/>
+      <c r="B425" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D425" s="3"/>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
@@ -8480,8 +8819,12 @@
       <c r="A426" s="3">
         <v>425</v>
       </c>
-      <c r="B426" s="4"/>
-      <c r="C426" s="4"/>
+      <c r="B426" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
@@ -8490,8 +8833,12 @@
       <c r="A427" s="3">
         <v>426</v>
       </c>
-      <c r="B427" s="4"/>
-      <c r="C427" s="4"/>
+      <c r="B427" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D427" s="3"/>
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
@@ -8500,8 +8847,12 @@
       <c r="A428" s="3">
         <v>427</v>
       </c>
-      <c r="B428" s="4"/>
-      <c r="C428" s="4"/>
+      <c r="B428" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
@@ -8510,8 +8861,12 @@
       <c r="A429" s="3">
         <v>428</v>
       </c>
-      <c r="B429" s="4"/>
-      <c r="C429" s="4"/>
+      <c r="B429" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D429" s="3"/>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
@@ -8520,8 +8875,12 @@
       <c r="A430" s="3">
         <v>429</v>
       </c>
-      <c r="B430" s="4"/>
-      <c r="C430" s="4"/>
+      <c r="B430" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
@@ -8530,8 +8889,12 @@
       <c r="A431" s="3">
         <v>430</v>
       </c>
-      <c r="B431" s="4"/>
-      <c r="C431" s="4"/>
+      <c r="B431" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D431" s="3"/>
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
@@ -8540,8 +8903,12 @@
       <c r="A432" s="3">
         <v>431</v>
       </c>
-      <c r="B432" s="4"/>
-      <c r="C432" s="4"/>
+      <c r="B432" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
@@ -8550,8 +8917,12 @@
       <c r="A433" s="3">
         <v>432</v>
       </c>
-      <c r="B433" s="4"/>
-      <c r="C433" s="4"/>
+      <c r="B433" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D433" s="3"/>
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
@@ -8560,8 +8931,12 @@
       <c r="A434" s="3">
         <v>433</v>
       </c>
-      <c r="B434" s="4"/>
-      <c r="C434" s="4"/>
+      <c r="B434" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
@@ -8570,8 +8945,12 @@
       <c r="A435" s="3">
         <v>434</v>
       </c>
-      <c r="B435" s="4"/>
-      <c r="C435" s="4"/>
+      <c r="B435" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="D435" s="3"/>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0036948C-3082-41DE-A179-B43190BB7BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F6F22F-FED2-44E8-853B-00FB0E906E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="454">
   <si>
     <t>STT</t>
   </si>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
-        <v>334</v>
+        <v>414</v>
       </c>
       <c r="I2" s="25">
         <f>COUNTIFS(D2:D1001,"Lỗi")</f>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>89</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7843,7 +7843,9 @@
       <c r="C356" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D356" s="3"/>
+      <c r="D356" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
     </row>
@@ -7857,7 +7859,9 @@
       <c r="C357" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D357" s="3"/>
+      <c r="D357" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
     </row>
@@ -7871,7 +7875,9 @@
       <c r="C358" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D358" s="3"/>
+      <c r="D358" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
     </row>
@@ -7885,7 +7891,9 @@
       <c r="C359" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D359" s="3"/>
+      <c r="D359" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
     </row>
@@ -7899,7 +7907,9 @@
       <c r="C360" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D360" s="3"/>
+      <c r="D360" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
     </row>
@@ -7913,7 +7923,9 @@
       <c r="C361" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D361" s="3"/>
+      <c r="D361" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
     </row>
@@ -7927,7 +7939,9 @@
       <c r="C362" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D362" s="3"/>
+      <c r="D362" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
     </row>
@@ -7941,7 +7955,9 @@
       <c r="C363" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D363" s="3"/>
+      <c r="D363" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
     </row>
@@ -7955,7 +7971,9 @@
       <c r="C364" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D364" s="3"/>
+      <c r="D364" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
     </row>
@@ -7969,7 +7987,9 @@
       <c r="C365" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D365" s="3"/>
+      <c r="D365" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
     </row>
@@ -7983,7 +8003,9 @@
       <c r="C366" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D366" s="3"/>
+      <c r="D366" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
     </row>
@@ -7997,7 +8019,9 @@
       <c r="C367" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D367" s="3"/>
+      <c r="D367" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
     </row>
@@ -8011,7 +8035,9 @@
       <c r="C368" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D368" s="3"/>
+      <c r="D368" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E368" s="3" t="s">
         <v>396</v>
       </c>
@@ -8027,7 +8053,9 @@
       <c r="C369" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D369" s="3"/>
+      <c r="D369" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
     </row>
@@ -8041,7 +8069,9 @@
       <c r="C370" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D370" s="3"/>
+      <c r="D370" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
     </row>
@@ -8055,7 +8085,9 @@
       <c r="C371" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D371" s="3"/>
+      <c r="D371" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
     </row>
@@ -8069,7 +8101,9 @@
       <c r="C372" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D372" s="3"/>
+      <c r="D372" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
     </row>
@@ -8083,7 +8117,9 @@
       <c r="C373" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D373" s="3"/>
+      <c r="D373" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
     </row>
@@ -8097,7 +8133,9 @@
       <c r="C374" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D374" s="3"/>
+      <c r="D374" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
     </row>
@@ -8111,7 +8149,9 @@
       <c r="C375" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D375" s="3"/>
+      <c r="D375" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
     </row>
@@ -8125,7 +8165,9 @@
       <c r="C376" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D376" s="3"/>
+      <c r="D376" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
     </row>
@@ -8139,7 +8181,9 @@
       <c r="C377" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D377" s="3"/>
+      <c r="D377" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
     </row>
@@ -8153,7 +8197,9 @@
       <c r="C378" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D378" s="3"/>
+      <c r="D378" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
     </row>
@@ -8167,7 +8213,9 @@
       <c r="C379" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D379" s="3"/>
+      <c r="D379" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
     </row>
@@ -8181,7 +8229,9 @@
       <c r="C380" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D380" s="3"/>
+      <c r="D380" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>
     </row>
@@ -8195,7 +8245,9 @@
       <c r="C381" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D381" s="3"/>
+      <c r="D381" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
     </row>
@@ -8209,7 +8261,9 @@
       <c r="C382" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D382" s="3"/>
+      <c r="D382" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
     </row>
@@ -8223,7 +8277,9 @@
       <c r="C383" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D383" s="3"/>
+      <c r="D383" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
     </row>
@@ -8237,7 +8293,9 @@
       <c r="C384" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D384" s="3"/>
+      <c r="D384" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
     </row>
@@ -8251,7 +8309,9 @@
       <c r="C385" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D385" s="3"/>
+      <c r="D385" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
     </row>
@@ -8265,7 +8325,9 @@
       <c r="C386" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D386" s="3"/>
+      <c r="D386" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
     </row>
@@ -8279,7 +8341,9 @@
       <c r="C387" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D387" s="3"/>
+      <c r="D387" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
     </row>
@@ -8293,7 +8357,9 @@
       <c r="C388" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D388" s="3"/>
+      <c r="D388" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
     </row>
@@ -8307,7 +8373,9 @@
       <c r="C389" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D389" s="3"/>
+      <c r="D389" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
     </row>
@@ -8321,7 +8389,9 @@
       <c r="C390" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D390" s="3"/>
+      <c r="D390" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
     </row>
@@ -8335,7 +8405,9 @@
       <c r="C391" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D391" s="3"/>
+      <c r="D391" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
     </row>
@@ -8349,7 +8421,9 @@
       <c r="C392" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D392" s="3"/>
+      <c r="D392" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
     </row>
@@ -8363,7 +8437,9 @@
       <c r="C393" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D393" s="3"/>
+      <c r="D393" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
     </row>
@@ -8377,7 +8453,9 @@
       <c r="C394" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D394" s="3"/>
+      <c r="D394" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
     </row>
@@ -8391,7 +8469,9 @@
       <c r="C395" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D395" s="3"/>
+      <c r="D395" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
     </row>
@@ -8405,7 +8485,9 @@
       <c r="C396" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D396" s="3"/>
+      <c r="D396" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
     </row>
@@ -8419,7 +8501,9 @@
       <c r="C397" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D397" s="3"/>
+      <c r="D397" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
     </row>
@@ -8433,7 +8517,9 @@
       <c r="C398" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D398" s="3"/>
+      <c r="D398" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
     </row>
@@ -8447,7 +8533,9 @@
       <c r="C399" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D399" s="3"/>
+      <c r="D399" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
     </row>
@@ -8461,7 +8549,9 @@
       <c r="C400" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D400" s="3"/>
+      <c r="D400" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
     </row>
@@ -8475,7 +8565,9 @@
       <c r="C401" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D401" s="3"/>
+      <c r="D401" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
     </row>
@@ -8489,7 +8581,9 @@
       <c r="C402" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D402" s="3"/>
+      <c r="D402" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
     </row>
@@ -8503,7 +8597,9 @@
       <c r="C403" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D403" s="3"/>
+      <c r="D403" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
     </row>
@@ -8517,7 +8613,9 @@
       <c r="C404" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D404" s="3"/>
+      <c r="D404" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
     </row>
@@ -8531,7 +8629,9 @@
       <c r="C405" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D405" s="3"/>
+      <c r="D405" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E405" s="14"/>
       <c r="F405" s="3"/>
     </row>
@@ -8545,7 +8645,9 @@
       <c r="C406" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D406" s="3"/>
+      <c r="D406" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
     </row>
@@ -8559,7 +8661,9 @@
       <c r="C407" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D407" s="3"/>
+      <c r="D407" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
     </row>
@@ -8573,7 +8677,9 @@
       <c r="C408" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D408" s="3"/>
+      <c r="D408" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
     </row>
@@ -8587,7 +8693,9 @@
       <c r="C409" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D409" s="3"/>
+      <c r="D409" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
     </row>
@@ -8601,7 +8709,9 @@
       <c r="C410" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D410" s="3"/>
+      <c r="D410" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
     </row>
@@ -8615,7 +8725,9 @@
       <c r="C411" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D411" s="3"/>
+      <c r="D411" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
     </row>
@@ -8629,7 +8741,9 @@
       <c r="C412" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D412" s="3"/>
+      <c r="D412" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
     </row>
@@ -8643,7 +8757,9 @@
       <c r="C413" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D413" s="3"/>
+      <c r="D413" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
     </row>
@@ -8657,7 +8773,9 @@
       <c r="C414" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D414" s="3"/>
+      <c r="D414" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
     </row>
@@ -8671,7 +8789,9 @@
       <c r="C415" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D415" s="3"/>
+      <c r="D415" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
     </row>
@@ -8685,7 +8805,9 @@
       <c r="C416" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D416" s="3"/>
+      <c r="D416" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
     </row>
@@ -8699,7 +8821,9 @@
       <c r="C417" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D417" s="3"/>
+      <c r="D417" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
     </row>
@@ -8713,7 +8837,9 @@
       <c r="C418" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D418" s="3"/>
+      <c r="D418" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
     </row>
@@ -8727,7 +8853,9 @@
       <c r="C419" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D419" s="3"/>
+      <c r="D419" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
     </row>
@@ -8741,7 +8869,9 @@
       <c r="C420" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D420" s="3"/>
+      <c r="D420" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
     </row>
@@ -8755,7 +8885,9 @@
       <c r="C421" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D421" s="3"/>
+      <c r="D421" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
     </row>
@@ -8769,7 +8901,9 @@
       <c r="C422" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D422" s="3"/>
+      <c r="D422" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
     </row>
@@ -8783,7 +8917,9 @@
       <c r="C423" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D423" s="3"/>
+      <c r="D423" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
     </row>
@@ -8797,7 +8933,9 @@
       <c r="C424" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D424" s="3"/>
+      <c r="D424" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
     </row>
@@ -8811,7 +8949,9 @@
       <c r="C425" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D425" s="3"/>
+      <c r="D425" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
     </row>
@@ -8825,7 +8965,9 @@
       <c r="C426" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D426" s="3"/>
+      <c r="D426" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
     </row>
@@ -8839,7 +8981,9 @@
       <c r="C427" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D427" s="3"/>
+      <c r="D427" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
     </row>
@@ -8853,7 +8997,9 @@
       <c r="C428" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D428" s="3"/>
+      <c r="D428" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
     </row>
@@ -8867,7 +9013,9 @@
       <c r="C429" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D429" s="3"/>
+      <c r="D429" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
     </row>
@@ -8881,7 +9029,9 @@
       <c r="C430" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D430" s="3"/>
+      <c r="D430" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
     </row>
@@ -8895,7 +9045,9 @@
       <c r="C431" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D431" s="3"/>
+      <c r="D431" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
     </row>
@@ -8909,7 +9061,9 @@
       <c r="C432" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D432" s="3"/>
+      <c r="D432" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
     </row>
@@ -8923,7 +9077,9 @@
       <c r="C433" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D433" s="3"/>
+      <c r="D433" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
     </row>
@@ -8937,7 +9093,9 @@
       <c r="C434" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D434" s="3"/>
+      <c r="D434" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
     </row>
@@ -8951,7 +9109,9 @@
       <c r="C435" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D435" s="3"/>
+      <c r="D435" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
     </row>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F6F22F-FED2-44E8-853B-00FB0E906E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621FFBF9-1274-4F68-8FB4-F25FC5B9A49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="565">
   <si>
     <t>STT</t>
   </si>
@@ -1390,6 +1390,339 @@
   </si>
   <si>
     <t>VNET860879084180302</t>
+  </si>
+  <si>
+    <t>22/10/26</t>
+  </si>
+  <si>
+    <t>VNET860879084181045</t>
+  </si>
+  <si>
+    <t>VNET860879084178819</t>
+  </si>
+  <si>
+    <t>VNET860879084174438</t>
+  </si>
+  <si>
+    <t>VNET860879084181110</t>
+  </si>
+  <si>
+    <t>VNET860879084179908</t>
+  </si>
+  <si>
+    <t>VNET860879084181599</t>
+  </si>
+  <si>
+    <t>VNET860879084181177</t>
+  </si>
+  <si>
+    <t>VNET860879084178330</t>
+  </si>
+  <si>
+    <t>VNET860879084174115</t>
+  </si>
+  <si>
+    <t>VNET860879084178728</t>
+  </si>
+  <si>
+    <t>VNET860879084183298</t>
+  </si>
+  <si>
+    <t>VNET860879084179627</t>
+  </si>
+  <si>
+    <t>VNET860879084179999</t>
+  </si>
+  <si>
+    <t>VNET860879084178280</t>
+  </si>
+  <si>
+    <t>VNET860879084182050</t>
+  </si>
+  <si>
+    <t>VNET860879084179189</t>
+  </si>
+  <si>
+    <t>VNET860879084174040</t>
+  </si>
+  <si>
+    <t>VNET860879084182290</t>
+  </si>
+  <si>
+    <t>VNET860879084179460</t>
+  </si>
+  <si>
+    <t>VNET860879084180732</t>
+  </si>
+  <si>
+    <t>VNET860879084181516</t>
+  </si>
+  <si>
+    <t>VNET860879084179478</t>
+  </si>
+  <si>
+    <t>VNET860879084179924</t>
+  </si>
+  <si>
+    <t>VNET860879084181029</t>
+  </si>
+  <si>
+    <t>VNET860879084177985</t>
+  </si>
+  <si>
+    <t>VNET860879084180310</t>
+  </si>
+  <si>
+    <t>VNET860879084175468</t>
+  </si>
+  <si>
+    <t>VNET860879084180476</t>
+  </si>
+  <si>
+    <t>VNET860879084178322</t>
+  </si>
+  <si>
+    <t>VNET860879084179221</t>
+  </si>
+  <si>
+    <t>VNET860879084181037</t>
+  </si>
+  <si>
+    <t>VNET860879084181938</t>
+  </si>
+  <si>
+    <t>VNET860879084173984</t>
+  </si>
+  <si>
+    <t>VNET860879084174180</t>
+  </si>
+  <si>
+    <t>VNET860879084181870</t>
+  </si>
+  <si>
+    <t>VNET860879084180146</t>
+  </si>
+  <si>
+    <t>VNET860879084182019</t>
+  </si>
+  <si>
+    <t>VNET860879084180047</t>
+  </si>
+  <si>
+    <t>VNET860879084174255</t>
+  </si>
+  <si>
+    <t>VNET860879084173901</t>
+  </si>
+  <si>
+    <t>VNET860879084177415</t>
+  </si>
+  <si>
+    <t>VNET860879084183256</t>
+  </si>
+  <si>
+    <t>VNET860879084180161</t>
+  </si>
+  <si>
+    <t>VNET860879084180138</t>
+  </si>
+  <si>
+    <t>VNET860879084177167</t>
+  </si>
+  <si>
+    <t>VNET860879084179940</t>
+  </si>
+  <si>
+    <t>VNET860879084179882</t>
+  </si>
+  <si>
+    <t>VNET860879084176060</t>
+  </si>
+  <si>
+    <t>VNET860879084179288</t>
+  </si>
+  <si>
+    <t>VNET860879084180252</t>
+  </si>
+  <si>
+    <t>VNET860879084181649</t>
+  </si>
+  <si>
+    <t>VNET860879084180179</t>
+  </si>
+  <si>
+    <t>VNET860879084180583</t>
+  </si>
+  <si>
+    <t>VNET860879084181664</t>
+  </si>
+  <si>
+    <t>VNET860879084178462</t>
+  </si>
+  <si>
+    <t>VNET860879084176565</t>
+  </si>
+  <si>
+    <t>VNET860879084176631</t>
+  </si>
+  <si>
+    <t>VNET860879084176623</t>
+  </si>
+  <si>
+    <t>VNET860879084177050</t>
+  </si>
+  <si>
+    <t>VNET860879084182589</t>
+  </si>
+  <si>
+    <t>VNET860879084174552</t>
+  </si>
+  <si>
+    <t>VNET860879084175567</t>
+  </si>
+  <si>
+    <t>VNET860879084176474</t>
+  </si>
+  <si>
+    <t>VNET860879084174735</t>
+  </si>
+  <si>
+    <t>VNET860879084176391</t>
+  </si>
+  <si>
+    <t>VNET860879084176409</t>
+  </si>
+  <si>
+    <t>VNET860879084176268</t>
+  </si>
+  <si>
+    <t>VNET860879084174768</t>
+  </si>
+  <si>
+    <t>VNET860879084177241</t>
+  </si>
+  <si>
+    <t>VNET860879084181698</t>
+  </si>
+  <si>
+    <t>VNET860879084175575</t>
+  </si>
+  <si>
+    <t>VNET860879084182837</t>
+  </si>
+  <si>
+    <t>VNET860879084176656</t>
+  </si>
+  <si>
+    <t>VNET860879084178272</t>
+  </si>
+  <si>
+    <t>VNET860879084174420</t>
+  </si>
+  <si>
+    <t>VNET860879084183744</t>
+  </si>
+  <si>
+    <t>VNET860879084181896</t>
+  </si>
+  <si>
+    <t>VNET860879084174818</t>
+  </si>
+  <si>
+    <t>VNET860879084174396</t>
+  </si>
+  <si>
+    <t>VNET860879084176581</t>
+  </si>
+  <si>
+    <t>VNET860879084178660</t>
+  </si>
+  <si>
+    <t>VNET860879084176524</t>
+  </si>
+  <si>
+    <t>VNET860879084175922</t>
+  </si>
+  <si>
+    <t>VNET860879084176342</t>
+  </si>
+  <si>
+    <t>VNET860879084174644</t>
+  </si>
+  <si>
+    <t>VNET860879084176680</t>
+  </si>
+  <si>
+    <t>VNET860879084182175</t>
+  </si>
+  <si>
+    <t>VNET860879084177647</t>
+  </si>
+  <si>
+    <t>VNET860879084174776</t>
+  </si>
+  <si>
+    <t>VNET860879084179312</t>
+  </si>
+  <si>
+    <t>VNET860879084180914</t>
+  </si>
+  <si>
+    <t>VNET860879084176516</t>
+  </si>
+  <si>
+    <t>VNET860879084180955</t>
+  </si>
+  <si>
+    <t>VNET860879084177712</t>
+  </si>
+  <si>
+    <t>VNET860879084177365</t>
+  </si>
+  <si>
+    <t>VNET860879084175971</t>
+  </si>
+  <si>
+    <t>VNET860879084174701</t>
+  </si>
+  <si>
+    <t>VNET860879084177324</t>
+  </si>
+  <si>
+    <t>VNET860879084182779</t>
+  </si>
+  <si>
+    <t>VNET860879084176649</t>
+  </si>
+  <si>
+    <t>VNET860879084178157</t>
+  </si>
+  <si>
+    <t>VNET860879084176862</t>
+  </si>
+  <si>
+    <t>VNET860879084175609</t>
+  </si>
+  <si>
+    <t>VNET860879084176219</t>
+  </si>
+  <si>
+    <t>VNET860879084179858</t>
+  </si>
+  <si>
+    <t>VNET860879084176789</t>
+  </si>
+  <si>
+    <t>VNET860879084178082</t>
+  </si>
+  <si>
+    <t>VNET860879084181771</t>
+  </si>
+  <si>
+    <t>VNET860879084178207</t>
+  </si>
+  <si>
+    <t>VNET860879084174982</t>
   </si>
 </sst>
 </file>
@@ -2105,7 +2438,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="3">
         <f>COUNTIFS(B2:B1001,"*VNET*")</f>
-        <v>434</v>
+        <v>544</v>
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
@@ -2129,7 +2462,7 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>9</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -9119,8 +9452,12 @@
       <c r="A436" s="3">
         <v>435</v>
       </c>
-      <c r="B436" s="4"/>
-      <c r="C436" s="4"/>
+      <c r="B436" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D436" s="3"/>
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
@@ -9129,8 +9466,12 @@
       <c r="A437" s="3">
         <v>436</v>
       </c>
-      <c r="B437" s="4"/>
-      <c r="C437" s="4"/>
+      <c r="B437" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D437" s="3"/>
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
@@ -9139,8 +9480,12 @@
       <c r="A438" s="3">
         <v>437</v>
       </c>
-      <c r="B438" s="4"/>
-      <c r="C438" s="4"/>
+      <c r="B438" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
@@ -9149,8 +9494,12 @@
       <c r="A439" s="3">
         <v>438</v>
       </c>
-      <c r="B439" s="4"/>
-      <c r="C439" s="4"/>
+      <c r="B439" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D439" s="3"/>
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
@@ -9159,8 +9508,12 @@
       <c r="A440" s="3">
         <v>439</v>
       </c>
-      <c r="B440" s="4"/>
-      <c r="C440" s="4"/>
+      <c r="B440" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D440" s="3"/>
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
@@ -9169,8 +9522,12 @@
       <c r="A441" s="3">
         <v>440</v>
       </c>
-      <c r="B441" s="4"/>
-      <c r="C441" s="4"/>
+      <c r="B441" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D441" s="3"/>
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
@@ -9179,8 +9536,12 @@
       <c r="A442" s="3">
         <v>441</v>
       </c>
-      <c r="B442" s="4"/>
-      <c r="C442" s="4"/>
+      <c r="B442" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
@@ -9189,8 +9550,12 @@
       <c r="A443" s="3">
         <v>442</v>
       </c>
-      <c r="B443" s="4"/>
-      <c r="C443" s="4"/>
+      <c r="B443" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D443" s="3"/>
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
@@ -9199,8 +9564,12 @@
       <c r="A444" s="3">
         <v>443</v>
       </c>
-      <c r="B444" s="4"/>
-      <c r="C444" s="4"/>
+      <c r="B444" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C444" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
@@ -9209,8 +9578,12 @@
       <c r="A445" s="3">
         <v>444</v>
       </c>
-      <c r="B445" s="4"/>
-      <c r="C445" s="4"/>
+      <c r="B445" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D445" s="3"/>
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
@@ -9219,8 +9592,12 @@
       <c r="A446" s="3">
         <v>445</v>
       </c>
-      <c r="B446" s="4"/>
-      <c r="C446" s="4"/>
+      <c r="B446" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
@@ -9229,8 +9606,12 @@
       <c r="A447" s="3">
         <v>446</v>
       </c>
-      <c r="B447" s="4"/>
-      <c r="C447" s="4"/>
+      <c r="B447" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C447" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D447" s="3"/>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
@@ -9239,8 +9620,12 @@
       <c r="A448" s="3">
         <v>447</v>
       </c>
-      <c r="B448" s="4"/>
-      <c r="C448" s="4"/>
+      <c r="B448" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C448" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
@@ -9249,8 +9634,12 @@
       <c r="A449" s="3">
         <v>448</v>
       </c>
-      <c r="B449" s="4"/>
-      <c r="C449" s="4"/>
+      <c r="B449" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C449" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D449" s="3"/>
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
@@ -9259,8 +9648,12 @@
       <c r="A450" s="3">
         <v>449</v>
       </c>
-      <c r="B450" s="4"/>
-      <c r="C450" s="4"/>
+      <c r="B450" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C450" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
@@ -9269,8 +9662,12 @@
       <c r="A451" s="3">
         <v>450</v>
       </c>
-      <c r="B451" s="4"/>
-      <c r="C451" s="4"/>
+      <c r="B451" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="C451" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D451" s="3"/>
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
@@ -9279,8 +9676,12 @@
       <c r="A452" s="3">
         <v>451</v>
       </c>
-      <c r="B452" s="4"/>
-      <c r="C452" s="4"/>
+      <c r="B452" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C452" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
@@ -9289,8 +9690,12 @@
       <c r="A453" s="3">
         <v>452</v>
       </c>
-      <c r="B453" s="4"/>
-      <c r="C453" s="4"/>
+      <c r="B453" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C453" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D453" s="3"/>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
@@ -9299,8 +9704,12 @@
       <c r="A454" s="3">
         <v>453</v>
       </c>
-      <c r="B454" s="4"/>
-      <c r="C454" s="4"/>
+      <c r="B454" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C454" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
@@ -9309,8 +9718,12 @@
       <c r="A455" s="3">
         <v>454</v>
       </c>
-      <c r="B455" s="4"/>
-      <c r="C455" s="4"/>
+      <c r="B455" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C455" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D455" s="3"/>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
@@ -9319,8 +9732,12 @@
       <c r="A456" s="3">
         <v>455</v>
       </c>
-      <c r="B456" s="4"/>
-      <c r="C456" s="4"/>
+      <c r="B456" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C456" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
@@ -9329,8 +9746,12 @@
       <c r="A457" s="3">
         <v>456</v>
       </c>
-      <c r="B457" s="4"/>
-      <c r="C457" s="4"/>
+      <c r="B457" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C457" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D457" s="3"/>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
@@ -9339,8 +9760,12 @@
       <c r="A458" s="3">
         <v>457</v>
       </c>
-      <c r="B458" s="4"/>
-      <c r="C458" s="4"/>
+      <c r="B458" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C458" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D458" s="3"/>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
@@ -9349,8 +9774,12 @@
       <c r="A459" s="3">
         <v>458</v>
       </c>
-      <c r="B459" s="4"/>
-      <c r="C459" s="4"/>
+      <c r="B459" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C459" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D459" s="3"/>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
@@ -9359,8 +9788,12 @@
       <c r="A460" s="3">
         <v>459</v>
       </c>
-      <c r="B460" s="4"/>
-      <c r="C460" s="4"/>
+      <c r="B460" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
@@ -9369,8 +9802,12 @@
       <c r="A461" s="3">
         <v>460</v>
       </c>
-      <c r="B461" s="4"/>
-      <c r="C461" s="4"/>
+      <c r="B461" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C461" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D461" s="3"/>
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
@@ -9379,8 +9816,12 @@
       <c r="A462" s="3">
         <v>461</v>
       </c>
-      <c r="B462" s="4"/>
-      <c r="C462" s="4"/>
+      <c r="B462" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C462" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D462" s="3"/>
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
@@ -9389,8 +9830,12 @@
       <c r="A463" s="3">
         <v>462</v>
       </c>
-      <c r="B463" s="4"/>
-      <c r="C463" s="4"/>
+      <c r="B463" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C463" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D463" s="3"/>
       <c r="E463" s="10"/>
       <c r="F463" s="10"/>
@@ -9399,8 +9844,12 @@
       <c r="A464" s="3">
         <v>463</v>
       </c>
-      <c r="B464" s="4"/>
-      <c r="C464" s="4"/>
+      <c r="B464" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D464" s="3"/>
       <c r="E464" s="10"/>
       <c r="F464" s="10"/>
@@ -9409,8 +9858,12 @@
       <c r="A465" s="3">
         <v>464</v>
       </c>
-      <c r="B465" s="4"/>
-      <c r="C465" s="4"/>
+      <c r="B465" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D465" s="3"/>
       <c r="E465" s="10"/>
       <c r="F465" s="10"/>
@@ -9419,8 +9872,12 @@
       <c r="A466" s="3">
         <v>465</v>
       </c>
-      <c r="B466" s="4"/>
-      <c r="C466" s="4"/>
+      <c r="B466" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D466" s="3"/>
       <c r="E466" s="10"/>
       <c r="F466" s="10"/>
@@ -9429,8 +9886,12 @@
       <c r="A467" s="3">
         <v>466</v>
       </c>
-      <c r="B467" s="4"/>
-      <c r="C467" s="4"/>
+      <c r="B467" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D467" s="3"/>
       <c r="E467" s="10"/>
       <c r="F467" s="10"/>
@@ -9439,8 +9900,12 @@
       <c r="A468" s="3">
         <v>467</v>
       </c>
-      <c r="B468" s="4"/>
-      <c r="C468" s="4"/>
+      <c r="B468" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C468" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D468" s="3"/>
       <c r="E468" s="10"/>
       <c r="F468" s="10"/>
@@ -9449,8 +9914,12 @@
       <c r="A469" s="3">
         <v>468</v>
       </c>
-      <c r="B469" s="4"/>
-      <c r="C469" s="4"/>
+      <c r="B469" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D469" s="3"/>
       <c r="E469" s="10"/>
       <c r="F469" s="10"/>
@@ -9459,8 +9928,12 @@
       <c r="A470" s="3">
         <v>469</v>
       </c>
-      <c r="B470" s="4"/>
-      <c r="C470" s="4"/>
+      <c r="B470" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D470" s="3"/>
       <c r="E470" s="10"/>
       <c r="F470" s="10"/>
@@ -9469,8 +9942,12 @@
       <c r="A471" s="3">
         <v>470</v>
       </c>
-      <c r="B471" s="15"/>
-      <c r="C471" s="4"/>
+      <c r="B471" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C471" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D471" s="3"/>
       <c r="E471" s="10"/>
       <c r="F471" s="10"/>
@@ -9479,8 +9956,12 @@
       <c r="A472" s="3">
         <v>471</v>
       </c>
-      <c r="B472" s="4"/>
-      <c r="C472" s="4"/>
+      <c r="B472" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D472" s="3"/>
       <c r="E472" s="10"/>
       <c r="F472" s="10"/>
@@ -9489,8 +9970,12 @@
       <c r="A473" s="3">
         <v>472</v>
       </c>
-      <c r="B473" s="4"/>
-      <c r="C473" s="4"/>
+      <c r="B473" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C473" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D473" s="3"/>
       <c r="E473" s="10"/>
       <c r="F473" s="10"/>
@@ -9499,8 +9984,12 @@
       <c r="A474" s="3">
         <v>473</v>
       </c>
-      <c r="B474" s="4"/>
-      <c r="C474" s="4"/>
+      <c r="B474" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C474" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D474" s="3"/>
       <c r="E474" s="10"/>
       <c r="F474" s="10"/>
@@ -9509,8 +9998,12 @@
       <c r="A475" s="3">
         <v>474</v>
       </c>
-      <c r="B475" s="4"/>
-      <c r="C475" s="4"/>
+      <c r="B475" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C475" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D475" s="3"/>
       <c r="E475" s="10"/>
       <c r="F475" s="10"/>
@@ -9519,8 +10012,12 @@
       <c r="A476" s="3">
         <v>475</v>
       </c>
-      <c r="B476" s="4"/>
-      <c r="C476" s="4"/>
+      <c r="B476" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C476" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D476" s="3"/>
       <c r="E476" s="10"/>
       <c r="F476" s="10"/>
@@ -9529,8 +10026,12 @@
       <c r="A477" s="3">
         <v>476</v>
       </c>
-      <c r="B477" s="4"/>
-      <c r="C477" s="4"/>
+      <c r="B477" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C477" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D477" s="3"/>
       <c r="E477" s="10"/>
       <c r="F477" s="10"/>
@@ -9539,8 +10040,12 @@
       <c r="A478" s="3">
         <v>477</v>
       </c>
-      <c r="B478" s="4"/>
-      <c r="C478" s="4"/>
+      <c r="B478" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C478" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D478" s="3"/>
       <c r="E478" s="10"/>
       <c r="F478" s="10"/>
@@ -9549,8 +10054,12 @@
       <c r="A479" s="3">
         <v>478</v>
       </c>
-      <c r="B479" s="4"/>
-      <c r="C479" s="4"/>
+      <c r="B479" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C479" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D479" s="3"/>
       <c r="E479" s="10"/>
       <c r="F479" s="10"/>
@@ -9559,8 +10068,12 @@
       <c r="A480" s="3">
         <v>479</v>
       </c>
-      <c r="B480" s="4"/>
-      <c r="C480" s="4"/>
+      <c r="B480" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D480" s="3"/>
       <c r="E480" s="10"/>
       <c r="F480" s="10"/>
@@ -9569,8 +10082,12 @@
       <c r="A481" s="3">
         <v>480</v>
       </c>
-      <c r="B481" s="4"/>
-      <c r="C481" s="4"/>
+      <c r="B481" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D481" s="3"/>
       <c r="E481" s="10"/>
       <c r="F481" s="10"/>
@@ -9579,8 +10096,12 @@
       <c r="A482" s="3">
         <v>481</v>
       </c>
-      <c r="B482" s="4"/>
-      <c r="C482" s="4"/>
+      <c r="B482" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D482" s="3"/>
       <c r="E482" s="10"/>
       <c r="F482" s="10"/>
@@ -9589,8 +10110,12 @@
       <c r="A483" s="3">
         <v>482</v>
       </c>
-      <c r="B483" s="4"/>
-      <c r="C483" s="4"/>
+      <c r="B483" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C483" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D483" s="3"/>
       <c r="E483" s="10"/>
       <c r="F483" s="10"/>
@@ -9599,8 +10124,12 @@
       <c r="A484" s="3">
         <v>483</v>
       </c>
-      <c r="B484" s="4"/>
-      <c r="C484" s="4"/>
+      <c r="B484" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C484" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D484" s="3"/>
       <c r="E484" s="10"/>
       <c r="F484" s="10"/>
@@ -9609,8 +10138,12 @@
       <c r="A485" s="3">
         <v>484</v>
       </c>
-      <c r="B485" s="4"/>
-      <c r="C485" s="4"/>
+      <c r="B485" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C485" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D485" s="3"/>
       <c r="E485" s="10"/>
       <c r="F485" s="10"/>
@@ -9619,8 +10152,12 @@
       <c r="A486" s="3">
         <v>485</v>
       </c>
-      <c r="B486" s="4"/>
-      <c r="C486" s="4"/>
+      <c r="B486" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C486" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D486" s="3"/>
       <c r="E486" s="10"/>
       <c r="F486" s="10"/>
@@ -9629,8 +10166,12 @@
       <c r="A487" s="3">
         <v>486</v>
       </c>
-      <c r="B487" s="4"/>
-      <c r="C487" s="4"/>
+      <c r="B487" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C487" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D487" s="3"/>
       <c r="E487" s="10"/>
       <c r="F487" s="10"/>
@@ -9639,8 +10180,12 @@
       <c r="A488" s="3">
         <v>487</v>
       </c>
-      <c r="B488" s="4"/>
-      <c r="C488" s="4"/>
+      <c r="B488" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C488" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D488" s="3"/>
       <c r="E488" s="10"/>
       <c r="F488" s="10"/>
@@ -9649,8 +10194,12 @@
       <c r="A489" s="3">
         <v>488</v>
       </c>
-      <c r="B489" s="4"/>
-      <c r="C489" s="4"/>
+      <c r="B489" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C489" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D489" s="3"/>
       <c r="E489" s="10"/>
       <c r="F489" s="10"/>
@@ -9659,8 +10208,12 @@
       <c r="A490" s="3">
         <v>489</v>
       </c>
-      <c r="B490" s="4"/>
-      <c r="C490" s="4"/>
+      <c r="B490" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C490" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D490" s="3"/>
       <c r="E490" s="10"/>
       <c r="F490" s="10"/>
@@ -9669,8 +10222,12 @@
       <c r="A491" s="3">
         <v>490</v>
       </c>
-      <c r="B491" s="4"/>
-      <c r="C491" s="4"/>
+      <c r="B491" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C491" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D491" s="3"/>
       <c r="E491" s="10"/>
       <c r="F491" s="10"/>
@@ -9679,8 +10236,12 @@
       <c r="A492" s="3">
         <v>491</v>
       </c>
-      <c r="B492" s="4"/>
-      <c r="C492" s="4"/>
+      <c r="B492" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C492" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D492" s="3"/>
       <c r="E492" s="10"/>
       <c r="F492" s="10"/>
@@ -9689,8 +10250,12 @@
       <c r="A493" s="3">
         <v>492</v>
       </c>
-      <c r="B493" s="4"/>
-      <c r="C493" s="4"/>
+      <c r="B493" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C493" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D493" s="3"/>
       <c r="E493" s="10"/>
       <c r="F493" s="10"/>
@@ -9699,8 +10264,12 @@
       <c r="A494" s="3">
         <v>493</v>
       </c>
-      <c r="B494" s="4"/>
-      <c r="C494" s="4"/>
+      <c r="B494" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C494" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D494" s="3"/>
       <c r="E494" s="10"/>
       <c r="F494" s="10"/>
@@ -9709,8 +10278,12 @@
       <c r="A495" s="3">
         <v>494</v>
       </c>
-      <c r="B495" s="4"/>
-      <c r="C495" s="4"/>
+      <c r="B495" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D495" s="3"/>
       <c r="E495" s="10"/>
       <c r="F495" s="10"/>
@@ -9719,8 +10292,12 @@
       <c r="A496" s="3">
         <v>495</v>
       </c>
-      <c r="B496" s="4"/>
-      <c r="C496" s="4"/>
+      <c r="B496" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="C496" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D496" s="3"/>
       <c r="E496" s="10"/>
       <c r="F496" s="10"/>
@@ -9729,8 +10306,12 @@
       <c r="A497" s="3">
         <v>496</v>
       </c>
-      <c r="B497" s="4"/>
-      <c r="C497" s="4"/>
+      <c r="B497" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C497" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D497" s="3"/>
       <c r="E497" s="10"/>
       <c r="F497" s="10"/>
@@ -9739,8 +10320,12 @@
       <c r="A498" s="3">
         <v>497</v>
       </c>
-      <c r="B498" s="4"/>
-      <c r="C498" s="4"/>
+      <c r="B498" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C498" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D498" s="3"/>
       <c r="E498" s="10"/>
       <c r="F498" s="10"/>
@@ -9749,8 +10334,12 @@
       <c r="A499" s="3">
         <v>498</v>
       </c>
-      <c r="B499" s="4"/>
-      <c r="C499" s="4"/>
+      <c r="B499" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C499" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D499" s="3"/>
       <c r="E499" s="10"/>
       <c r="F499" s="10"/>
@@ -9759,8 +10348,12 @@
       <c r="A500" s="3">
         <v>499</v>
       </c>
-      <c r="B500" s="4"/>
-      <c r="C500" s="4"/>
+      <c r="B500" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D500" s="3"/>
       <c r="E500" s="10"/>
       <c r="F500" s="10"/>
@@ -9769,8 +10362,12 @@
       <c r="A501" s="3">
         <v>500</v>
       </c>
-      <c r="B501" s="4"/>
-      <c r="C501" s="4"/>
+      <c r="B501" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C501" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D501" s="3"/>
       <c r="E501" s="10"/>
       <c r="F501" s="10"/>
@@ -9779,8 +10376,12 @@
       <c r="A502" s="3">
         <v>501</v>
       </c>
-      <c r="B502" s="4"/>
-      <c r="C502" s="4"/>
+      <c r="B502" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C502" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D502" s="3"/>
       <c r="E502" s="10"/>
       <c r="F502" s="10"/>
@@ -9789,8 +10390,12 @@
       <c r="A503" s="3">
         <v>502</v>
       </c>
-      <c r="B503" s="4"/>
-      <c r="C503" s="4"/>
+      <c r="B503" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C503" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D503" s="3"/>
       <c r="E503" s="10"/>
       <c r="F503" s="10"/>
@@ -9799,8 +10404,12 @@
       <c r="A504" s="3">
         <v>503</v>
       </c>
-      <c r="B504" s="4"/>
-      <c r="C504" s="4"/>
+      <c r="B504" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="C504" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D504" s="3"/>
       <c r="E504" s="10"/>
       <c r="F504" s="10"/>
@@ -9809,8 +10418,12 @@
       <c r="A505" s="3">
         <v>504</v>
       </c>
-      <c r="B505" s="4"/>
-      <c r="C505" s="4"/>
+      <c r="B505" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D505" s="3"/>
       <c r="E505" s="10"/>
       <c r="F505" s="10"/>
@@ -9819,8 +10432,12 @@
       <c r="A506" s="3">
         <v>505</v>
       </c>
-      <c r="B506" s="4"/>
-      <c r="C506" s="4"/>
+      <c r="B506" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C506" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D506" s="3"/>
       <c r="E506" s="10"/>
       <c r="F506" s="10"/>
@@ -9829,8 +10446,12 @@
       <c r="A507" s="3">
         <v>506</v>
       </c>
-      <c r="B507" s="4"/>
-      <c r="C507" s="4"/>
+      <c r="B507" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C507" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D507" s="3"/>
       <c r="E507" s="10"/>
       <c r="F507" s="10"/>
@@ -9839,8 +10460,12 @@
       <c r="A508" s="3">
         <v>507</v>
       </c>
-      <c r="B508" s="4"/>
-      <c r="C508" s="4"/>
+      <c r="B508" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D508" s="3"/>
       <c r="E508" s="10"/>
       <c r="F508" s="10"/>
@@ -9849,8 +10474,12 @@
       <c r="A509" s="3">
         <v>508</v>
       </c>
-      <c r="B509" s="4"/>
-      <c r="C509" s="4"/>
+      <c r="B509" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D509" s="3"/>
       <c r="E509" s="10"/>
       <c r="F509" s="10"/>
@@ -9859,8 +10488,12 @@
       <c r="A510" s="3">
         <v>509</v>
       </c>
-      <c r="B510" s="4"/>
-      <c r="C510" s="4"/>
+      <c r="B510" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D510" s="3"/>
       <c r="E510" s="10"/>
       <c r="F510" s="10"/>
@@ -9869,8 +10502,12 @@
       <c r="A511" s="3">
         <v>510</v>
       </c>
-      <c r="B511" s="4"/>
-      <c r="C511" s="4"/>
+      <c r="B511" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D511" s="3"/>
       <c r="E511" s="10"/>
       <c r="F511" s="10"/>
@@ -9879,8 +10516,12 @@
       <c r="A512" s="3">
         <v>511</v>
       </c>
-      <c r="B512" s="4"/>
-      <c r="C512" s="4"/>
+      <c r="B512" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D512" s="3"/>
       <c r="E512" s="10"/>
       <c r="F512" s="10"/>
@@ -9889,8 +10530,12 @@
       <c r="A513" s="3">
         <v>512</v>
       </c>
-      <c r="B513" s="4"/>
-      <c r="C513" s="4"/>
+      <c r="B513" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C513" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D513" s="3"/>
       <c r="E513" s="10"/>
       <c r="F513" s="10"/>
@@ -9899,8 +10544,12 @@
       <c r="A514" s="3">
         <v>513</v>
       </c>
-      <c r="B514" s="4"/>
-      <c r="C514" s="4"/>
+      <c r="B514" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D514" s="3"/>
       <c r="E514" s="10"/>
       <c r="F514" s="10"/>
@@ -9909,8 +10558,12 @@
       <c r="A515" s="3">
         <v>514</v>
       </c>
-      <c r="B515" s="4"/>
-      <c r="C515" s="4"/>
+      <c r="B515" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D515" s="3"/>
       <c r="E515" s="10"/>
       <c r="F515" s="10"/>
@@ -9919,8 +10572,12 @@
       <c r="A516" s="3">
         <v>515</v>
       </c>
-      <c r="B516" s="4"/>
-      <c r="C516" s="4"/>
+      <c r="B516" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D516" s="3"/>
       <c r="E516" s="10"/>
       <c r="F516" s="10"/>
@@ -9929,8 +10586,12 @@
       <c r="A517" s="3">
         <v>516</v>
       </c>
-      <c r="B517" s="4"/>
-      <c r="C517" s="4"/>
+      <c r="B517" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D517" s="3"/>
       <c r="E517" s="10"/>
       <c r="F517" s="10"/>
@@ -9939,8 +10600,12 @@
       <c r="A518" s="3">
         <v>517</v>
       </c>
-      <c r="B518" s="4"/>
-      <c r="C518" s="4"/>
+      <c r="B518" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D518" s="3"/>
       <c r="E518" s="10"/>
       <c r="F518" s="10"/>
@@ -9949,8 +10614,12 @@
       <c r="A519" s="3">
         <v>518</v>
       </c>
-      <c r="B519" s="4"/>
-      <c r="C519" s="4"/>
+      <c r="B519" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D519" s="3"/>
       <c r="E519" s="10"/>
       <c r="F519" s="10"/>
@@ -9959,8 +10628,12 @@
       <c r="A520" s="3">
         <v>519</v>
       </c>
-      <c r="B520" s="4"/>
-      <c r="C520" s="4"/>
+      <c r="B520" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D520" s="3"/>
       <c r="E520" s="10"/>
       <c r="F520" s="10"/>
@@ -9969,8 +10642,12 @@
       <c r="A521" s="3">
         <v>520</v>
       </c>
-      <c r="B521" s="4"/>
-      <c r="C521" s="4"/>
+      <c r="B521" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D521" s="3"/>
       <c r="E521" s="10"/>
       <c r="F521" s="10"/>
@@ -9979,8 +10656,12 @@
       <c r="A522" s="3">
         <v>521</v>
       </c>
-      <c r="B522" s="4"/>
-      <c r="C522" s="4"/>
+      <c r="B522" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D522" s="3"/>
       <c r="E522" s="10"/>
       <c r="F522" s="10"/>
@@ -9989,8 +10670,12 @@
       <c r="A523" s="3">
         <v>522</v>
       </c>
-      <c r="B523" s="4"/>
-      <c r="C523" s="4"/>
+      <c r="B523" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="C523" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D523" s="3"/>
       <c r="E523" s="10"/>
       <c r="F523" s="10"/>
@@ -9999,8 +10684,12 @@
       <c r="A524" s="3">
         <v>523</v>
       </c>
-      <c r="B524" s="4"/>
-      <c r="C524" s="4"/>
+      <c r="B524" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D524" s="3"/>
       <c r="E524" s="10"/>
       <c r="F524" s="10"/>
@@ -10009,8 +10698,12 @@
       <c r="A525" s="3">
         <v>524</v>
       </c>
-      <c r="B525" s="4"/>
-      <c r="C525" s="4"/>
+      <c r="B525" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D525" s="3"/>
       <c r="E525" s="10"/>
       <c r="F525" s="10"/>
@@ -10019,8 +10712,12 @@
       <c r="A526" s="3">
         <v>525</v>
       </c>
-      <c r="B526" s="4"/>
-      <c r="C526" s="4"/>
+      <c r="B526" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D526" s="3"/>
       <c r="E526" s="10"/>
       <c r="F526" s="10"/>
@@ -10029,8 +10726,12 @@
       <c r="A527" s="3">
         <v>526</v>
       </c>
-      <c r="B527" s="4"/>
-      <c r="C527" s="4"/>
+      <c r="B527" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C527" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D527" s="3"/>
       <c r="E527" s="10"/>
       <c r="F527" s="10"/>
@@ -10039,8 +10740,12 @@
       <c r="A528" s="3">
         <v>527</v>
       </c>
-      <c r="B528" s="4"/>
-      <c r="C528" s="4"/>
+      <c r="B528" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="C528" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D528" s="3"/>
       <c r="E528" s="10"/>
       <c r="F528" s="10"/>
@@ -10049,8 +10754,12 @@
       <c r="A529" s="3">
         <v>528</v>
       </c>
-      <c r="B529" s="4"/>
-      <c r="C529" s="4"/>
+      <c r="B529" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C529" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D529" s="3"/>
       <c r="E529" s="10"/>
       <c r="F529" s="10"/>
@@ -10059,8 +10768,12 @@
       <c r="A530" s="3">
         <v>529</v>
       </c>
-      <c r="B530" s="4"/>
-      <c r="C530" s="4"/>
+      <c r="B530" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D530" s="3"/>
       <c r="E530" s="10"/>
       <c r="F530" s="10"/>
@@ -10069,8 +10782,12 @@
       <c r="A531" s="3">
         <v>530</v>
       </c>
-      <c r="B531" s="4"/>
-      <c r="C531" s="4"/>
+      <c r="B531" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C531" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D531" s="3"/>
       <c r="E531" s="10"/>
       <c r="F531" s="10"/>
@@ -10079,8 +10796,12 @@
       <c r="A532" s="3">
         <v>531</v>
       </c>
-      <c r="B532" s="4"/>
-      <c r="C532" s="4"/>
+      <c r="B532" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D532" s="3"/>
       <c r="E532" s="10"/>
       <c r="F532" s="10"/>
@@ -10089,8 +10810,12 @@
       <c r="A533" s="3">
         <v>532</v>
       </c>
-      <c r="B533" s="4"/>
-      <c r="C533" s="4"/>
+      <c r="B533" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D533" s="3"/>
       <c r="E533" s="10"/>
       <c r="F533" s="10"/>
@@ -10099,8 +10824,12 @@
       <c r="A534" s="3">
         <v>533</v>
       </c>
-      <c r="B534" s="4"/>
-      <c r="C534" s="4"/>
+      <c r="B534" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D534" s="3"/>
       <c r="E534" s="10"/>
       <c r="F534" s="10"/>
@@ -10109,8 +10838,12 @@
       <c r="A535" s="3">
         <v>534</v>
       </c>
-      <c r="B535" s="4"/>
-      <c r="C535" s="4"/>
+      <c r="B535" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C535" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D535" s="3"/>
       <c r="E535" s="10"/>
       <c r="F535" s="10"/>
@@ -10119,8 +10852,12 @@
       <c r="A536" s="3">
         <v>535</v>
       </c>
-      <c r="B536" s="4"/>
-      <c r="C536" s="4"/>
+      <c r="B536" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C536" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D536" s="3"/>
       <c r="E536" s="10"/>
       <c r="F536" s="10"/>
@@ -10129,8 +10866,12 @@
       <c r="A537" s="3">
         <v>536</v>
       </c>
-      <c r="B537" s="4"/>
-      <c r="C537" s="4"/>
+      <c r="B537" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C537" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D537" s="3"/>
       <c r="E537" s="10"/>
       <c r="F537" s="10"/>
@@ -10139,8 +10880,12 @@
       <c r="A538" s="3">
         <v>537</v>
       </c>
-      <c r="B538" s="4"/>
-      <c r="C538" s="4"/>
+      <c r="B538" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D538" s="3"/>
       <c r="E538" s="10"/>
       <c r="F538" s="10"/>
@@ -10149,8 +10894,12 @@
       <c r="A539" s="3">
         <v>538</v>
       </c>
-      <c r="B539" s="4"/>
-      <c r="C539" s="4"/>
+      <c r="B539" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C539" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D539" s="3"/>
       <c r="E539" s="10"/>
       <c r="F539" s="10"/>
@@ -10159,8 +10908,12 @@
       <c r="A540" s="3">
         <v>539</v>
       </c>
-      <c r="B540" s="4"/>
-      <c r="C540" s="4"/>
+      <c r="B540" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C540" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D540" s="3"/>
       <c r="E540" s="10"/>
       <c r="F540" s="10"/>
@@ -10169,8 +10922,12 @@
       <c r="A541" s="3">
         <v>540</v>
       </c>
-      <c r="B541" s="4"/>
-      <c r="C541" s="4"/>
+      <c r="B541" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C541" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D541" s="3"/>
       <c r="E541" s="10"/>
       <c r="F541" s="10"/>
@@ -10179,8 +10936,12 @@
       <c r="A542" s="3">
         <v>541</v>
       </c>
-      <c r="B542" s="4"/>
-      <c r="C542" s="4"/>
+      <c r="B542" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D542" s="3"/>
       <c r="E542" s="10"/>
       <c r="F542" s="10"/>
@@ -10189,8 +10950,12 @@
       <c r="A543" s="3">
         <v>542</v>
       </c>
-      <c r="B543" s="4"/>
-      <c r="C543" s="4"/>
+      <c r="B543" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C543" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D543" s="3"/>
       <c r="E543" s="10"/>
       <c r="F543" s="10"/>
@@ -10199,8 +10964,12 @@
       <c r="A544" s="3">
         <v>543</v>
       </c>
-      <c r="B544" s="4"/>
-      <c r="C544" s="4"/>
+      <c r="B544" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D544" s="3"/>
       <c r="E544" s="10"/>
       <c r="F544" s="10"/>
@@ -10209,8 +10978,12 @@
       <c r="A545" s="3">
         <v>544</v>
       </c>
-      <c r="B545" s="4"/>
-      <c r="C545" s="4"/>
+      <c r="B545" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="D545" s="3"/>
       <c r="E545" s="10"/>
       <c r="F545" s="10"/>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621FFBF9-1274-4F68-8FB4-F25FC5B9A49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4279DD81-783E-41F6-91E0-3B6116F8EF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="565">
   <si>
     <t>STT</t>
   </si>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
-        <v>414</v>
+        <v>521</v>
       </c>
       <c r="I2" s="25">
         <f>COUNTIFS(D2:D1001,"Lỗi")</f>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>119</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -2479,7 +2479,9 @@
         <v>3</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="15"/>
+      <c r="F3" s="15" t="s">
+        <v>455</v>
+      </c>
       <c r="G3" s="7"/>
       <c r="L3" s="7"/>
     </row>
@@ -2497,7 +2499,9 @@
         <v>3</v>
       </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="15"/>
+      <c r="F4" s="15" t="s">
+        <v>456</v>
+      </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2514,7 +2518,9 @@
         <v>3</v>
       </c>
       <c r="E5" s="10"/>
-      <c r="F5" s="15"/>
+      <c r="F5" s="15" t="s">
+        <v>457</v>
+      </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2531,7 +2537,9 @@
         <v>3</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="15"/>
+      <c r="F6" s="15" t="s">
+        <v>458</v>
+      </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2548,7 +2556,9 @@
         <v>3</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="15"/>
+      <c r="F7" s="15" t="s">
+        <v>459</v>
+      </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2565,7 +2575,9 @@
         <v>3</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="15"/>
+      <c r="F8" s="15" t="s">
+        <v>460</v>
+      </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2582,7 +2594,9 @@
         <v>3</v>
       </c>
       <c r="E9" s="10"/>
-      <c r="F9" s="15"/>
+      <c r="F9" s="15" t="s">
+        <v>461</v>
+      </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -2599,7 +2613,9 @@
         <v>3</v>
       </c>
       <c r="E10" s="10"/>
-      <c r="F10" s="15"/>
+      <c r="F10" s="15" t="s">
+        <v>462</v>
+      </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -2616,7 +2632,9 @@
         <v>3</v>
       </c>
       <c r="E11" s="10"/>
-      <c r="F11" s="15"/>
+      <c r="F11" s="15" t="s">
+        <v>463</v>
+      </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -2633,7 +2651,9 @@
         <v>3</v>
       </c>
       <c r="E12" s="10"/>
-      <c r="F12" s="15"/>
+      <c r="F12" s="15" t="s">
+        <v>464</v>
+      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -2650,7 +2670,9 @@
         <v>3</v>
       </c>
       <c r="E13" s="10"/>
-      <c r="F13" s="15"/>
+      <c r="F13" s="15" t="s">
+        <v>465</v>
+      </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -2667,7 +2689,9 @@
         <v>3</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="15"/>
+      <c r="F14" s="15" t="s">
+        <v>466</v>
+      </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -2684,7 +2708,9 @@
         <v>3</v>
       </c>
       <c r="E15" s="10"/>
-      <c r="F15" s="15"/>
+      <c r="F15" s="15" t="s">
+        <v>467</v>
+      </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -2701,7 +2727,9 @@
         <v>3</v>
       </c>
       <c r="E16" s="10"/>
-      <c r="F16" s="15"/>
+      <c r="F16" s="15" t="s">
+        <v>468</v>
+      </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2718,7 +2746,9 @@
         <v>3</v>
       </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="15" t="s">
+        <v>469</v>
+      </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2735,7 +2765,9 @@
         <v>3</v>
       </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="15"/>
+      <c r="F18" s="15" t="s">
+        <v>470</v>
+      </c>
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2752,7 +2784,9 @@
         <v>3</v>
       </c>
       <c r="E19" s="10"/>
-      <c r="F19" s="15"/>
+      <c r="F19" s="15" t="s">
+        <v>471</v>
+      </c>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2769,7 +2803,9 @@
         <v>3</v>
       </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="15"/>
+      <c r="F20" s="15" t="s">
+        <v>472</v>
+      </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2786,7 +2822,9 @@
         <v>3</v>
       </c>
       <c r="E21" s="10"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="15" t="s">
+        <v>473</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2803,7 +2841,9 @@
         <v>3</v>
       </c>
       <c r="E22" s="10"/>
-      <c r="F22" s="18"/>
+      <c r="F22" s="18" t="s">
+        <v>474</v>
+      </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2820,7 +2860,9 @@
         <v>3</v>
       </c>
       <c r="E23" s="10"/>
-      <c r="F23" s="18"/>
+      <c r="F23" s="18" t="s">
+        <v>475</v>
+      </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2837,7 +2879,9 @@
         <v>3</v>
       </c>
       <c r="E24" s="10"/>
-      <c r="F24" s="18"/>
+      <c r="F24" s="18" t="s">
+        <v>476</v>
+      </c>
       <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2854,7 +2898,9 @@
         <v>3</v>
       </c>
       <c r="E25" s="10"/>
-      <c r="F25" s="18"/>
+      <c r="F25" s="18" t="s">
+        <v>477</v>
+      </c>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2871,7 +2917,9 @@
         <v>3</v>
       </c>
       <c r="E26" s="10"/>
-      <c r="F26" s="18"/>
+      <c r="F26" s="18" t="s">
+        <v>478</v>
+      </c>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2888,7 +2936,9 @@
         <v>3</v>
       </c>
       <c r="E27" s="10"/>
-      <c r="F27" s="18"/>
+      <c r="F27" s="18" t="s">
+        <v>479</v>
+      </c>
       <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2905,7 +2955,9 @@
         <v>3</v>
       </c>
       <c r="E28" s="10"/>
-      <c r="F28" s="18"/>
+      <c r="F28" s="18" t="s">
+        <v>480</v>
+      </c>
       <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2922,7 +2974,9 @@
         <v>3</v>
       </c>
       <c r="E29" s="10"/>
-      <c r="F29" s="18"/>
+      <c r="F29" s="18" t="s">
+        <v>481</v>
+      </c>
       <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2939,7 +2993,9 @@
         <v>3</v>
       </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="18"/>
+      <c r="F30" s="18" t="s">
+        <v>482</v>
+      </c>
       <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2956,7 +3012,9 @@
         <v>3</v>
       </c>
       <c r="E31" s="10"/>
-      <c r="F31" s="18"/>
+      <c r="F31" s="18" t="s">
+        <v>483</v>
+      </c>
       <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2973,7 +3031,9 @@
         <v>3</v>
       </c>
       <c r="E32" s="10"/>
-      <c r="F32" s="18"/>
+      <c r="F32" s="18" t="s">
+        <v>484</v>
+      </c>
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2990,7 +3050,9 @@
         <v>3</v>
       </c>
       <c r="E33" s="10"/>
-      <c r="F33" s="18"/>
+      <c r="F33" s="18" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
@@ -3006,7 +3068,9 @@
         <v>3</v>
       </c>
       <c r="E34" s="10"/>
-      <c r="F34" s="18"/>
+      <c r="F34" s="18" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
@@ -3022,7 +3086,9 @@
         <v>3</v>
       </c>
       <c r="E35" s="10"/>
-      <c r="F35" s="18"/>
+      <c r="F35" s="18" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
@@ -3038,7 +3104,9 @@
         <v>3</v>
       </c>
       <c r="E36" s="10"/>
-      <c r="F36" s="18"/>
+      <c r="F36" s="18" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
@@ -3054,7 +3122,9 @@
         <v>3</v>
       </c>
       <c r="E37" s="10"/>
-      <c r="F37" s="18"/>
+      <c r="F37" s="18" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
@@ -3070,7 +3140,9 @@
         <v>3</v>
       </c>
       <c r="E38" s="10"/>
-      <c r="F38" s="18"/>
+      <c r="F38" s="18" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
@@ -3086,7 +3158,9 @@
         <v>3</v>
       </c>
       <c r="E39" s="10"/>
-      <c r="F39" s="18"/>
+      <c r="F39" s="18" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
@@ -3102,7 +3176,9 @@
         <v>3</v>
       </c>
       <c r="E40" s="10"/>
-      <c r="F40" s="18"/>
+      <c r="F40" s="18" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
@@ -3118,7 +3194,9 @@
         <v>3</v>
       </c>
       <c r="E41" s="10"/>
-      <c r="F41" s="18"/>
+      <c r="F41" s="18" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
@@ -3134,7 +3212,9 @@
         <v>3</v>
       </c>
       <c r="E42" s="10"/>
-      <c r="F42" s="18"/>
+      <c r="F42" s="18" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
@@ -3150,7 +3230,9 @@
         <v>3</v>
       </c>
       <c r="E43" s="10"/>
-      <c r="F43" s="18"/>
+      <c r="F43" s="18" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
@@ -3166,7 +3248,9 @@
         <v>3</v>
       </c>
       <c r="E44" s="10"/>
-      <c r="F44" s="18"/>
+      <c r="F44" s="18" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
@@ -3182,7 +3266,9 @@
         <v>3</v>
       </c>
       <c r="E45" s="10"/>
-      <c r="F45" s="18"/>
+      <c r="F45" s="18" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
@@ -3198,7 +3284,9 @@
         <v>3</v>
       </c>
       <c r="E46" s="10"/>
-      <c r="F46" s="18"/>
+      <c r="F46" s="18" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
@@ -3214,7 +3302,9 @@
         <v>3</v>
       </c>
       <c r="E47" s="10"/>
-      <c r="F47" s="18"/>
+      <c r="F47" s="18" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
@@ -3230,7 +3320,9 @@
         <v>3</v>
       </c>
       <c r="E48" s="10"/>
-      <c r="F48" s="18"/>
+      <c r="F48" s="18" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
@@ -3246,7 +3338,9 @@
         <v>3</v>
       </c>
       <c r="E49" s="10"/>
-      <c r="F49" s="18"/>
+      <c r="F49" s="18" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
@@ -3262,7 +3356,9 @@
         <v>3</v>
       </c>
       <c r="E50" s="10"/>
-      <c r="F50" s="18"/>
+      <c r="F50" s="18" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
@@ -3278,7 +3374,9 @@
         <v>3</v>
       </c>
       <c r="E51" s="10"/>
-      <c r="F51" s="18"/>
+      <c r="F51" s="18" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
@@ -3294,7 +3392,9 @@
         <v>3</v>
       </c>
       <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
+      <c r="F52" s="10" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
@@ -3310,7 +3410,9 @@
         <v>3</v>
       </c>
       <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
+      <c r="F53" s="10" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
@@ -3326,7 +3428,9 @@
         <v>3</v>
       </c>
       <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
+      <c r="F54" s="10" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
@@ -3342,7 +3446,9 @@
         <v>3</v>
       </c>
       <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
+      <c r="F55" s="10" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
@@ -3358,7 +3464,9 @@
         <v>3</v>
       </c>
       <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
+      <c r="F56" s="10" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
@@ -3374,7 +3482,9 @@
         <v>3</v>
       </c>
       <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
+      <c r="F57" s="10" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
@@ -3390,7 +3500,9 @@
         <v>3</v>
       </c>
       <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
+      <c r="F58" s="10" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
@@ -3406,7 +3518,9 @@
         <v>3</v>
       </c>
       <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
+      <c r="F59" s="10" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
@@ -3422,7 +3536,9 @@
         <v>3</v>
       </c>
       <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
+      <c r="F60" s="10" t="s">
+        <v>513</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
@@ -3438,7 +3554,9 @@
         <v>3</v>
       </c>
       <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
+      <c r="F61" s="10" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
@@ -3454,7 +3572,9 @@
         <v>3</v>
       </c>
       <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
+      <c r="F62" s="10" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
@@ -3470,7 +3590,9 @@
         <v>3</v>
       </c>
       <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
+      <c r="F63" s="10" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
@@ -3486,7 +3608,9 @@
         <v>3</v>
       </c>
       <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
+      <c r="F64" s="10" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
@@ -3502,7 +3626,9 @@
         <v>3</v>
       </c>
       <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
+      <c r="F65" s="10" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
@@ -3518,7 +3644,9 @@
         <v>3</v>
       </c>
       <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
+      <c r="F66" s="10" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
@@ -3534,7 +3662,9 @@
         <v>3</v>
       </c>
       <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
+      <c r="F67" s="10" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
@@ -3550,7 +3680,9 @@
         <v>3</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
+      <c r="F68" s="10" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
@@ -3566,7 +3698,9 @@
         <v>3</v>
       </c>
       <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
+      <c r="F69" s="10" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
@@ -3582,7 +3716,9 @@
         <v>3</v>
       </c>
       <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
+      <c r="F70" s="10" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
@@ -3598,7 +3734,9 @@
         <v>3</v>
       </c>
       <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
+      <c r="F71" s="10" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
@@ -3614,7 +3752,9 @@
         <v>3</v>
       </c>
       <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
+      <c r="F72" s="10" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
@@ -3630,7 +3770,9 @@
         <v>3</v>
       </c>
       <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
+      <c r="F73" s="10" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
@@ -3646,7 +3788,9 @@
         <v>3</v>
       </c>
       <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
+      <c r="F74" s="10" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
@@ -3662,7 +3806,9 @@
         <v>3</v>
       </c>
       <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
+      <c r="F75" s="10" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
@@ -3678,7 +3824,9 @@
         <v>3</v>
       </c>
       <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
+      <c r="F76" s="10" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
@@ -3694,7 +3842,9 @@
         <v>3</v>
       </c>
       <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
+      <c r="F77" s="10" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
@@ -3710,7 +3860,9 @@
         <v>3</v>
       </c>
       <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
+      <c r="F78" s="10" t="s">
+        <v>533</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
@@ -3726,7 +3878,9 @@
         <v>3</v>
       </c>
       <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
+      <c r="F79" s="10" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
@@ -3742,7 +3896,9 @@
         <v>3</v>
       </c>
       <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
+      <c r="F80" s="10" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
@@ -3758,7 +3914,9 @@
         <v>3</v>
       </c>
       <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
+      <c r="F81" s="10" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
@@ -3774,7 +3932,9 @@
         <v>3</v>
       </c>
       <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
+      <c r="F82" s="10" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
@@ -3790,7 +3950,9 @@
         <v>3</v>
       </c>
       <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
+      <c r="F83" s="10" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
@@ -3806,7 +3968,9 @@
         <v>3</v>
       </c>
       <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
+      <c r="F84" s="10" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
@@ -3822,7 +3986,9 @@
         <v>3</v>
       </c>
       <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
+      <c r="F85" s="10" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
@@ -3838,7 +4004,9 @@
         <v>3</v>
       </c>
       <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
+      <c r="F86" s="10" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
@@ -3854,7 +4022,9 @@
         <v>3</v>
       </c>
       <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
+      <c r="F87" s="10" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
@@ -3870,7 +4040,9 @@
         <v>3</v>
       </c>
       <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
+      <c r="F88" s="10" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
@@ -3886,7 +4058,9 @@
         <v>3</v>
       </c>
       <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
+      <c r="F89" s="10" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
@@ -3902,7 +4076,9 @@
         <v>3</v>
       </c>
       <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
+      <c r="F90" s="10" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
@@ -3918,7 +4094,9 @@
         <v>3</v>
       </c>
       <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
+      <c r="F91" s="10" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
@@ -3934,7 +4112,9 @@
         <v>3</v>
       </c>
       <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
+      <c r="F92" s="10" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
@@ -3950,7 +4130,9 @@
         <v>3</v>
       </c>
       <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
+      <c r="F93" s="10" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
@@ -3966,7 +4148,9 @@
         <v>3</v>
       </c>
       <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
+      <c r="F94" s="10" t="s">
+        <v>549</v>
+      </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
@@ -3982,7 +4166,9 @@
         <v>3</v>
       </c>
       <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
+      <c r="F95" s="10" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
@@ -3998,7 +4184,9 @@
         <v>3</v>
       </c>
       <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
+      <c r="F96" s="10" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
@@ -4014,7 +4202,9 @@
         <v>3</v>
       </c>
       <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
+      <c r="F97" s="10" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
@@ -4030,7 +4220,9 @@
         <v>3</v>
       </c>
       <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
+      <c r="F98" s="10" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
@@ -4046,7 +4238,9 @@
         <v>3</v>
       </c>
       <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
+      <c r="F99" s="10" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
@@ -4062,7 +4256,9 @@
         <v>3</v>
       </c>
       <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
+      <c r="F100" s="10" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
@@ -4078,7 +4274,9 @@
         <v>3</v>
       </c>
       <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
+      <c r="F101" s="10" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
@@ -4094,7 +4292,9 @@
         <v>3</v>
       </c>
       <c r="E102" s="10"/>
-      <c r="F102" s="10"/>
+      <c r="F102" s="10" t="s">
+        <v>557</v>
+      </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
@@ -4110,7 +4310,9 @@
         <v>3</v>
       </c>
       <c r="E103" s="10"/>
-      <c r="F103" s="10"/>
+      <c r="F103" s="10" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
@@ -4126,7 +4328,9 @@
         <v>3</v>
       </c>
       <c r="E104" s="10"/>
-      <c r="F104" s="10"/>
+      <c r="F104" s="10" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
@@ -4142,7 +4346,9 @@
         <v>3</v>
       </c>
       <c r="E105" s="10"/>
-      <c r="F105" s="10"/>
+      <c r="F105" s="10" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
@@ -4158,7 +4364,9 @@
         <v>3</v>
       </c>
       <c r="E106" s="10"/>
-      <c r="F106" s="10"/>
+      <c r="F106" s="10" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
@@ -4174,7 +4382,9 @@
         <v>3</v>
       </c>
       <c r="E107" s="10"/>
-      <c r="F107" s="10"/>
+      <c r="F107" s="10" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
@@ -4190,7 +4400,9 @@
         <v>3</v>
       </c>
       <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
+      <c r="F108" s="10" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
@@ -4206,7 +4418,9 @@
         <v>3</v>
       </c>
       <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
+      <c r="F109" s="10" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
@@ -9458,7 +9672,9 @@
       <c r="C436" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D436" s="3"/>
+      <c r="D436" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
     </row>
@@ -9472,7 +9688,9 @@
       <c r="C437" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D437" s="3"/>
+      <c r="D437" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
     </row>
@@ -9486,7 +9704,9 @@
       <c r="C438" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="3"/>
+      <c r="D438" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
     </row>
@@ -9500,7 +9720,9 @@
       <c r="C439" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D439" s="3"/>
+      <c r="D439" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
     </row>
@@ -9514,7 +9736,9 @@
       <c r="C440" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D440" s="3"/>
+      <c r="D440" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
     </row>
@@ -9528,7 +9752,9 @@
       <c r="C441" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D441" s="3"/>
+      <c r="D441" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
     </row>
@@ -9542,7 +9768,9 @@
       <c r="C442" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D442" s="3"/>
+      <c r="D442" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
     </row>
@@ -9556,7 +9784,9 @@
       <c r="C443" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D443" s="3"/>
+      <c r="D443" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
     </row>
@@ -9570,7 +9800,9 @@
       <c r="C444" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D444" s="3"/>
+      <c r="D444" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
     </row>
@@ -9584,7 +9816,9 @@
       <c r="C445" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D445" s="3"/>
+      <c r="D445" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
     </row>
@@ -9598,7 +9832,9 @@
       <c r="C446" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D446" s="3"/>
+      <c r="D446" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
     </row>
@@ -9612,7 +9848,9 @@
       <c r="C447" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D447" s="3"/>
+      <c r="D447" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
     </row>
@@ -9626,7 +9864,9 @@
       <c r="C448" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D448" s="3"/>
+      <c r="D448" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
     </row>
@@ -9640,7 +9880,9 @@
       <c r="C449" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D449" s="3"/>
+      <c r="D449" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
     </row>
@@ -9654,7 +9896,9 @@
       <c r="C450" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D450" s="3"/>
+      <c r="D450" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
     </row>
@@ -9668,7 +9912,9 @@
       <c r="C451" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D451" s="3"/>
+      <c r="D451" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
     </row>
@@ -9682,7 +9928,9 @@
       <c r="C452" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D452" s="3"/>
+      <c r="D452" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
     </row>
@@ -9696,7 +9944,9 @@
       <c r="C453" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D453" s="3"/>
+      <c r="D453" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
     </row>
@@ -9710,7 +9960,9 @@
       <c r="C454" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D454" s="3"/>
+      <c r="D454" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
     </row>
@@ -9724,7 +9976,9 @@
       <c r="C455" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D455" s="3"/>
+      <c r="D455" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
     </row>
@@ -9738,7 +9992,9 @@
       <c r="C456" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D456" s="3"/>
+      <c r="D456" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
     </row>
@@ -9752,7 +10008,9 @@
       <c r="C457" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D457" s="3"/>
+      <c r="D457" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
     </row>
@@ -9766,7 +10024,9 @@
       <c r="C458" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D458" s="3"/>
+      <c r="D458" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
     </row>
@@ -9780,7 +10040,9 @@
       <c r="C459" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D459" s="3"/>
+      <c r="D459" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
     </row>
@@ -9794,7 +10056,9 @@
       <c r="C460" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D460" s="3"/>
+      <c r="D460" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
     </row>
@@ -9808,7 +10072,9 @@
       <c r="C461" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D461" s="3"/>
+      <c r="D461" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
     </row>
@@ -9822,7 +10088,9 @@
       <c r="C462" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D462" s="3"/>
+      <c r="D462" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
     </row>
@@ -9836,7 +10104,9 @@
       <c r="C463" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D463" s="3"/>
+      <c r="D463" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E463" s="10"/>
       <c r="F463" s="10"/>
     </row>
@@ -9850,7 +10120,9 @@
       <c r="C464" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D464" s="3"/>
+      <c r="D464" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E464" s="10"/>
       <c r="F464" s="10"/>
     </row>
@@ -9864,7 +10136,9 @@
       <c r="C465" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D465" s="3"/>
+      <c r="D465" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E465" s="10"/>
       <c r="F465" s="10"/>
     </row>
@@ -9878,7 +10152,9 @@
       <c r="C466" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D466" s="3"/>
+      <c r="D466" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E466" s="10"/>
       <c r="F466" s="10"/>
     </row>
@@ -9892,7 +10168,9 @@
       <c r="C467" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D467" s="3"/>
+      <c r="D467" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E467" s="10"/>
       <c r="F467" s="10"/>
     </row>
@@ -9906,7 +10184,9 @@
       <c r="C468" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D468" s="3"/>
+      <c r="D468" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E468" s="10"/>
       <c r="F468" s="10"/>
     </row>
@@ -9920,7 +10200,9 @@
       <c r="C469" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D469" s="3"/>
+      <c r="D469" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E469" s="10"/>
       <c r="F469" s="10"/>
     </row>
@@ -9934,7 +10216,9 @@
       <c r="C470" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D470" s="3"/>
+      <c r="D470" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E470" s="10"/>
       <c r="F470" s="10"/>
     </row>
@@ -9948,7 +10232,9 @@
       <c r="C471" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D471" s="3"/>
+      <c r="D471" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E471" s="10"/>
       <c r="F471" s="10"/>
     </row>
@@ -9962,7 +10248,9 @@
       <c r="C472" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D472" s="3"/>
+      <c r="D472" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E472" s="10"/>
       <c r="F472" s="10"/>
     </row>
@@ -9976,7 +10264,9 @@
       <c r="C473" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D473" s="3"/>
+      <c r="D473" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E473" s="10"/>
       <c r="F473" s="10"/>
     </row>
@@ -9990,7 +10280,9 @@
       <c r="C474" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D474" s="3"/>
+      <c r="D474" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E474" s="10"/>
       <c r="F474" s="10"/>
     </row>
@@ -10004,7 +10296,9 @@
       <c r="C475" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D475" s="3"/>
+      <c r="D475" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E475" s="10"/>
       <c r="F475" s="10"/>
     </row>
@@ -10018,7 +10312,9 @@
       <c r="C476" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D476" s="3"/>
+      <c r="D476" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E476" s="10"/>
       <c r="F476" s="10"/>
     </row>
@@ -10032,7 +10328,9 @@
       <c r="C477" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D477" s="3"/>
+      <c r="D477" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E477" s="10"/>
       <c r="F477" s="10"/>
     </row>
@@ -10046,7 +10344,9 @@
       <c r="C478" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D478" s="3"/>
+      <c r="D478" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E478" s="10"/>
       <c r="F478" s="10"/>
     </row>
@@ -10060,7 +10360,9 @@
       <c r="C479" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D479" s="3"/>
+      <c r="D479" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E479" s="10"/>
       <c r="F479" s="10"/>
     </row>
@@ -10074,7 +10376,9 @@
       <c r="C480" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D480" s="3"/>
+      <c r="D480" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E480" s="10"/>
       <c r="F480" s="10"/>
     </row>
@@ -10088,7 +10392,9 @@
       <c r="C481" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D481" s="3"/>
+      <c r="D481" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E481" s="10"/>
       <c r="F481" s="10"/>
     </row>
@@ -10102,7 +10408,9 @@
       <c r="C482" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D482" s="3"/>
+      <c r="D482" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E482" s="10"/>
       <c r="F482" s="10"/>
     </row>
@@ -10116,7 +10424,9 @@
       <c r="C483" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D483" s="3"/>
+      <c r="D483" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E483" s="10"/>
       <c r="F483" s="10"/>
     </row>
@@ -10130,7 +10440,9 @@
       <c r="C484" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D484" s="3"/>
+      <c r="D484" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E484" s="10"/>
       <c r="F484" s="10"/>
     </row>
@@ -10144,7 +10456,9 @@
       <c r="C485" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D485" s="3"/>
+      <c r="D485" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E485" s="10"/>
       <c r="F485" s="10"/>
     </row>
@@ -10158,7 +10472,9 @@
       <c r="C486" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D486" s="3"/>
+      <c r="D486" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E486" s="10"/>
       <c r="F486" s="10"/>
     </row>
@@ -10172,7 +10488,9 @@
       <c r="C487" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D487" s="3"/>
+      <c r="D487" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E487" s="10"/>
       <c r="F487" s="10"/>
     </row>
@@ -10186,7 +10504,9 @@
       <c r="C488" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D488" s="3"/>
+      <c r="D488" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E488" s="10"/>
       <c r="F488" s="10"/>
     </row>
@@ -10200,7 +10520,9 @@
       <c r="C489" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D489" s="3"/>
+      <c r="D489" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E489" s="10"/>
       <c r="F489" s="10"/>
     </row>
@@ -10228,7 +10550,9 @@
       <c r="C491" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D491" s="3"/>
+      <c r="D491" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E491" s="10"/>
       <c r="F491" s="10"/>
     </row>
@@ -10242,7 +10566,9 @@
       <c r="C492" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D492" s="3"/>
+      <c r="D492" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E492" s="10"/>
       <c r="F492" s="10"/>
     </row>
@@ -10256,7 +10582,9 @@
       <c r="C493" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D493" s="3"/>
+      <c r="D493" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E493" s="10"/>
       <c r="F493" s="10"/>
     </row>
@@ -10270,7 +10598,9 @@
       <c r="C494" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D494" s="3"/>
+      <c r="D494" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E494" s="10"/>
       <c r="F494" s="10"/>
     </row>
@@ -10284,7 +10614,9 @@
       <c r="C495" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D495" s="3"/>
+      <c r="D495" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E495" s="10"/>
       <c r="F495" s="10"/>
     </row>
@@ -10326,7 +10658,9 @@
       <c r="C498" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D498" s="3"/>
+      <c r="D498" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E498" s="10"/>
       <c r="F498" s="10"/>
     </row>
@@ -10340,7 +10674,9 @@
       <c r="C499" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D499" s="3"/>
+      <c r="D499" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E499" s="10"/>
       <c r="F499" s="10"/>
     </row>
@@ -10354,7 +10690,9 @@
       <c r="C500" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D500" s="3"/>
+      <c r="D500" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E500" s="10"/>
       <c r="F500" s="10"/>
     </row>
@@ -10368,7 +10706,9 @@
       <c r="C501" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D501" s="3"/>
+      <c r="D501" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E501" s="10"/>
       <c r="F501" s="10"/>
     </row>
@@ -10382,7 +10722,9 @@
       <c r="C502" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D502" s="3"/>
+      <c r="D502" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E502" s="10"/>
       <c r="F502" s="10"/>
     </row>
@@ -10396,7 +10738,9 @@
       <c r="C503" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D503" s="3"/>
+      <c r="D503" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E503" s="10"/>
       <c r="F503" s="10"/>
     </row>
@@ -10410,7 +10754,9 @@
       <c r="C504" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D504" s="3"/>
+      <c r="D504" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E504" s="10"/>
       <c r="F504" s="10"/>
     </row>
@@ -10424,7 +10770,9 @@
       <c r="C505" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D505" s="3"/>
+      <c r="D505" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E505" s="10"/>
       <c r="F505" s="10"/>
     </row>
@@ -10438,7 +10786,9 @@
       <c r="C506" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D506" s="3"/>
+      <c r="D506" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E506" s="10"/>
       <c r="F506" s="10"/>
     </row>
@@ -10452,7 +10802,9 @@
       <c r="C507" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D507" s="3"/>
+      <c r="D507" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E507" s="10"/>
       <c r="F507" s="10"/>
     </row>
@@ -10466,7 +10818,9 @@
       <c r="C508" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D508" s="3"/>
+      <c r="D508" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E508" s="10"/>
       <c r="F508" s="10"/>
     </row>
@@ -10480,7 +10834,9 @@
       <c r="C509" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D509" s="3"/>
+      <c r="D509" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E509" s="10"/>
       <c r="F509" s="10"/>
     </row>
@@ -10494,7 +10850,9 @@
       <c r="C510" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D510" s="3"/>
+      <c r="D510" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E510" s="10"/>
       <c r="F510" s="10"/>
     </row>
@@ -10508,7 +10866,9 @@
       <c r="C511" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D511" s="3"/>
+      <c r="D511" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E511" s="10"/>
       <c r="F511" s="10"/>
     </row>
@@ -10522,7 +10882,9 @@
       <c r="C512" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D512" s="3"/>
+      <c r="D512" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E512" s="10"/>
       <c r="F512" s="10"/>
     </row>
@@ -10536,7 +10898,9 @@
       <c r="C513" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D513" s="3"/>
+      <c r="D513" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E513" s="10"/>
       <c r="F513" s="10"/>
     </row>
@@ -10550,7 +10914,9 @@
       <c r="C514" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D514" s="3"/>
+      <c r="D514" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E514" s="10"/>
       <c r="F514" s="10"/>
     </row>
@@ -10564,7 +10930,9 @@
       <c r="C515" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D515" s="3"/>
+      <c r="D515" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E515" s="10"/>
       <c r="F515" s="10"/>
     </row>
@@ -10578,7 +10946,9 @@
       <c r="C516" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D516" s="3"/>
+      <c r="D516" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E516" s="10"/>
       <c r="F516" s="10"/>
     </row>
@@ -10592,7 +10962,9 @@
       <c r="C517" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D517" s="3"/>
+      <c r="D517" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E517" s="10"/>
       <c r="F517" s="10"/>
     </row>
@@ -10606,7 +10978,9 @@
       <c r="C518" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D518" s="3"/>
+      <c r="D518" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E518" s="10"/>
       <c r="F518" s="10"/>
     </row>
@@ -10620,7 +10994,9 @@
       <c r="C519" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D519" s="3"/>
+      <c r="D519" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E519" s="10"/>
       <c r="F519" s="10"/>
     </row>
@@ -10634,7 +11010,9 @@
       <c r="C520" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D520" s="3"/>
+      <c r="D520" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E520" s="10"/>
       <c r="F520" s="10"/>
     </row>
@@ -10648,7 +11026,9 @@
       <c r="C521" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D521" s="3"/>
+      <c r="D521" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E521" s="10"/>
       <c r="F521" s="10"/>
     </row>
@@ -10662,7 +11042,9 @@
       <c r="C522" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D522" s="3"/>
+      <c r="D522" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E522" s="10"/>
       <c r="F522" s="10"/>
     </row>
@@ -10676,7 +11058,9 @@
       <c r="C523" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D523" s="3"/>
+      <c r="D523" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E523" s="10"/>
       <c r="F523" s="10"/>
     </row>
@@ -10690,7 +11074,9 @@
       <c r="C524" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D524" s="3"/>
+      <c r="D524" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E524" s="10"/>
       <c r="F524" s="10"/>
     </row>
@@ -10704,7 +11090,9 @@
       <c r="C525" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D525" s="3"/>
+      <c r="D525" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E525" s="10"/>
       <c r="F525" s="10"/>
     </row>
@@ -10718,7 +11106,9 @@
       <c r="C526" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D526" s="3"/>
+      <c r="D526" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E526" s="10"/>
       <c r="F526" s="10"/>
     </row>
@@ -10732,7 +11122,9 @@
       <c r="C527" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D527" s="3"/>
+      <c r="D527" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E527" s="10"/>
       <c r="F527" s="10"/>
     </row>
@@ -10746,7 +11138,9 @@
       <c r="C528" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D528" s="3"/>
+      <c r="D528" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E528" s="10"/>
       <c r="F528" s="10"/>
     </row>
@@ -10760,7 +11154,9 @@
       <c r="C529" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D529" s="3"/>
+      <c r="D529" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E529" s="10"/>
       <c r="F529" s="10"/>
     </row>
@@ -10774,7 +11170,9 @@
       <c r="C530" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D530" s="3"/>
+      <c r="D530" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E530" s="10"/>
       <c r="F530" s="10"/>
     </row>
@@ -10788,7 +11186,9 @@
       <c r="C531" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D531" s="3"/>
+      <c r="D531" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E531" s="10"/>
       <c r="F531" s="10"/>
     </row>
@@ -10802,7 +11202,9 @@
       <c r="C532" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D532" s="3"/>
+      <c r="D532" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E532" s="10"/>
       <c r="F532" s="10"/>
     </row>
@@ -10816,7 +11218,9 @@
       <c r="C533" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D533" s="3"/>
+      <c r="D533" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E533" s="10"/>
       <c r="F533" s="10"/>
     </row>
@@ -10830,7 +11234,9 @@
       <c r="C534" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D534" s="3"/>
+      <c r="D534" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E534" s="10"/>
       <c r="F534" s="10"/>
     </row>
@@ -10844,7 +11250,9 @@
       <c r="C535" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D535" s="3"/>
+      <c r="D535" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E535" s="10"/>
       <c r="F535" s="10"/>
     </row>
@@ -10858,7 +11266,9 @@
       <c r="C536" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D536" s="3"/>
+      <c r="D536" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E536" s="10"/>
       <c r="F536" s="10"/>
     </row>
@@ -10872,7 +11282,9 @@
       <c r="C537" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D537" s="3"/>
+      <c r="D537" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E537" s="10"/>
       <c r="F537" s="10"/>
     </row>
@@ -10886,7 +11298,9 @@
       <c r="C538" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D538" s="3"/>
+      <c r="D538" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E538" s="10"/>
       <c r="F538" s="10"/>
     </row>
@@ -10900,7 +11314,9 @@
       <c r="C539" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D539" s="3"/>
+      <c r="D539" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E539" s="10"/>
       <c r="F539" s="10"/>
     </row>
@@ -10914,7 +11330,9 @@
       <c r="C540" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D540" s="3"/>
+      <c r="D540" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E540" s="10"/>
       <c r="F540" s="10"/>
     </row>
@@ -10928,7 +11346,9 @@
       <c r="C541" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D541" s="3"/>
+      <c r="D541" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E541" s="10"/>
       <c r="F541" s="10"/>
     </row>
@@ -10942,7 +11362,9 @@
       <c r="C542" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D542" s="3"/>
+      <c r="D542" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E542" s="10"/>
       <c r="F542" s="10"/>
     </row>
@@ -10956,7 +11378,9 @@
       <c r="C543" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D543" s="3"/>
+      <c r="D543" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E543" s="10"/>
       <c r="F543" s="10"/>
     </row>
@@ -10970,7 +11394,9 @@
       <c r="C544" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D544" s="3"/>
+      <c r="D544" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E544" s="10"/>
       <c r="F544" s="10"/>
     </row>
@@ -10984,7 +11410,9 @@
       <c r="C545" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D545" s="3"/>
+      <c r="D545" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E545" s="10"/>
       <c r="F545" s="10"/>
     </row>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4279DD81-783E-41F6-91E0-3B6116F8EF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E649D0-3499-4612-A279-B95DBFE16307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="567">
   <si>
     <t>STT</t>
   </si>
@@ -1723,6 +1723,12 @@
   </si>
   <si>
     <t>VNET860879084174982</t>
+  </si>
+  <si>
+    <t>112 thiết bị chưa nhập ID</t>
+  </si>
+  <si>
+    <t>Lỗi, Đã trả lại gia công</t>
   </si>
 </sst>
 </file>
@@ -2366,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:M1001"/>
+  <dimension ref="A1:N1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="8" customWidth="1"/>
@@ -2382,7 +2388,7 @@
     <col min="13" max="13" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2421,7 +2427,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2442,11 +2448,11 @@
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="I2" s="25">
         <f>COUNTIFS(D2:D1001,"Lỗi")</f>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J2" s="25">
         <f>COUNTIFS(E2:E1001,"*Trả lại X-Force*")</f>
@@ -2454,7 +2460,7 @@
       </c>
       <c r="K2" s="25">
         <f>SUM(I2-J2)</f>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="30">
         <f>COUNTIFS(D2:D1001,"Đã cho mượn")</f>
@@ -2462,10 +2468,13 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2480,12 +2489,12 @@
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="15" t="s">
-        <v>455</v>
+        <v>554</v>
       </c>
       <c r="G3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2500,11 +2509,11 @@
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="15" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2519,11 +2528,11 @@
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="15" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2538,11 +2547,11 @@
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="15" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2557,11 +2566,11 @@
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="15" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2576,11 +2585,11 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="15" t="s">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2595,11 +2604,11 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="15" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2614,11 +2623,11 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="15" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2633,11 +2642,11 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="15" t="s">
-        <v>463</v>
+        <v>425</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2652,11 +2661,11 @@
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="15" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2671,11 +2680,11 @@
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="15" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2690,11 +2699,11 @@
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="15" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2709,11 +2718,11 @@
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="15" t="s">
-        <v>467</v>
+        <v>417</v>
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2728,7 +2737,7 @@
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="15" t="s">
-        <v>468</v>
+        <v>414</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -2747,7 +2756,7 @@
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="15" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -2766,7 +2775,7 @@
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="15" t="s">
-        <v>470</v>
+        <v>421</v>
       </c>
       <c r="G18" s="16"/>
     </row>
@@ -2785,7 +2794,7 @@
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="15" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="G19" s="7"/>
     </row>
@@ -2804,7 +2813,7 @@
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="15" t="s">
-        <v>472</v>
+        <v>415</v>
       </c>
       <c r="G20" s="7"/>
     </row>
@@ -2823,7 +2832,7 @@
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="15" t="s">
-        <v>473</v>
+        <v>416</v>
       </c>
       <c r="G21" s="7"/>
     </row>
@@ -2842,7 +2851,7 @@
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="18" t="s">
-        <v>474</v>
+        <v>435</v>
       </c>
       <c r="G22" s="7"/>
     </row>
@@ -2861,7 +2870,7 @@
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="18" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="G23" s="7"/>
     </row>
@@ -2879,9 +2888,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="10"/>
-      <c r="F24" s="18" t="s">
-        <v>476</v>
-      </c>
+      <c r="F24" s="18"/>
       <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,9 +2905,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="10"/>
-      <c r="F25" s="18" t="s">
-        <v>477</v>
-      </c>
+      <c r="F25" s="18"/>
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2917,9 +2922,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="10"/>
-      <c r="F26" s="18" t="s">
-        <v>478</v>
-      </c>
+      <c r="F26" s="18"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2936,9 +2939,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="10"/>
-      <c r="F27" s="18" t="s">
-        <v>479</v>
-      </c>
+      <c r="F27" s="18"/>
       <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2955,9 +2956,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="10"/>
-      <c r="F28" s="18" t="s">
-        <v>480</v>
-      </c>
+      <c r="F28" s="18"/>
       <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2974,9 +2973,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="10"/>
-      <c r="F29" s="18" t="s">
-        <v>481</v>
-      </c>
+      <c r="F29" s="18"/>
       <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2993,9 +2990,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="18" t="s">
-        <v>482</v>
-      </c>
+      <c r="F30" s="18"/>
       <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3012,9 +3007,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="10"/>
-      <c r="F31" s="18" t="s">
-        <v>483</v>
-      </c>
+      <c r="F31" s="18"/>
       <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3031,9 +3024,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="10"/>
-      <c r="F32" s="18" t="s">
-        <v>484</v>
-      </c>
+      <c r="F32" s="18"/>
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3050,9 +3041,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="10"/>
-      <c r="F33" s="18" t="s">
-        <v>485</v>
-      </c>
+      <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
@@ -3068,9 +3057,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="10"/>
-      <c r="F34" s="18" t="s">
-        <v>486</v>
-      </c>
+      <c r="F34" s="18"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
@@ -3086,9 +3073,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="10"/>
-      <c r="F35" s="18" t="s">
-        <v>487</v>
-      </c>
+      <c r="F35" s="18"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
@@ -3104,9 +3089,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="10"/>
-      <c r="F36" s="18" t="s">
-        <v>488</v>
-      </c>
+      <c r="F36" s="18"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
@@ -3122,9 +3105,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="10"/>
-      <c r="F37" s="18" t="s">
-        <v>489</v>
-      </c>
+      <c r="F37" s="18"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
@@ -3140,9 +3121,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="10"/>
-      <c r="F38" s="18" t="s">
-        <v>490</v>
-      </c>
+      <c r="F38" s="18"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
@@ -3158,9 +3137,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="10"/>
-      <c r="F39" s="18" t="s">
-        <v>491</v>
-      </c>
+      <c r="F39" s="18"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
@@ -3176,9 +3153,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="10"/>
-      <c r="F40" s="18" t="s">
-        <v>492</v>
-      </c>
+      <c r="F40" s="18"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
@@ -3194,9 +3169,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="10"/>
-      <c r="F41" s="18" t="s">
-        <v>493</v>
-      </c>
+      <c r="F41" s="18"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
@@ -3212,9 +3185,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="10"/>
-      <c r="F42" s="18" t="s">
-        <v>494</v>
-      </c>
+      <c r="F42" s="18"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
@@ -3230,9 +3201,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="10"/>
-      <c r="F43" s="18" t="s">
-        <v>495</v>
-      </c>
+      <c r="F43" s="18"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
@@ -3248,9 +3217,7 @@
         <v>3</v>
       </c>
       <c r="E44" s="10"/>
-      <c r="F44" s="18" t="s">
-        <v>496</v>
-      </c>
+      <c r="F44" s="18"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
@@ -3266,9 +3233,7 @@
         <v>3</v>
       </c>
       <c r="E45" s="10"/>
-      <c r="F45" s="18" t="s">
-        <v>497</v>
-      </c>
+      <c r="F45" s="18"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
@@ -3284,9 +3249,7 @@
         <v>3</v>
       </c>
       <c r="E46" s="10"/>
-      <c r="F46" s="18" t="s">
-        <v>498</v>
-      </c>
+      <c r="F46" s="18"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
@@ -3302,9 +3265,7 @@
         <v>3</v>
       </c>
       <c r="E47" s="10"/>
-      <c r="F47" s="18" t="s">
-        <v>499</v>
-      </c>
+      <c r="F47" s="18"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
@@ -3320,9 +3281,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="10"/>
-      <c r="F48" s="18" t="s">
-        <v>500</v>
-      </c>
+      <c r="F48" s="18"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
@@ -3338,9 +3297,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="10"/>
-      <c r="F49" s="18" t="s">
-        <v>501</v>
-      </c>
+      <c r="F49" s="18"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
@@ -3356,9 +3313,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="10"/>
-      <c r="F50" s="18" t="s">
-        <v>502</v>
-      </c>
+      <c r="F50" s="18"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
@@ -3374,9 +3329,7 @@
         <v>3</v>
       </c>
       <c r="E51" s="10"/>
-      <c r="F51" s="18" t="s">
-        <v>503</v>
-      </c>
+      <c r="F51" s="18"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
@@ -3392,9 +3345,7 @@
         <v>3</v>
       </c>
       <c r="E52" s="10"/>
-      <c r="F52" s="10" t="s">
-        <v>504</v>
-      </c>
+      <c r="F52" s="10"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
@@ -3410,9 +3361,7 @@
         <v>3</v>
       </c>
       <c r="E53" s="10"/>
-      <c r="F53" s="10" t="s">
-        <v>505</v>
-      </c>
+      <c r="F53" s="10"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
@@ -3428,9 +3377,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="10"/>
-      <c r="F54" s="10" t="s">
-        <v>506</v>
-      </c>
+      <c r="F54" s="10"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
@@ -3446,9 +3393,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="10"/>
-      <c r="F55" s="10" t="s">
-        <v>507</v>
-      </c>
+      <c r="F55" s="10"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
@@ -3464,9 +3409,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="10"/>
-      <c r="F56" s="10" t="s">
-        <v>508</v>
-      </c>
+      <c r="F56" s="10"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
@@ -3482,9 +3425,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="10"/>
-      <c r="F57" s="10" t="s">
-        <v>510</v>
-      </c>
+      <c r="F57" s="10"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
@@ -3500,9 +3441,7 @@
         <v>3</v>
       </c>
       <c r="E58" s="10"/>
-      <c r="F58" s="10" t="s">
-        <v>511</v>
-      </c>
+      <c r="F58" s="10"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
@@ -3518,9 +3457,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="10"/>
-      <c r="F59" s="10" t="s">
-        <v>512</v>
-      </c>
+      <c r="F59" s="10"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
@@ -3536,9 +3473,7 @@
         <v>3</v>
       </c>
       <c r="E60" s="10"/>
-      <c r="F60" s="10" t="s">
-        <v>513</v>
-      </c>
+      <c r="F60" s="10"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
@@ -3554,9 +3489,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="10"/>
-      <c r="F61" s="10" t="s">
-        <v>514</v>
-      </c>
+      <c r="F61" s="10"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
@@ -3572,9 +3505,7 @@
         <v>3</v>
       </c>
       <c r="E62" s="10"/>
-      <c r="F62" s="10" t="s">
-        <v>517</v>
-      </c>
+      <c r="F62" s="10"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
@@ -3590,9 +3521,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="10"/>
-      <c r="F63" s="10" t="s">
-        <v>518</v>
-      </c>
+      <c r="F63" s="10"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
@@ -3608,9 +3537,7 @@
         <v>3</v>
       </c>
       <c r="E64" s="10"/>
-      <c r="F64" s="10" t="s">
-        <v>519</v>
-      </c>
+      <c r="F64" s="10"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
@@ -3626,9 +3553,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="10"/>
-      <c r="F65" s="10" t="s">
-        <v>520</v>
-      </c>
+      <c r="F65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
@@ -3644,9 +3569,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="10"/>
-      <c r="F66" s="10" t="s">
-        <v>521</v>
-      </c>
+      <c r="F66" s="10"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
@@ -3662,9 +3585,7 @@
         <v>3</v>
       </c>
       <c r="E67" s="10"/>
-      <c r="F67" s="10" t="s">
-        <v>522</v>
-      </c>
+      <c r="F67" s="10"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
@@ -3680,9 +3601,7 @@
         <v>3</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="10" t="s">
-        <v>523</v>
-      </c>
+      <c r="F68" s="10"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
@@ -3698,9 +3617,7 @@
         <v>3</v>
       </c>
       <c r="E69" s="10"/>
-      <c r="F69" s="10" t="s">
-        <v>524</v>
-      </c>
+      <c r="F69" s="10"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
@@ -3716,9 +3633,7 @@
         <v>3</v>
       </c>
       <c r="E70" s="10"/>
-      <c r="F70" s="10" t="s">
-        <v>525</v>
-      </c>
+      <c r="F70" s="10"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
@@ -3734,9 +3649,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="10"/>
-      <c r="F71" s="10" t="s">
-        <v>526</v>
-      </c>
+      <c r="F71" s="10"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
@@ -3752,9 +3665,7 @@
         <v>3</v>
       </c>
       <c r="E72" s="10"/>
-      <c r="F72" s="10" t="s">
-        <v>527</v>
-      </c>
+      <c r="F72" s="10"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
@@ -3770,9 +3681,7 @@
         <v>3</v>
       </c>
       <c r="E73" s="10"/>
-      <c r="F73" s="10" t="s">
-        <v>528</v>
-      </c>
+      <c r="F73" s="10"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
@@ -3788,9 +3697,7 @@
         <v>3</v>
       </c>
       <c r="E74" s="10"/>
-      <c r="F74" s="10" t="s">
-        <v>529</v>
-      </c>
+      <c r="F74" s="10"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
@@ -3806,9 +3713,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="10"/>
-      <c r="F75" s="10" t="s">
-        <v>530</v>
-      </c>
+      <c r="F75" s="10"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
@@ -3824,9 +3729,7 @@
         <v>3</v>
       </c>
       <c r="E76" s="10"/>
-      <c r="F76" s="10" t="s">
-        <v>531</v>
-      </c>
+      <c r="F76" s="10"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
@@ -3842,9 +3745,7 @@
         <v>3</v>
       </c>
       <c r="E77" s="10"/>
-      <c r="F77" s="10" t="s">
-        <v>532</v>
-      </c>
+      <c r="F77" s="10"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
@@ -3860,9 +3761,7 @@
         <v>3</v>
       </c>
       <c r="E78" s="10"/>
-      <c r="F78" s="10" t="s">
-        <v>533</v>
-      </c>
+      <c r="F78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
@@ -3878,9 +3777,7 @@
         <v>3</v>
       </c>
       <c r="E79" s="10"/>
-      <c r="F79" s="10" t="s">
-        <v>534</v>
-      </c>
+      <c r="F79" s="10"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
@@ -3896,9 +3793,7 @@
         <v>3</v>
       </c>
       <c r="E80" s="10"/>
-      <c r="F80" s="10" t="s">
-        <v>535</v>
-      </c>
+      <c r="F80" s="10"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
@@ -3914,9 +3809,7 @@
         <v>3</v>
       </c>
       <c r="E81" s="10"/>
-      <c r="F81" s="10" t="s">
-        <v>536</v>
-      </c>
+      <c r="F81" s="10"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
@@ -3932,9 +3825,7 @@
         <v>3</v>
       </c>
       <c r="E82" s="10"/>
-      <c r="F82" s="10" t="s">
-        <v>537</v>
-      </c>
+      <c r="F82" s="10"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
@@ -3950,9 +3841,7 @@
         <v>3</v>
       </c>
       <c r="E83" s="10"/>
-      <c r="F83" s="10" t="s">
-        <v>538</v>
-      </c>
+      <c r="F83" s="10"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
@@ -3968,9 +3857,7 @@
         <v>3</v>
       </c>
       <c r="E84" s="10"/>
-      <c r="F84" s="10" t="s">
-        <v>539</v>
-      </c>
+      <c r="F84" s="10"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
@@ -3986,9 +3873,7 @@
         <v>3</v>
       </c>
       <c r="E85" s="10"/>
-      <c r="F85" s="10" t="s">
-        <v>540</v>
-      </c>
+      <c r="F85" s="10"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
@@ -4004,9 +3889,7 @@
         <v>3</v>
       </c>
       <c r="E86" s="10"/>
-      <c r="F86" s="10" t="s">
-        <v>541</v>
-      </c>
+      <c r="F86" s="10"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
@@ -4022,9 +3905,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="10"/>
-      <c r="F87" s="10" t="s">
-        <v>542</v>
-      </c>
+      <c r="F87" s="10"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
@@ -4040,9 +3921,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="10"/>
-      <c r="F88" s="10" t="s">
-        <v>543</v>
-      </c>
+      <c r="F88" s="10"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
@@ -4058,9 +3937,7 @@
         <v>3</v>
       </c>
       <c r="E89" s="10"/>
-      <c r="F89" s="10" t="s">
-        <v>544</v>
-      </c>
+      <c r="F89" s="10"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
@@ -4076,9 +3953,7 @@
         <v>3</v>
       </c>
       <c r="E90" s="10"/>
-      <c r="F90" s="10" t="s">
-        <v>545</v>
-      </c>
+      <c r="F90" s="10"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
@@ -4094,9 +3969,7 @@
         <v>3</v>
       </c>
       <c r="E91" s="10"/>
-      <c r="F91" s="10" t="s">
-        <v>546</v>
-      </c>
+      <c r="F91" s="10"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
@@ -4112,9 +3985,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="10"/>
-      <c r="F92" s="10" t="s">
-        <v>547</v>
-      </c>
+      <c r="F92" s="10"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
@@ -4130,9 +4001,7 @@
         <v>3</v>
       </c>
       <c r="E93" s="10"/>
-      <c r="F93" s="10" t="s">
-        <v>548</v>
-      </c>
+      <c r="F93" s="10"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
@@ -4148,9 +4017,7 @@
         <v>3</v>
       </c>
       <c r="E94" s="10"/>
-      <c r="F94" s="10" t="s">
-        <v>549</v>
-      </c>
+      <c r="F94" s="10"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
@@ -4166,9 +4033,7 @@
         <v>3</v>
       </c>
       <c r="E95" s="10"/>
-      <c r="F95" s="10" t="s">
-        <v>550</v>
-      </c>
+      <c r="F95" s="10"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
@@ -4184,9 +4049,7 @@
         <v>3</v>
       </c>
       <c r="E96" s="10"/>
-      <c r="F96" s="10" t="s">
-        <v>551</v>
-      </c>
+      <c r="F96" s="10"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
@@ -4202,9 +4065,7 @@
         <v>3</v>
       </c>
       <c r="E97" s="10"/>
-      <c r="F97" s="10" t="s">
-        <v>552</v>
-      </c>
+      <c r="F97" s="10"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
@@ -4220,9 +4081,7 @@
         <v>3</v>
       </c>
       <c r="E98" s="10"/>
-      <c r="F98" s="10" t="s">
-        <v>553</v>
-      </c>
+      <c r="F98" s="10"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
@@ -4238,9 +4097,7 @@
         <v>3</v>
       </c>
       <c r="E99" s="10"/>
-      <c r="F99" s="10" t="s">
-        <v>554</v>
-      </c>
+      <c r="F99" s="10"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
@@ -4256,9 +4113,7 @@
         <v>3</v>
       </c>
       <c r="E100" s="10"/>
-      <c r="F100" s="10" t="s">
-        <v>555</v>
-      </c>
+      <c r="F100" s="10"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
@@ -4274,9 +4129,7 @@
         <v>3</v>
       </c>
       <c r="E101" s="10"/>
-      <c r="F101" s="10" t="s">
-        <v>556</v>
-      </c>
+      <c r="F101" s="10"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
@@ -4292,9 +4145,7 @@
         <v>3</v>
       </c>
       <c r="E102" s="10"/>
-      <c r="F102" s="10" t="s">
-        <v>557</v>
-      </c>
+      <c r="F102" s="10"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
@@ -4310,9 +4161,7 @@
         <v>3</v>
       </c>
       <c r="E103" s="10"/>
-      <c r="F103" s="10" t="s">
-        <v>558</v>
-      </c>
+      <c r="F103" s="10"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
@@ -4328,9 +4177,7 @@
         <v>3</v>
       </c>
       <c r="E104" s="10"/>
-      <c r="F104" s="10" t="s">
-        <v>559</v>
-      </c>
+      <c r="F104" s="10"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
@@ -4346,9 +4193,7 @@
         <v>3</v>
       </c>
       <c r="E105" s="10"/>
-      <c r="F105" s="10" t="s">
-        <v>560</v>
-      </c>
+      <c r="F105" s="10"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
@@ -4364,9 +4209,7 @@
         <v>3</v>
       </c>
       <c r="E106" s="10"/>
-      <c r="F106" s="10" t="s">
-        <v>561</v>
-      </c>
+      <c r="F106" s="10"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
@@ -4382,9 +4225,7 @@
         <v>3</v>
       </c>
       <c r="E107" s="10"/>
-      <c r="F107" s="10" t="s">
-        <v>562</v>
-      </c>
+      <c r="F107" s="10"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
@@ -4400,9 +4241,7 @@
         <v>3</v>
       </c>
       <c r="E108" s="10"/>
-      <c r="F108" s="10" t="s">
-        <v>563</v>
-      </c>
+      <c r="F108" s="10"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
@@ -4418,9 +4257,7 @@
         <v>3</v>
       </c>
       <c r="E109" s="10"/>
-      <c r="F109" s="10" t="s">
-        <v>564</v>
-      </c>
+      <c r="F109" s="10"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
@@ -5073,7 +4910,7 @@
         <v>166</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E150" s="14" t="s">
         <v>165</v>
@@ -5091,7 +4928,7 @@
         <v>166</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>165</v>
@@ -5109,7 +4946,7 @@
         <v>166</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>165</v>
@@ -5127,7 +4964,7 @@
         <v>166</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>165</v>
@@ -5145,7 +4982,7 @@
         <v>166</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E154" s="32" t="s">
         <v>397</v>
@@ -5163,7 +5000,7 @@
         <v>166</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>165</v>
@@ -5181,7 +5018,7 @@
         <v>166</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E156" s="14" t="s">
         <v>165</v>
@@ -5199,7 +5036,7 @@
         <v>166</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>165</v>
@@ -5217,7 +5054,7 @@
         <v>166</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>165</v>
@@ -5235,7 +5072,7 @@
         <v>166</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>165</v>
@@ -9032,9 +8869,7 @@
       <c r="C396" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D396" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D396" s="3"/>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
     </row>
@@ -9048,9 +8883,7 @@
       <c r="C397" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D397" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D397" s="3"/>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
     </row>
@@ -9064,9 +8897,7 @@
       <c r="C398" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D398" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D398" s="3"/>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
     </row>
@@ -9080,9 +8911,7 @@
       <c r="C399" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D399" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D399" s="3"/>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
     </row>
@@ -9096,9 +8925,7 @@
       <c r="C400" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D400" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D400" s="3"/>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
     </row>
@@ -9112,9 +8939,7 @@
       <c r="C401" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D401" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D401" s="3"/>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
     </row>
@@ -9128,9 +8953,7 @@
       <c r="C402" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D402" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D402" s="3"/>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
     </row>
@@ -9144,9 +8967,7 @@
       <c r="C403" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D403" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D403" s="3"/>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
     </row>
@@ -9160,9 +8981,7 @@
       <c r="C404" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D404" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D404" s="3"/>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
     </row>
@@ -9208,9 +9027,7 @@
       <c r="C407" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D407" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D407" s="3"/>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
     </row>
@@ -9304,9 +9121,7 @@
       <c r="C413" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D413" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D413" s="3"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
     </row>
@@ -9320,9 +9135,7 @@
       <c r="C414" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D414" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D414" s="3"/>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
     </row>
@@ -9352,9 +9165,7 @@
       <c r="C416" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D416" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D416" s="3"/>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
     </row>
@@ -9368,9 +9179,7 @@
       <c r="C417" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D417" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D417" s="3"/>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
     </row>
@@ -9432,9 +9241,7 @@
       <c r="C421" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D421" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D421" s="3"/>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
     </row>
@@ -9448,9 +9255,7 @@
       <c r="C422" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D422" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D422" s="3"/>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
     </row>
@@ -9496,9 +9301,7 @@
       <c r="C425" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D425" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D425" s="3"/>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
     </row>
@@ -9560,9 +9363,7 @@
       <c r="C429" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D429" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D429" s="3"/>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
     </row>
@@ -9576,9 +9377,7 @@
       <c r="C430" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D430" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D430" s="3"/>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
     </row>
@@ -9656,9 +9455,7 @@
       <c r="C435" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D435" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D435" s="3"/>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
     </row>
@@ -11250,9 +11047,7 @@
       <c r="C535" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="D535" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="D535" s="3"/>
       <c r="E535" s="10"/>
       <c r="F535" s="10"/>
     </row>

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E649D0-3499-4612-A279-B95DBFE16307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EC3C6F-A114-4C16-A7F3-07A5FE3B8A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="677">
   <si>
     <t>STT</t>
   </si>
@@ -1729,6 +1729,336 @@
   </si>
   <si>
     <t>Lỗi, Đã trả lại gia công</t>
+  </si>
+  <si>
+    <t>VNET860879084173968</t>
+  </si>
+  <si>
+    <t>VNET860879084178868</t>
+  </si>
+  <si>
+    <t>VNET860879084175948</t>
+  </si>
+  <si>
+    <t>VNET860879084174305</t>
+  </si>
+  <si>
+    <t>VNET860879084175799</t>
+  </si>
+  <si>
+    <t>VNET860879084176755</t>
+  </si>
+  <si>
+    <t>VNET860879084177175</t>
+  </si>
+  <si>
+    <t>VNET860879084176466</t>
+  </si>
+  <si>
+    <t>VNET860879084175906</t>
+  </si>
+  <si>
+    <t>VNET860879084176250</t>
+  </si>
+  <si>
+    <t>VNET860879084182068</t>
+  </si>
+  <si>
+    <t>VNET860879084181565</t>
+  </si>
+  <si>
+    <t>VNET860879084180328</t>
+  </si>
+  <si>
+    <t>VNET860879084177589</t>
+  </si>
+  <si>
+    <t>VNET860879084174024</t>
+  </si>
+  <si>
+    <t>VNET860879084176185</t>
+  </si>
+  <si>
+    <t>VNET860879084177233</t>
+  </si>
+  <si>
+    <t>VNET860879084175070</t>
+  </si>
+  <si>
+    <t>VNET860879084181060</t>
+  </si>
+  <si>
+    <t>VNET860879084177332</t>
+  </si>
+  <si>
+    <t>VNET860879084174446</t>
+  </si>
+  <si>
+    <t>VNET860879084179510</t>
+  </si>
+  <si>
+    <t>VNET860879084175260</t>
+  </si>
+  <si>
+    <t>VNET860879084174172</t>
+  </si>
+  <si>
+    <t>VNET860879084176029</t>
+  </si>
+  <si>
+    <t>VNET860879084183231</t>
+  </si>
+  <si>
+    <t>VNET860879084174784</t>
+  </si>
+  <si>
+    <t>VNET860879084176813</t>
+  </si>
+  <si>
+    <t>VNET860879084175872</t>
+  </si>
+  <si>
+    <t>VNET860879084179106</t>
+  </si>
+  <si>
+    <t>VNET860879084180625</t>
+  </si>
+  <si>
+    <t>VNET860879084173992</t>
+  </si>
+  <si>
+    <t>VNET860879084180039</t>
+  </si>
+  <si>
+    <t>VNET860879084180997</t>
+  </si>
+  <si>
+    <t>VNET860879084177308</t>
+  </si>
+  <si>
+    <t>VNET860879084179064</t>
+  </si>
+  <si>
+    <t>VNET860879084176458</t>
+  </si>
+  <si>
+    <t>VNET860879084178801</t>
+  </si>
+  <si>
+    <t>VNET860879084180344</t>
+  </si>
+  <si>
+    <t>VNET860879084178298</t>
+  </si>
+  <si>
+    <t>VNET860879084182415</t>
+  </si>
+  <si>
+    <t>VNET860879084177373</t>
+  </si>
+  <si>
+    <t>VNET860879084176904</t>
+  </si>
+  <si>
+    <t>VNET860879084176177</t>
+  </si>
+  <si>
+    <t>VNET860879084176763</t>
+  </si>
+  <si>
+    <t>VNET860879084179122</t>
+  </si>
+  <si>
+    <t>VNET860879084174750</t>
+  </si>
+  <si>
+    <t>VNET860879084175021</t>
+  </si>
+  <si>
+    <t>VNET860879084174222</t>
+  </si>
+  <si>
+    <t>VNET860879084174271</t>
+  </si>
+  <si>
+    <t>VNET860879084180898</t>
+  </si>
+  <si>
+    <t>VNET860879084179163</t>
+  </si>
+  <si>
+    <t>VNET860879084174891</t>
+  </si>
+  <si>
+    <t>VNET860879084175518</t>
+  </si>
+  <si>
+    <t>VNET860879084179379</t>
+  </si>
+  <si>
+    <t>VNET860879084181656</t>
+  </si>
+  <si>
+    <t>VNET860879084175880</t>
+  </si>
+  <si>
+    <t>VNET860879084181227</t>
+  </si>
+  <si>
+    <t>VNET860879084176326</t>
+  </si>
+  <si>
+    <t>VNET860879084182795</t>
+  </si>
+  <si>
+    <t>VNET860879084179841</t>
+  </si>
+  <si>
+    <t>VNET860879084174354</t>
+  </si>
+  <si>
+    <t>VNET860879084176425</t>
+  </si>
+  <si>
+    <t>VNET860879084180765</t>
+  </si>
+  <si>
+    <t>VNET860879084181490</t>
+  </si>
+  <si>
+    <t>VNET860879084179213</t>
+  </si>
+  <si>
+    <t>VNET860879084177225</t>
+  </si>
+  <si>
+    <t>VNET860879084176805</t>
+  </si>
+  <si>
+    <t>VNET860879084178751</t>
+  </si>
+  <si>
+    <t>VNET860879084181847</t>
+  </si>
+  <si>
+    <t>VNET860879084182829</t>
+  </si>
+  <si>
+    <t>VNET860879084181805</t>
+  </si>
+  <si>
+    <t>VNET860879084176896</t>
+  </si>
+  <si>
+    <t>VNET860879084181979</t>
+  </si>
+  <si>
+    <t>VNET860879084179791</t>
+  </si>
+  <si>
+    <t>VNET860879084174990</t>
+  </si>
+  <si>
+    <t>VNET860879084174230</t>
+  </si>
+  <si>
+    <t>VNET860879084180575</t>
+  </si>
+  <si>
+    <t>VNET860879084174123</t>
+  </si>
+  <si>
+    <t>VNET860879084181417</t>
+  </si>
+  <si>
+    <t>VNET860879084180518</t>
+  </si>
+  <si>
+    <t>VNET860879084177126</t>
+  </si>
+  <si>
+    <t>VNET860879084181292</t>
+  </si>
+  <si>
+    <t>VNET860879084183488</t>
+  </si>
+  <si>
+    <t>VNET860879084181409</t>
+  </si>
+  <si>
+    <t>VNET860879084182746</t>
+  </si>
+  <si>
+    <t>VNET860879084178470</t>
+  </si>
+  <si>
+    <t>VNET860879084182811</t>
+  </si>
+  <si>
+    <t>VNET860879084183074</t>
+  </si>
+  <si>
+    <t>VNET860879084178124</t>
+  </si>
+  <si>
+    <t>VNET860879084176227</t>
+  </si>
+  <si>
+    <t>VNET860879084174099</t>
+  </si>
+  <si>
+    <t>VNET860879084180559</t>
+  </si>
+  <si>
+    <t>VNET860879084177076</t>
+  </si>
+  <si>
+    <t>VNET860879084183694</t>
+  </si>
+  <si>
+    <t>VNET860879084175914</t>
+  </si>
+  <si>
+    <t>VNET860879084180468</t>
+  </si>
+  <si>
+    <t>VNET860879084179270</t>
+  </si>
+  <si>
+    <t>VNET860879084183702</t>
+  </si>
+  <si>
+    <t>VNET860879084181920</t>
+  </si>
+  <si>
+    <t>VNET860879084183264</t>
+  </si>
+  <si>
+    <t>VNET860879084182308</t>
+  </si>
+  <si>
+    <t>VNET860879084179353</t>
+  </si>
+  <si>
+    <t>VNET860879084179973</t>
+  </si>
+  <si>
+    <t>VNET860879084181441</t>
+  </si>
+  <si>
+    <t>VNET860879084174156</t>
+  </si>
+  <si>
+    <t>VNET860879084174453</t>
+  </si>
+  <si>
+    <t>VNET860879084180542</t>
+  </si>
+  <si>
+    <t>VNET860879084174289</t>
+  </si>
+  <si>
+    <t>VNET860879084174164</t>
   </si>
 </sst>
 </file>
@@ -2372,7 +2702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:N1001"/>
+  <dimension ref="A1:S1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="8" customWidth="1"/>
@@ -2388,7 +2718,7 @@
     <col min="13" max="13" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2427,7 +2757,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2444,7 +2774,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="3">
         <f>COUNTIFS(B2:B1001,"*VNET*")</f>
-        <v>544</v>
+        <v>656</v>
       </c>
       <c r="H2" s="23">
         <f>COUNTIFS(D2:D1001,"Đã nhập kho")</f>
@@ -2468,13 +2798,14 @@
       </c>
       <c r="M2" s="31">
         <f>SUM(G2-(H2+J2+L2))</f>
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="N2" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S2" s="15"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2488,13 +2819,12 @@
         <v>3</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="15" t="s">
-        <v>554</v>
-      </c>
+      <c r="F3" s="10"/>
       <c r="G3" s="7"/>
       <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S3" s="15"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2508,12 +2838,11 @@
         <v>3</v>
       </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="15" t="s">
-        <v>448</v>
-      </c>
+      <c r="F4" s="10"/>
       <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S4" s="15"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2527,12 +2856,11 @@
         <v>3</v>
       </c>
       <c r="E5" s="10"/>
-      <c r="F5" s="15" t="s">
-        <v>439</v>
-      </c>
+      <c r="F5" s="10"/>
       <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S5" s="15"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2546,12 +2874,11 @@
         <v>3</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="15" t="s">
-        <v>440</v>
-      </c>
+      <c r="F6" s="10"/>
       <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S6" s="15"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2565,12 +2892,11 @@
         <v>3</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="15" t="s">
-        <v>422</v>
-      </c>
+      <c r="F7" s="10"/>
       <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S7" s="15"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2584,12 +2910,11 @@
         <v>3</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="15" t="s">
-        <v>431</v>
-      </c>
+      <c r="F8" s="10"/>
       <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2603,12 +2928,11 @@
         <v>3</v>
       </c>
       <c r="E9" s="10"/>
-      <c r="F9" s="15" t="s">
-        <v>432</v>
-      </c>
+      <c r="F9" s="10"/>
       <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2622,12 +2946,11 @@
         <v>3</v>
       </c>
       <c r="E10" s="10"/>
-      <c r="F10" s="15" t="s">
-        <v>434</v>
-      </c>
+      <c r="F10" s="10"/>
       <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S10" s="15"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2641,12 +2964,11 @@
         <v>3</v>
       </c>
       <c r="E11" s="10"/>
-      <c r="F11" s="15" t="s">
-        <v>425</v>
-      </c>
+      <c r="F11" s="10"/>
       <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S11" s="15"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2660,12 +2982,11 @@
         <v>3</v>
       </c>
       <c r="E12" s="10"/>
-      <c r="F12" s="15" t="s">
-        <v>420</v>
-      </c>
+      <c r="F12" s="10"/>
       <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2679,12 +3000,11 @@
         <v>3</v>
       </c>
       <c r="E13" s="10"/>
-      <c r="F13" s="15" t="s">
-        <v>418</v>
-      </c>
+      <c r="F13" s="10"/>
       <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S13" s="15"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2698,12 +3018,11 @@
         <v>3</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="15" t="s">
-        <v>419</v>
-      </c>
+      <c r="F14" s="10"/>
       <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S14" s="15"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2717,12 +3036,11 @@
         <v>3</v>
       </c>
       <c r="E15" s="10"/>
-      <c r="F15" s="15" t="s">
-        <v>417</v>
-      </c>
+      <c r="F15" s="10"/>
       <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="S15" s="15"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2736,12 +3054,11 @@
         <v>3</v>
       </c>
       <c r="E16" s="10"/>
-      <c r="F16" s="15" t="s">
-        <v>414</v>
-      </c>
+      <c r="F16" s="10"/>
       <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S16" s="15"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2755,12 +3072,11 @@
         <v>3</v>
       </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="15" t="s">
-        <v>443</v>
-      </c>
+      <c r="F17" s="10"/>
       <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S17" s="15"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2774,12 +3090,11 @@
         <v>3</v>
       </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="15" t="s">
-        <v>421</v>
-      </c>
+      <c r="F18" s="10"/>
       <c r="G18" s="16"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S18" s="15"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2793,12 +3108,11 @@
         <v>3</v>
       </c>
       <c r="E19" s="10"/>
-      <c r="F19" s="15" t="s">
-        <v>453</v>
-      </c>
+      <c r="F19" s="10"/>
       <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S19" s="15"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2812,12 +3126,11 @@
         <v>3</v>
       </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="15" t="s">
-        <v>415</v>
-      </c>
+      <c r="F20" s="10"/>
       <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S20" s="15"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2831,12 +3144,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="10"/>
-      <c r="F21" s="15" t="s">
-        <v>416</v>
-      </c>
+      <c r="F21" s="10"/>
       <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S21" s="18"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -2850,12 +3162,11 @@
         <v>3</v>
       </c>
       <c r="E22" s="10"/>
-      <c r="F22" s="18" t="s">
-        <v>435</v>
-      </c>
+      <c r="F22" s="10"/>
       <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="S22" s="18"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2869,12 +3180,10 @@
         <v>3</v>
       </c>
       <c r="E23" s="10"/>
-      <c r="F23" s="18" t="s">
-        <v>447</v>
-      </c>
+      <c r="F23" s="10"/>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -2891,7 +3200,7 @@
       <c r="F24" s="18"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -2908,7 +3217,7 @@
       <c r="F25" s="18"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -2925,7 +3234,7 @@
       <c r="F26" s="18"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -2942,7 +3251,7 @@
       <c r="F27" s="18"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -2959,7 +3268,7 @@
       <c r="F28" s="18"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -2976,7 +3285,7 @@
       <c r="F29" s="18"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -2993,7 +3302,7 @@
       <c r="F30" s="18"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3010,7 +3319,7 @@
       <c r="F31" s="18"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -11215,7 +11524,9 @@
       <c r="A546" s="3">
         <v>545</v>
       </c>
-      <c r="B546" s="4"/>
+      <c r="B546" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="C546" s="4"/>
       <c r="D546" s="3"/>
       <c r="E546" s="10"/>
@@ -11225,7 +11536,9 @@
       <c r="A547" s="3">
         <v>546</v>
       </c>
-      <c r="B547" s="4"/>
+      <c r="B547" s="4" t="s">
+        <v>568</v>
+      </c>
       <c r="C547" s="4"/>
       <c r="D547" s="3"/>
       <c r="E547" s="10"/>
@@ -11235,7 +11548,9 @@
       <c r="A548" s="3">
         <v>547</v>
       </c>
-      <c r="B548" s="4"/>
+      <c r="B548" s="4" t="s">
+        <v>569</v>
+      </c>
       <c r="C548" s="4"/>
       <c r="D548" s="3"/>
       <c r="E548" s="10"/>
@@ -11245,7 +11560,9 @@
       <c r="A549" s="3">
         <v>548</v>
       </c>
-      <c r="B549" s="4"/>
+      <c r="B549" s="4" t="s">
+        <v>570</v>
+      </c>
       <c r="C549" s="4"/>
       <c r="D549" s="3"/>
       <c r="E549" s="10"/>
@@ -11255,7 +11572,9 @@
       <c r="A550" s="3">
         <v>549</v>
       </c>
-      <c r="B550" s="4"/>
+      <c r="B550" s="4" t="s">
+        <v>571</v>
+      </c>
       <c r="C550" s="4"/>
       <c r="D550" s="3"/>
       <c r="E550" s="10"/>
@@ -11265,7 +11584,9 @@
       <c r="A551" s="3">
         <v>550</v>
       </c>
-      <c r="B551" s="4"/>
+      <c r="B551" s="4" t="s">
+        <v>572</v>
+      </c>
       <c r="C551" s="4"/>
       <c r="D551" s="3"/>
       <c r="E551" s="10"/>
@@ -11275,7 +11596,9 @@
       <c r="A552" s="3">
         <v>551</v>
       </c>
-      <c r="B552" s="4"/>
+      <c r="B552" s="4" t="s">
+        <v>573</v>
+      </c>
       <c r="C552" s="4"/>
       <c r="D552" s="3"/>
       <c r="E552" s="10"/>
@@ -11285,7 +11608,9 @@
       <c r="A553" s="3">
         <v>552</v>
       </c>
-      <c r="B553" s="4"/>
+      <c r="B553" s="4" t="s">
+        <v>574</v>
+      </c>
       <c r="C553" s="4"/>
       <c r="D553" s="3"/>
       <c r="E553" s="10"/>
@@ -11295,7 +11620,9 @@
       <c r="A554" s="3">
         <v>553</v>
       </c>
-      <c r="B554" s="4"/>
+      <c r="B554" s="4" t="s">
+        <v>575</v>
+      </c>
       <c r="C554" s="4"/>
       <c r="D554" s="3"/>
       <c r="E554" s="10"/>
@@ -11305,7 +11632,9 @@
       <c r="A555" s="3">
         <v>554</v>
       </c>
-      <c r="B555" s="4"/>
+      <c r="B555" s="4" t="s">
+        <v>576</v>
+      </c>
       <c r="C555" s="4"/>
       <c r="D555" s="3"/>
       <c r="E555" s="10"/>
@@ -11315,7 +11644,9 @@
       <c r="A556" s="3">
         <v>555</v>
       </c>
-      <c r="B556" s="4"/>
+      <c r="B556" s="4" t="s">
+        <v>577</v>
+      </c>
       <c r="C556" s="4"/>
       <c r="D556" s="3"/>
       <c r="E556" s="10"/>
@@ -11325,7 +11656,9 @@
       <c r="A557" s="3">
         <v>556</v>
       </c>
-      <c r="B557" s="4"/>
+      <c r="B557" s="4" t="s">
+        <v>578</v>
+      </c>
       <c r="C557" s="4"/>
       <c r="D557" s="3"/>
       <c r="E557" s="10"/>
@@ -11335,7 +11668,9 @@
       <c r="A558" s="3">
         <v>557</v>
       </c>
-      <c r="B558" s="4"/>
+      <c r="B558" s="4" t="s">
+        <v>579</v>
+      </c>
       <c r="C558" s="4"/>
       <c r="D558" s="3"/>
       <c r="E558" s="10"/>
@@ -11345,7 +11680,9 @@
       <c r="A559" s="3">
         <v>558</v>
       </c>
-      <c r="B559" s="4"/>
+      <c r="B559" s="4" t="s">
+        <v>580</v>
+      </c>
       <c r="C559" s="4"/>
       <c r="D559" s="3"/>
       <c r="E559" s="10"/>
@@ -11355,7 +11692,9 @@
       <c r="A560" s="3">
         <v>559</v>
       </c>
-      <c r="B560" s="4"/>
+      <c r="B560" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="C560" s="4"/>
       <c r="D560" s="3"/>
       <c r="E560" s="10"/>
@@ -11365,7 +11704,9 @@
       <c r="A561" s="3">
         <v>560</v>
       </c>
-      <c r="B561" s="4"/>
+      <c r="B561" s="4" t="s">
+        <v>582</v>
+      </c>
       <c r="C561" s="4"/>
       <c r="D561" s="3"/>
       <c r="E561" s="10"/>
@@ -11375,7 +11716,9 @@
       <c r="A562" s="3">
         <v>561</v>
       </c>
-      <c r="B562" s="4"/>
+      <c r="B562" s="4" t="s">
+        <v>583</v>
+      </c>
       <c r="C562" s="4"/>
       <c r="D562" s="3"/>
       <c r="E562" s="10"/>
@@ -11385,7 +11728,9 @@
       <c r="A563" s="3">
         <v>562</v>
       </c>
-      <c r="B563" s="4"/>
+      <c r="B563" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="C563" s="4"/>
       <c r="D563" s="3"/>
       <c r="E563" s="10"/>
@@ -11395,7 +11740,9 @@
       <c r="A564" s="3">
         <v>563</v>
       </c>
-      <c r="B564" s="4"/>
+      <c r="B564" s="4" t="s">
+        <v>585</v>
+      </c>
       <c r="C564" s="4"/>
       <c r="D564" s="3"/>
       <c r="E564" s="10"/>
@@ -11405,7 +11752,9 @@
       <c r="A565" s="3">
         <v>564</v>
       </c>
-      <c r="B565" s="4"/>
+      <c r="B565" s="4" t="s">
+        <v>586</v>
+      </c>
       <c r="C565" s="4"/>
       <c r="D565" s="3"/>
       <c r="E565" s="10"/>
@@ -11415,7 +11764,9 @@
       <c r="A566" s="3">
         <v>565</v>
       </c>
-      <c r="B566" s="4"/>
+      <c r="B566" s="4" t="s">
+        <v>587</v>
+      </c>
       <c r="C566" s="4"/>
       <c r="D566" s="3"/>
       <c r="E566" s="10"/>
@@ -11425,7 +11776,9 @@
       <c r="A567" s="3">
         <v>566</v>
       </c>
-      <c r="B567" s="4"/>
+      <c r="B567" s="4" t="s">
+        <v>588</v>
+      </c>
       <c r="C567" s="4"/>
       <c r="D567" s="3"/>
       <c r="E567" s="10"/>
@@ -11435,7 +11788,9 @@
       <c r="A568" s="3">
         <v>567</v>
       </c>
-      <c r="B568" s="4"/>
+      <c r="B568" s="4" t="s">
+        <v>589</v>
+      </c>
       <c r="C568" s="4"/>
       <c r="D568" s="3"/>
       <c r="E568" s="10"/>
@@ -11445,7 +11800,9 @@
       <c r="A569" s="3">
         <v>568</v>
       </c>
-      <c r="B569" s="4"/>
+      <c r="B569" s="4" t="s">
+        <v>590</v>
+      </c>
       <c r="C569" s="4"/>
       <c r="D569" s="3"/>
       <c r="E569" s="10"/>
@@ -11455,7 +11812,9 @@
       <c r="A570" s="3">
         <v>569</v>
       </c>
-      <c r="B570" s="4"/>
+      <c r="B570" s="4" t="s">
+        <v>591</v>
+      </c>
       <c r="C570" s="4"/>
       <c r="D570" s="3"/>
       <c r="E570" s="10"/>
@@ -11465,7 +11824,9 @@
       <c r="A571" s="3">
         <v>570</v>
       </c>
-      <c r="B571" s="4"/>
+      <c r="B571" s="4" t="s">
+        <v>592</v>
+      </c>
       <c r="C571" s="4"/>
       <c r="D571" s="3"/>
       <c r="E571" s="10"/>
@@ -11475,7 +11836,9 @@
       <c r="A572" s="3">
         <v>571</v>
       </c>
-      <c r="B572" s="4"/>
+      <c r="B572" s="4" t="s">
+        <v>593</v>
+      </c>
       <c r="C572" s="4"/>
       <c r="D572" s="3"/>
       <c r="E572" s="10"/>
@@ -11485,7 +11848,9 @@
       <c r="A573" s="3">
         <v>572</v>
       </c>
-      <c r="B573" s="4"/>
+      <c r="B573" s="4" t="s">
+        <v>593</v>
+      </c>
       <c r="C573" s="4"/>
       <c r="D573" s="3"/>
       <c r="E573" s="10"/>
@@ -11495,7 +11860,9 @@
       <c r="A574" s="3">
         <v>573</v>
       </c>
-      <c r="B574" s="4"/>
+      <c r="B574" s="4" t="s">
+        <v>571</v>
+      </c>
       <c r="C574" s="4"/>
       <c r="D574" s="3"/>
       <c r="E574" s="10"/>
@@ -11505,7 +11872,9 @@
       <c r="A575" s="3">
         <v>574</v>
       </c>
-      <c r="B575" s="4"/>
+      <c r="B575" s="4" t="s">
+        <v>594</v>
+      </c>
       <c r="C575" s="4"/>
       <c r="D575" s="3"/>
       <c r="E575" s="10"/>
@@ -11515,7 +11884,9 @@
       <c r="A576" s="3">
         <v>575</v>
       </c>
-      <c r="B576" s="4"/>
+      <c r="B576" s="4" t="s">
+        <v>595</v>
+      </c>
       <c r="C576" s="4"/>
       <c r="D576" s="3"/>
       <c r="E576" s="10"/>
@@ -11525,7 +11896,9 @@
       <c r="A577" s="3">
         <v>576</v>
       </c>
-      <c r="B577" s="4"/>
+      <c r="B577" s="4" t="s">
+        <v>596</v>
+      </c>
       <c r="C577" s="4"/>
       <c r="D577" s="3"/>
       <c r="E577" s="10"/>
@@ -11535,7 +11908,9 @@
       <c r="A578" s="3">
         <v>577</v>
       </c>
-      <c r="B578" s="4"/>
+      <c r="B578" s="4" t="s">
+        <v>597</v>
+      </c>
       <c r="C578" s="4"/>
       <c r="D578" s="3"/>
       <c r="E578" s="10"/>
@@ -11545,7 +11920,9 @@
       <c r="A579" s="3">
         <v>578</v>
       </c>
-      <c r="B579" s="4"/>
+      <c r="B579" s="4" t="s">
+        <v>598</v>
+      </c>
       <c r="C579" s="4"/>
       <c r="D579" s="3"/>
       <c r="E579" s="10"/>
@@ -11555,7 +11932,9 @@
       <c r="A580" s="3">
         <v>579</v>
       </c>
-      <c r="B580" s="4"/>
+      <c r="B580" s="4" t="s">
+        <v>599</v>
+      </c>
       <c r="C580" s="4"/>
       <c r="D580" s="3"/>
       <c r="E580" s="10"/>
@@ -11565,7 +11944,9 @@
       <c r="A581" s="3">
         <v>580</v>
       </c>
-      <c r="B581" s="4"/>
+      <c r="B581" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="C581" s="4"/>
       <c r="D581" s="3"/>
       <c r="E581" s="10"/>
@@ -11575,7 +11956,9 @@
       <c r="A582" s="3">
         <v>581</v>
       </c>
-      <c r="B582" s="4"/>
+      <c r="B582" s="4" t="s">
+        <v>601</v>
+      </c>
       <c r="C582" s="4"/>
       <c r="D582" s="3"/>
       <c r="E582" s="10"/>
@@ -11585,7 +11968,9 @@
       <c r="A583" s="3">
         <v>582</v>
       </c>
-      <c r="B583" s="4"/>
+      <c r="B583" s="4" t="s">
+        <v>602</v>
+      </c>
       <c r="C583" s="4"/>
       <c r="D583" s="3"/>
       <c r="E583" s="10"/>
@@ -11595,7 +11980,9 @@
       <c r="A584" s="3">
         <v>583</v>
       </c>
-      <c r="B584" s="4"/>
+      <c r="B584" s="4" t="s">
+        <v>603</v>
+      </c>
       <c r="C584" s="4"/>
       <c r="D584" s="3"/>
       <c r="E584" s="10"/>
@@ -11605,7 +11992,9 @@
       <c r="A585" s="3">
         <v>584</v>
       </c>
-      <c r="B585" s="4"/>
+      <c r="B585" s="4" t="s">
+        <v>604</v>
+      </c>
       <c r="C585" s="4"/>
       <c r="D585" s="3"/>
       <c r="E585" s="10"/>
@@ -11615,7 +12004,9 @@
       <c r="A586" s="3">
         <v>585</v>
       </c>
-      <c r="B586" s="4"/>
+      <c r="B586" s="4" t="s">
+        <v>605</v>
+      </c>
       <c r="C586" s="4"/>
       <c r="D586" s="3"/>
       <c r="E586" s="10"/>
@@ -11625,7 +12016,9 @@
       <c r="A587" s="3">
         <v>586</v>
       </c>
-      <c r="B587" s="4"/>
+      <c r="B587" s="4" t="s">
+        <v>606</v>
+      </c>
       <c r="C587" s="4"/>
       <c r="D587" s="3"/>
       <c r="E587" s="10"/>
@@ -11635,7 +12028,9 @@
       <c r="A588" s="3">
         <v>587</v>
       </c>
-      <c r="B588" s="4"/>
+      <c r="B588" s="4" t="s">
+        <v>607</v>
+      </c>
       <c r="C588" s="4"/>
       <c r="D588" s="3"/>
       <c r="E588" s="10"/>
@@ -11645,7 +12040,9 @@
       <c r="A589" s="3">
         <v>588</v>
       </c>
-      <c r="B589" s="4"/>
+      <c r="B589" s="4" t="s">
+        <v>608</v>
+      </c>
       <c r="C589" s="4"/>
       <c r="D589" s="3"/>
       <c r="E589" s="10"/>
@@ -11655,7 +12052,9 @@
       <c r="A590" s="3">
         <v>589</v>
       </c>
-      <c r="B590" s="4"/>
+      <c r="B590" s="4" t="s">
+        <v>609</v>
+      </c>
       <c r="C590" s="4"/>
       <c r="D590" s="3"/>
       <c r="E590" s="10"/>
@@ -11665,7 +12064,9 @@
       <c r="A591" s="3">
         <v>590</v>
       </c>
-      <c r="B591" s="4"/>
+      <c r="B591" s="4" t="s">
+        <v>610</v>
+      </c>
       <c r="C591" s="4"/>
       <c r="D591" s="3"/>
       <c r="E591" s="10"/>
@@ -11675,7 +12076,9 @@
       <c r="A592" s="3">
         <v>591</v>
       </c>
-      <c r="B592" s="4"/>
+      <c r="B592" s="4" t="s">
+        <v>611</v>
+      </c>
       <c r="C592" s="4"/>
       <c r="D592" s="3"/>
       <c r="E592" s="10"/>
@@ -11685,7 +12088,9 @@
       <c r="A593" s="3">
         <v>592</v>
       </c>
-      <c r="B593" s="4"/>
+      <c r="B593" s="4" t="s">
+        <v>612</v>
+      </c>
       <c r="C593" s="4"/>
       <c r="D593" s="3"/>
       <c r="E593" s="10"/>
@@ -11695,7 +12100,9 @@
       <c r="A594" s="3">
         <v>593</v>
       </c>
-      <c r="B594" s="4"/>
+      <c r="B594" s="4" t="s">
+        <v>613</v>
+      </c>
       <c r="C594" s="4"/>
       <c r="D594" s="3"/>
       <c r="E594" s="10"/>
@@ -11705,7 +12112,9 @@
       <c r="A595" s="3">
         <v>594</v>
       </c>
-      <c r="B595" s="4"/>
+      <c r="B595" s="4" t="s">
+        <v>614</v>
+      </c>
       <c r="C595" s="4"/>
       <c r="D595" s="3"/>
       <c r="E595" s="10"/>
@@ -11715,7 +12124,9 @@
       <c r="A596" s="3">
         <v>595</v>
       </c>
-      <c r="B596" s="4"/>
+      <c r="B596" s="4" t="s">
+        <v>615</v>
+      </c>
       <c r="C596" s="4"/>
       <c r="D596" s="3"/>
       <c r="E596" s="10"/>
@@ -11725,7 +12136,9 @@
       <c r="A597" s="3">
         <v>596</v>
       </c>
-      <c r="B597" s="4"/>
+      <c r="B597" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="C597" s="4"/>
       <c r="D597" s="3"/>
       <c r="E597" s="10"/>
@@ -11735,7 +12148,9 @@
       <c r="A598" s="3">
         <v>597</v>
       </c>
-      <c r="B598" s="4"/>
+      <c r="B598" s="4" t="s">
+        <v>617</v>
+      </c>
       <c r="C598" s="4"/>
       <c r="D598" s="3"/>
       <c r="E598" s="10"/>
@@ -11745,7 +12160,9 @@
       <c r="A599" s="3">
         <v>598</v>
       </c>
-      <c r="B599" s="4"/>
+      <c r="B599" s="4" t="s">
+        <v>618</v>
+      </c>
       <c r="C599" s="4"/>
       <c r="D599" s="3"/>
       <c r="E599" s="10"/>
@@ -11755,7 +12172,9 @@
       <c r="A600" s="3">
         <v>599</v>
       </c>
-      <c r="B600" s="4"/>
+      <c r="B600" s="4" t="s">
+        <v>619</v>
+      </c>
       <c r="C600" s="4"/>
       <c r="D600" s="3"/>
       <c r="E600" s="10"/>
@@ -11765,7 +12184,9 @@
       <c r="A601" s="3">
         <v>600</v>
       </c>
-      <c r="B601" s="4"/>
+      <c r="B601" s="4" t="s">
+        <v>620</v>
+      </c>
       <c r="C601" s="4"/>
       <c r="D601" s="3"/>
       <c r="E601" s="10"/>
@@ -11775,7 +12196,9 @@
       <c r="A602" s="3">
         <v>601</v>
       </c>
-      <c r="B602" s="4"/>
+      <c r="B602" s="4" t="s">
+        <v>621</v>
+      </c>
       <c r="C602" s="4"/>
       <c r="D602" s="3"/>
       <c r="E602" s="10"/>
@@ -11785,7 +12208,9 @@
       <c r="A603" s="3">
         <v>602</v>
       </c>
-      <c r="B603" s="4"/>
+      <c r="B603" s="4" t="s">
+        <v>622</v>
+      </c>
       <c r="C603" s="4"/>
       <c r="D603" s="3"/>
       <c r="E603" s="10"/>
@@ -11795,7 +12220,9 @@
       <c r="A604" s="3">
         <v>603</v>
       </c>
-      <c r="B604" s="4"/>
+      <c r="B604" s="4" t="s">
+        <v>623</v>
+      </c>
       <c r="C604" s="4"/>
       <c r="D604" s="3"/>
       <c r="E604" s="10"/>
@@ -11805,7 +12232,9 @@
       <c r="A605" s="3">
         <v>604</v>
       </c>
-      <c r="B605" s="4"/>
+      <c r="B605" s="4" t="s">
+        <v>624</v>
+      </c>
       <c r="C605" s="4"/>
       <c r="D605" s="3"/>
       <c r="E605" s="10"/>
@@ -11815,7 +12244,9 @@
       <c r="A606" s="3">
         <v>605</v>
       </c>
-      <c r="B606" s="4"/>
+      <c r="B606" s="4" t="s">
+        <v>625</v>
+      </c>
       <c r="C606" s="4"/>
       <c r="D606" s="3"/>
       <c r="E606" s="10"/>
@@ -11825,7 +12256,9 @@
       <c r="A607" s="3">
         <v>606</v>
       </c>
-      <c r="B607" s="4"/>
+      <c r="B607" s="4" t="s">
+        <v>626</v>
+      </c>
       <c r="C607" s="4"/>
       <c r="D607" s="3"/>
       <c r="E607" s="10"/>
@@ -11835,7 +12268,9 @@
       <c r="A608" s="3">
         <v>607</v>
       </c>
-      <c r="B608" s="4"/>
+      <c r="B608" s="4" t="s">
+        <v>627</v>
+      </c>
       <c r="C608" s="4"/>
       <c r="D608" s="3"/>
       <c r="E608" s="10"/>
@@ -11845,7 +12280,9 @@
       <c r="A609" s="3">
         <v>608</v>
       </c>
-      <c r="B609" s="4"/>
+      <c r="B609" s="4" t="s">
+        <v>628</v>
+      </c>
       <c r="C609" s="4"/>
       <c r="D609" s="3"/>
       <c r="E609" s="10"/>
@@ -11855,7 +12292,9 @@
       <c r="A610" s="3">
         <v>609</v>
       </c>
-      <c r="B610" s="4"/>
+      <c r="B610" s="4" t="s">
+        <v>629</v>
+      </c>
       <c r="C610" s="4"/>
       <c r="D610" s="3"/>
       <c r="E610" s="10"/>
@@ -11865,7 +12304,9 @@
       <c r="A611" s="3">
         <v>610</v>
       </c>
-      <c r="B611" s="4"/>
+      <c r="B611" s="4" t="s">
+        <v>630</v>
+      </c>
       <c r="C611" s="4"/>
       <c r="D611" s="3"/>
       <c r="E611" s="10"/>
@@ -11875,7 +12316,9 @@
       <c r="A612" s="3">
         <v>611</v>
       </c>
-      <c r="B612" s="4"/>
+      <c r="B612" s="4" t="s">
+        <v>631</v>
+      </c>
       <c r="C612" s="4"/>
       <c r="D612" s="3"/>
       <c r="E612" s="10"/>
@@ -11885,7 +12328,9 @@
       <c r="A613" s="3">
         <v>612</v>
       </c>
-      <c r="B613" s="4"/>
+      <c r="B613" s="4" t="s">
+        <v>632</v>
+      </c>
       <c r="C613" s="4"/>
       <c r="D613" s="3"/>
       <c r="E613" s="10"/>
@@ -11895,7 +12340,9 @@
       <c r="A614" s="3">
         <v>613</v>
       </c>
-      <c r="B614" s="4"/>
+      <c r="B614" s="4" t="s">
+        <v>633</v>
+      </c>
       <c r="C614" s="4"/>
       <c r="D614" s="3"/>
       <c r="E614" s="10"/>
@@ -11905,7 +12352,9 @@
       <c r="A615" s="3">
         <v>614</v>
       </c>
-      <c r="B615" s="4"/>
+      <c r="B615" s="4" t="s">
+        <v>634</v>
+      </c>
       <c r="C615" s="4"/>
       <c r="D615" s="3"/>
       <c r="E615" s="10"/>
@@ -11915,7 +12364,9 @@
       <c r="A616" s="3">
         <v>615</v>
       </c>
-      <c r="B616" s="4"/>
+      <c r="B616" s="4" t="s">
+        <v>635</v>
+      </c>
       <c r="C616" s="4"/>
       <c r="D616" s="3"/>
       <c r="E616" s="10"/>
@@ -11925,7 +12376,9 @@
       <c r="A617" s="3">
         <v>616</v>
       </c>
-      <c r="B617" s="4"/>
+      <c r="B617" s="4" t="s">
+        <v>636</v>
+      </c>
       <c r="C617" s="4"/>
       <c r="D617" s="3"/>
       <c r="E617" s="10"/>
@@ -11935,7 +12388,9 @@
       <c r="A618" s="3">
         <v>617</v>
       </c>
-      <c r="B618" s="4"/>
+      <c r="B618" s="4" t="s">
+        <v>637</v>
+      </c>
       <c r="C618" s="4"/>
       <c r="D618" s="3"/>
       <c r="E618" s="10"/>
@@ -11945,7 +12400,9 @@
       <c r="A619" s="3">
         <v>618</v>
       </c>
-      <c r="B619" s="4"/>
+      <c r="B619" s="4" t="s">
+        <v>638</v>
+      </c>
       <c r="C619" s="4"/>
       <c r="D619" s="3"/>
       <c r="E619" s="10"/>
@@ -11955,7 +12412,9 @@
       <c r="A620" s="3">
         <v>619</v>
       </c>
-      <c r="B620" s="4"/>
+      <c r="B620" s="4" t="s">
+        <v>639</v>
+      </c>
       <c r="C620" s="4"/>
       <c r="D620" s="3"/>
       <c r="E620" s="10"/>
@@ -11965,7 +12424,9 @@
       <c r="A621" s="3">
         <v>620</v>
       </c>
-      <c r="B621" s="4"/>
+      <c r="B621" s="4" t="s">
+        <v>640</v>
+      </c>
       <c r="C621" s="4"/>
       <c r="D621" s="3"/>
       <c r="E621" s="10"/>
@@ -11975,7 +12436,9 @@
       <c r="A622" s="3">
         <v>621</v>
       </c>
-      <c r="B622" s="4"/>
+      <c r="B622" s="4" t="s">
+        <v>641</v>
+      </c>
       <c r="C622" s="4"/>
       <c r="D622" s="3"/>
       <c r="E622" s="10"/>
@@ -11985,7 +12448,9 @@
       <c r="A623" s="3">
         <v>622</v>
       </c>
-      <c r="B623" s="4"/>
+      <c r="B623" s="4" t="s">
+        <v>642</v>
+      </c>
       <c r="C623" s="4"/>
       <c r="D623" s="3"/>
       <c r="E623" s="10"/>
@@ -11995,7 +12460,9 @@
       <c r="A624" s="3">
         <v>623</v>
       </c>
-      <c r="B624" s="4"/>
+      <c r="B624" s="4" t="s">
+        <v>643</v>
+      </c>
       <c r="C624" s="4"/>
       <c r="D624" s="3"/>
       <c r="E624" s="10"/>
@@ -12005,7 +12472,9 @@
       <c r="A625" s="3">
         <v>624</v>
       </c>
-      <c r="B625" s="4"/>
+      <c r="B625" s="4" t="s">
+        <v>644</v>
+      </c>
       <c r="C625" s="4"/>
       <c r="D625" s="3"/>
       <c r="E625" s="10"/>
@@ -12015,7 +12484,9 @@
       <c r="A626" s="3">
         <v>625</v>
       </c>
-      <c r="B626" s="4"/>
+      <c r="B626" s="4" t="s">
+        <v>645</v>
+      </c>
       <c r="C626" s="4"/>
       <c r="D626" s="3"/>
       <c r="E626" s="10"/>
@@ -12025,7 +12496,9 @@
       <c r="A627" s="3">
         <v>626</v>
       </c>
-      <c r="B627" s="4"/>
+      <c r="B627" s="4" t="s">
+        <v>646</v>
+      </c>
       <c r="C627" s="4"/>
       <c r="D627" s="3"/>
       <c r="E627" s="10"/>
@@ -12035,7 +12508,9 @@
       <c r="A628" s="3">
         <v>627</v>
       </c>
-      <c r="B628" s="4"/>
+      <c r="B628" s="4" t="s">
+        <v>647</v>
+      </c>
       <c r="C628" s="4"/>
       <c r="D628" s="3"/>
       <c r="E628" s="10"/>
@@ -12045,7 +12520,9 @@
       <c r="A629" s="3">
         <v>628</v>
       </c>
-      <c r="B629" s="4"/>
+      <c r="B629" s="4" t="s">
+        <v>648</v>
+      </c>
       <c r="C629" s="4"/>
       <c r="D629" s="3"/>
       <c r="E629" s="10"/>
@@ -12055,7 +12532,9 @@
       <c r="A630" s="3">
         <v>629</v>
       </c>
-      <c r="B630" s="4"/>
+      <c r="B630" s="4" t="s">
+        <v>649</v>
+      </c>
       <c r="C630" s="4"/>
       <c r="D630" s="3"/>
       <c r="E630" s="10"/>
@@ -12065,7 +12544,9 @@
       <c r="A631" s="3">
         <v>630</v>
       </c>
-      <c r="B631" s="4"/>
+      <c r="B631" s="4" t="s">
+        <v>650</v>
+      </c>
       <c r="C631" s="4"/>
       <c r="D631" s="3"/>
       <c r="E631" s="10"/>
@@ -12075,7 +12556,9 @@
       <c r="A632" s="3">
         <v>631</v>
       </c>
-      <c r="B632" s="4"/>
+      <c r="B632" s="4" t="s">
+        <v>651</v>
+      </c>
       <c r="C632" s="4"/>
       <c r="D632" s="3"/>
       <c r="E632" s="10"/>
@@ -12085,7 +12568,9 @@
       <c r="A633" s="3">
         <v>632</v>
       </c>
-      <c r="B633" s="4"/>
+      <c r="B633" s="4" t="s">
+        <v>652</v>
+      </c>
       <c r="C633" s="4"/>
       <c r="D633" s="3"/>
       <c r="E633" s="10"/>
@@ -12095,7 +12580,9 @@
       <c r="A634" s="3">
         <v>633</v>
       </c>
-      <c r="B634" s="4"/>
+      <c r="B634" s="4" t="s">
+        <v>653</v>
+      </c>
       <c r="C634" s="4"/>
       <c r="D634" s="3"/>
       <c r="E634" s="10"/>
@@ -12105,7 +12592,9 @@
       <c r="A635" s="3">
         <v>634</v>
       </c>
-      <c r="B635" s="4"/>
+      <c r="B635" s="4" t="s">
+        <v>654</v>
+      </c>
       <c r="C635" s="4"/>
       <c r="D635" s="3"/>
       <c r="E635" s="10"/>
@@ -12115,7 +12604,9 @@
       <c r="A636" s="3">
         <v>635</v>
       </c>
-      <c r="B636" s="4"/>
+      <c r="B636" s="4" t="s">
+        <v>655</v>
+      </c>
       <c r="C636" s="4"/>
       <c r="D636" s="3"/>
       <c r="E636" s="10"/>
@@ -12125,7 +12616,9 @@
       <c r="A637" s="3">
         <v>636</v>
       </c>
-      <c r="B637" s="4"/>
+      <c r="B637" s="4" t="s">
+        <v>656</v>
+      </c>
       <c r="C637" s="4"/>
       <c r="D637" s="3"/>
       <c r="E637" s="10"/>
@@ -12135,7 +12628,9 @@
       <c r="A638" s="3">
         <v>637</v>
       </c>
-      <c r="B638" s="4"/>
+      <c r="B638" s="4" t="s">
+        <v>657</v>
+      </c>
       <c r="C638" s="4"/>
       <c r="D638" s="3"/>
       <c r="E638" s="10"/>
@@ -12145,7 +12640,9 @@
       <c r="A639" s="3">
         <v>638</v>
       </c>
-      <c r="B639" s="4"/>
+      <c r="B639" s="4" t="s">
+        <v>658</v>
+      </c>
       <c r="C639" s="4"/>
       <c r="D639" s="3"/>
       <c r="E639" s="10"/>
@@ -12155,7 +12652,9 @@
       <c r="A640" s="3">
         <v>639</v>
       </c>
-      <c r="B640" s="4"/>
+      <c r="B640" s="4" t="s">
+        <v>659</v>
+      </c>
       <c r="C640" s="4"/>
       <c r="D640" s="3"/>
       <c r="E640" s="10"/>
@@ -12165,7 +12664,9 @@
       <c r="A641" s="3">
         <v>640</v>
       </c>
-      <c r="B641" s="4"/>
+      <c r="B641" s="4" t="s">
+        <v>660</v>
+      </c>
       <c r="C641" s="4"/>
       <c r="D641" s="3"/>
       <c r="E641" s="10"/>
@@ -12175,7 +12676,9 @@
       <c r="A642" s="3">
         <v>641</v>
       </c>
-      <c r="B642" s="4"/>
+      <c r="B642" s="4" t="s">
+        <v>661</v>
+      </c>
       <c r="C642" s="4"/>
       <c r="D642" s="3"/>
       <c r="E642" s="10"/>
@@ -12185,7 +12688,9 @@
       <c r="A643" s="3">
         <v>642</v>
       </c>
-      <c r="B643" s="4"/>
+      <c r="B643" s="4" t="s">
+        <v>662</v>
+      </c>
       <c r="C643" s="4"/>
       <c r="D643" s="3"/>
       <c r="E643" s="10"/>
@@ -12195,7 +12700,9 @@
       <c r="A644" s="3">
         <v>643</v>
       </c>
-      <c r="B644" s="4"/>
+      <c r="B644" s="4" t="s">
+        <v>663</v>
+      </c>
       <c r="C644" s="4"/>
       <c r="D644" s="3"/>
       <c r="E644" s="10"/>
@@ -12205,7 +12712,9 @@
       <c r="A645" s="3">
         <v>644</v>
       </c>
-      <c r="B645" s="4"/>
+      <c r="B645" s="4" t="s">
+        <v>664</v>
+      </c>
       <c r="C645" s="4"/>
       <c r="D645" s="3"/>
       <c r="E645" s="10"/>
@@ -12215,7 +12724,9 @@
       <c r="A646" s="3">
         <v>645</v>
       </c>
-      <c r="B646" s="4"/>
+      <c r="B646" s="4" t="s">
+        <v>665</v>
+      </c>
       <c r="C646" s="4"/>
       <c r="D646" s="3"/>
       <c r="E646" s="10"/>
@@ -12225,7 +12736,9 @@
       <c r="A647" s="3">
         <v>646</v>
       </c>
-      <c r="B647" s="4"/>
+      <c r="B647" s="4" t="s">
+        <v>666</v>
+      </c>
       <c r="C647" s="4"/>
       <c r="D647" s="3"/>
       <c r="E647" s="10"/>
@@ -12235,7 +12748,9 @@
       <c r="A648" s="3">
         <v>647</v>
       </c>
-      <c r="B648" s="4"/>
+      <c r="B648" s="4" t="s">
+        <v>667</v>
+      </c>
       <c r="C648" s="4"/>
       <c r="D648" s="3"/>
       <c r="E648" s="10"/>
@@ -12245,7 +12760,9 @@
       <c r="A649" s="3">
         <v>648</v>
       </c>
-      <c r="B649" s="4"/>
+      <c r="B649" s="4" t="s">
+        <v>668</v>
+      </c>
       <c r="C649" s="4"/>
       <c r="D649" s="3"/>
       <c r="E649" s="10"/>
@@ -12255,7 +12772,9 @@
       <c r="A650" s="3">
         <v>649</v>
       </c>
-      <c r="B650" s="4"/>
+      <c r="B650" s="4" t="s">
+        <v>669</v>
+      </c>
       <c r="C650" s="4"/>
       <c r="D650" s="3"/>
       <c r="E650" s="10"/>
@@ -12265,7 +12784,9 @@
       <c r="A651" s="3">
         <v>650</v>
       </c>
-      <c r="B651" s="4"/>
+      <c r="B651" s="4" t="s">
+        <v>670</v>
+      </c>
       <c r="C651" s="4"/>
       <c r="D651" s="3"/>
       <c r="E651" s="10"/>
@@ -12275,7 +12796,9 @@
       <c r="A652" s="3">
         <v>651</v>
       </c>
-      <c r="B652" s="4"/>
+      <c r="B652" s="4" t="s">
+        <v>671</v>
+      </c>
       <c r="C652" s="4"/>
       <c r="D652" s="3"/>
       <c r="E652" s="10"/>
@@ -12285,7 +12808,9 @@
       <c r="A653" s="3">
         <v>652</v>
       </c>
-      <c r="B653" s="4"/>
+      <c r="B653" s="4" t="s">
+        <v>672</v>
+      </c>
       <c r="C653" s="4"/>
       <c r="D653" s="3"/>
       <c r="E653" s="10"/>
@@ -12295,7 +12820,9 @@
       <c r="A654" s="3">
         <v>653</v>
       </c>
-      <c r="B654" s="4"/>
+      <c r="B654" s="4" t="s">
+        <v>673</v>
+      </c>
       <c r="C654" s="4"/>
       <c r="D654" s="3"/>
       <c r="E654" s="10"/>
@@ -12305,7 +12832,9 @@
       <c r="A655" s="3">
         <v>654</v>
       </c>
-      <c r="B655" s="4"/>
+      <c r="B655" s="4" t="s">
+        <v>674</v>
+      </c>
       <c r="C655" s="4"/>
       <c r="D655" s="3"/>
       <c r="E655" s="10"/>
@@ -12315,7 +12844,9 @@
       <c r="A656" s="3">
         <v>655</v>
       </c>
-      <c r="B656" s="4"/>
+      <c r="B656" s="4" t="s">
+        <v>675</v>
+      </c>
       <c r="C656" s="4"/>
       <c r="D656" s="3"/>
       <c r="E656" s="10"/>
@@ -12325,7 +12856,9 @@
       <c r="A657" s="3">
         <v>656</v>
       </c>
-      <c r="B657" s="4"/>
+      <c r="B657" s="4" t="s">
+        <v>676</v>
+      </c>
       <c r="C657" s="4"/>
       <c r="D657" s="3"/>
       <c r="E657" s="10"/>
@@ -15806,7 +16339,7 @@
   <conditionalFormatting sqref="B100:B102">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576 B1:B62 B150:B1048576">
+  <conditionalFormatting sqref="F1:F2 F24:F1048576 S2:S22 B1:B62 B150:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18">

--- a/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 lô 1000 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EC3C6F-A114-4C16-A7F3-07A5FE3B8A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBB913F-4CE1-4D29-9C57-AA15B73FD89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="679">
   <si>
     <t>STT</t>
   </si>
@@ -1725,9 +1725,6 @@
     <t>VNET860879084174982</t>
   </si>
   <si>
-    <t>112 thiết bị chưa nhập ID</t>
-  </si>
-  <si>
     <t>Lỗi, Đã trả lại gia công</t>
   </si>
   <si>
@@ -2059,13 +2056,22 @@
   </si>
   <si>
     <t>VNET860879084174164</t>
+  </si>
+  <si>
+    <t>334 thiết bị chưa nhập ID</t>
+  </si>
+  <si>
+    <t>VNET860879084177993</t>
+  </si>
+  <si>
+    <t>VNET860879084182027</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2108,6 +2114,12 @@
       <color rgb="FF00B0F0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2175,7 +2187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2256,6 +2268,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2801,9 +2822,10 @@
         <v>145</v>
       </c>
       <c r="N2" t="s">
-        <v>565</v>
-      </c>
-      <c r="S2" s="15"/>
+        <v>676</v>
+      </c>
+      <c r="R2" s="33"/>
+      <c r="S2" s="34"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -2822,7 +2844,8 @@
       <c r="F3" s="10"/>
       <c r="G3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="S3" s="15"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="34"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -2840,7 +2863,8 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="7"/>
-      <c r="S4" s="15"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="34"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -2858,7 +2882,8 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="7"/>
-      <c r="S5" s="15"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="34"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -2876,7 +2901,8 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="7"/>
-      <c r="S6" s="15"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="34"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -2894,7 +2920,8 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="7"/>
-      <c r="S7" s="15"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="34"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -2912,7 +2939,8 @@
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="7"/>
-      <c r="S8" s="15"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="34"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -2930,7 +2958,8 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="7"/>
-      <c r="S9" s="15"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="34"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -2948,7 +2977,8 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="7"/>
-      <c r="S10" s="15"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="34"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -2966,7 +2996,8 @@
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="7"/>
-      <c r="S11" s="15"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="34"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -2984,7 +3015,8 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="34"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -3002,7 +3034,8 @@
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="34"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -3020,7 +3053,8 @@
       <c r="E14" s="11"/>
       <c r="F14" s="10"/>
       <c r="G14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="34"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -3038,7 +3072,8 @@
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="34"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -3056,7 +3091,8 @@
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="34"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -3074,7 +3110,8 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="34"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -3092,7 +3129,8 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="16"/>
-      <c r="S18" s="15"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="34"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -3110,7 +3148,8 @@
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="7"/>
-      <c r="S19" s="15"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="34"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -3128,7 +3167,8 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="7"/>
-      <c r="S20" s="15"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="34"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -3146,7 +3186,8 @@
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="7"/>
-      <c r="S21" s="18"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="35"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -3164,7 +3205,8 @@
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="7"/>
-      <c r="S22" s="18"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="35"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
@@ -3182,6 +3224,8 @@
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="7"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -3199,6 +3243,8 @@
       <c r="E24" s="10"/>
       <c r="F24" s="18"/>
       <c r="G24" s="8"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -3216,6 +3262,8 @@
       <c r="E25" s="10"/>
       <c r="F25" s="18"/>
       <c r="G25" s="8"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -5219,7 +5267,7 @@
         <v>166</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E150" s="14" t="s">
         <v>165</v>
@@ -5237,7 +5285,7 @@
         <v>166</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>165</v>
@@ -5255,7 +5303,7 @@
         <v>166</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>165</v>
@@ -5273,7 +5321,7 @@
         <v>166</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>165</v>
@@ -5291,7 +5339,7 @@
         <v>166</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E154" s="32" t="s">
         <v>397</v>
@@ -5309,7 +5357,7 @@
         <v>166</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>165</v>
@@ -5327,7 +5375,7 @@
         <v>166</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E156" s="14" t="s">
         <v>165</v>
@@ -5345,7 +5393,7 @@
         <v>166</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>165</v>
@@ -5363,7 +5411,7 @@
         <v>166</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>165</v>
@@ -5381,7 +5429,7 @@
         <v>166</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>165</v>
@@ -11525,7 +11573,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>567</v>
+        <v>638</v>
       </c>
       <c r="C546" s="4"/>
       <c r="D546" s="3"/>
@@ -11537,7 +11585,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>568</v>
+        <v>672</v>
       </c>
       <c r="C547" s="4"/>
       <c r="D547" s="3"/>
@@ -11549,7 +11597,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>569</v>
+        <v>639</v>
       </c>
       <c r="C548" s="4"/>
       <c r="D548" s="3"/>
@@ -11561,7 +11609,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>570</v>
+        <v>662</v>
       </c>
       <c r="C549" s="4"/>
       <c r="D549" s="3"/>
@@ -11573,7 +11621,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>571</v>
+        <v>673</v>
       </c>
       <c r="C550" s="4"/>
       <c r="D550" s="3"/>
@@ -11585,7 +11633,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>572</v>
+        <v>663</v>
       </c>
       <c r="C551" s="4"/>
       <c r="D551" s="3"/>
@@ -11597,7 +11645,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="4" t="s">
-        <v>573</v>
+        <v>653</v>
       </c>
       <c r="C552" s="4"/>
       <c r="D552" s="3"/>
@@ -11609,7 +11657,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="4" t="s">
-        <v>574</v>
+        <v>652</v>
       </c>
       <c r="C553" s="4"/>
       <c r="D553" s="3"/>
@@ -11621,7 +11669,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="4" t="s">
-        <v>575</v>
+        <v>637</v>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="3"/>
@@ -11633,7 +11681,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="4" t="s">
-        <v>576</v>
+        <v>670</v>
       </c>
       <c r="C555" s="4"/>
       <c r="D555" s="3"/>
@@ -11645,7 +11693,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="4" t="s">
-        <v>577</v>
+        <v>660</v>
       </c>
       <c r="C556" s="4"/>
       <c r="D556" s="3"/>
@@ -11657,7 +11705,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>578</v>
+        <v>628</v>
       </c>
       <c r="C557" s="4"/>
       <c r="D557" s="3"/>
@@ -11669,7 +11717,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="4" t="s">
-        <v>579</v>
+        <v>621</v>
       </c>
       <c r="C558" s="4"/>
       <c r="D558" s="3"/>
@@ -11681,7 +11729,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="4" t="s">
-        <v>580</v>
+        <v>661</v>
       </c>
       <c r="C559" s="4"/>
       <c r="D559" s="3"/>
@@ -11693,7 +11741,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="4" t="s">
-        <v>581</v>
+        <v>671</v>
       </c>
       <c r="C560" s="4"/>
       <c r="D560" s="3"/>
@@ -11705,7 +11753,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="4" t="s">
-        <v>582</v>
+        <v>650</v>
       </c>
       <c r="C561" s="4"/>
       <c r="D561" s="3"/>
@@ -11717,7 +11765,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="4" t="s">
-        <v>583</v>
+        <v>636</v>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="3"/>
@@ -11729,7 +11777,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="4" t="s">
-        <v>584</v>
+        <v>631</v>
       </c>
       <c r="C563" s="4"/>
       <c r="D563" s="3"/>
@@ -11741,7 +11789,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="4" t="s">
-        <v>585</v>
+        <v>668</v>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="3"/>
@@ -11753,7 +11801,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="4" t="s">
-        <v>586</v>
+        <v>642</v>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="3"/>
@@ -11765,7 +11813,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="4" t="s">
-        <v>587</v>
+        <v>669</v>
       </c>
       <c r="C566" s="4"/>
       <c r="D566" s="3"/>
@@ -11777,7 +11825,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="4" t="s">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="C567" s="4"/>
       <c r="D567" s="3"/>
@@ -11789,7 +11837,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="4" t="s">
-        <v>589</v>
+        <v>667</v>
       </c>
       <c r="C568" s="4"/>
       <c r="D568" s="3"/>
@@ -11801,7 +11849,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="4" t="s">
-        <v>590</v>
+        <v>643</v>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="3"/>
@@ -11813,7 +11861,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="4" t="s">
-        <v>591</v>
+        <v>664</v>
       </c>
       <c r="C570" s="4"/>
       <c r="D570" s="3"/>
@@ -11825,7 +11873,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="4" t="s">
-        <v>592</v>
+        <v>665</v>
       </c>
       <c r="C571" s="4"/>
       <c r="D571" s="3"/>
@@ -11837,7 +11885,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="4" t="s">
-        <v>593</v>
+        <v>641</v>
       </c>
       <c r="C572" s="4"/>
       <c r="D572" s="3"/>
@@ -11849,7 +11897,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="4" t="s">
-        <v>593</v>
+        <v>640</v>
       </c>
       <c r="C573" s="4"/>
       <c r="D573" s="3"/>
@@ -11861,7 +11909,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>571</v>
+        <v>674</v>
       </c>
       <c r="C574" s="4"/>
       <c r="D574" s="3"/>
@@ -11873,7 +11921,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="4" t="s">
-        <v>594</v>
+        <v>675</v>
       </c>
       <c r="C575" s="4"/>
       <c r="D575" s="3"/>
@@ -11885,7 +11933,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="4" t="s">
-        <v>595</v>
+        <v>630</v>
       </c>
       <c r="C576" s="4"/>
       <c r="D576" s="3"/>
@@ -11897,7 +11945,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>596</v>
+        <v>658</v>
       </c>
       <c r="C577" s="4"/>
       <c r="D577" s="3"/>
@@ -11909,7 +11957,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="4" t="s">
-        <v>597</v>
+        <v>659</v>
       </c>
       <c r="C578" s="4"/>
       <c r="D578" s="3"/>
@@ -11921,7 +11969,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="4" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="C579" s="4"/>
       <c r="D579" s="3"/>
@@ -11933,7 +11981,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="4" t="s">
-        <v>599</v>
+        <v>656</v>
       </c>
       <c r="C580" s="4"/>
       <c r="D580" s="3"/>
@@ -11945,7 +11993,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="4" t="s">
-        <v>600</v>
+        <v>654</v>
       </c>
       <c r="C581" s="4"/>
       <c r="D581" s="3"/>
@@ -11957,7 +12005,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="4" t="s">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="3"/>
@@ -11969,7 +12017,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="4" t="s">
-        <v>602</v>
+        <v>629</v>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="3"/>
@@ -11981,7 +12029,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="4" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="C584" s="4"/>
       <c r="D584" s="3"/>
@@ -11993,7 +12041,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="4" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="3"/>
@@ -12005,7 +12053,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="4" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="3"/>
@@ -12017,7 +12065,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="4" t="s">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="C587" s="4"/>
       <c r="D587" s="3"/>
@@ -12029,7 +12077,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="4" t="s">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="C588" s="4"/>
       <c r="D588" s="3"/>
@@ -12041,7 +12089,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="4" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="C589" s="4"/>
       <c r="D589" s="3"/>
@@ -12053,7 +12101,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="4" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="C590" s="4"/>
       <c r="D590" s="3"/>
@@ -12065,7 +12113,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="4" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="C591" s="4"/>
       <c r="D591" s="3"/>
@@ -12077,7 +12125,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="4" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="C592" s="4"/>
       <c r="D592" s="3"/>
@@ -12089,7 +12137,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="4" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="C593" s="4"/>
       <c r="D593" s="3"/>
@@ -12101,7 +12149,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="C594" s="4"/>
       <c r="D594" s="3"/>
@@ -12113,7 +12161,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="4" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="3"/>
@@ -12125,7 +12173,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="4" t="s">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="C596" s="4"/>
       <c r="D596" s="3"/>
@@ -12137,7 +12185,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="4" t="s">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="C597" s="4"/>
       <c r="D597" s="3"/>
@@ -12149,7 +12197,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="4" t="s">
-        <v>617</v>
+        <v>647</v>
       </c>
       <c r="C598" s="4"/>
       <c r="D598" s="3"/>
@@ -12161,7 +12209,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="4" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="C599" s="4"/>
       <c r="D599" s="3"/>
@@ -12173,7 +12221,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="4" t="s">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="C600" s="4"/>
       <c r="D600" s="3"/>
@@ -12185,7 +12233,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="4" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="C601" s="4"/>
       <c r="D601" s="3"/>
@@ -12197,7 +12245,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="4" t="s">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="C602" s="4"/>
       <c r="D602" s="3"/>
@@ -12209,7 +12257,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="4" t="s">
-        <v>622</v>
+        <v>574</v>
       </c>
       <c r="C603" s="4"/>
       <c r="D603" s="3"/>
@@ -12221,7 +12269,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="4" t="s">
-        <v>623</v>
+        <v>575</v>
       </c>
       <c r="C604" s="4"/>
       <c r="D604" s="3"/>
@@ -12233,7 +12281,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="4" t="s">
-        <v>624</v>
+        <v>569</v>
       </c>
       <c r="C605" s="4"/>
       <c r="D605" s="3"/>
@@ -12245,7 +12293,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="4" t="s">
-        <v>625</v>
+        <v>576</v>
       </c>
       <c r="C606" s="4"/>
       <c r="D606" s="3"/>
@@ -12257,7 +12305,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="4" t="s">
-        <v>626</v>
+        <v>577</v>
       </c>
       <c r="C607" s="4"/>
       <c r="D607" s="3"/>
@@ -12269,7 +12317,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="4" t="s">
-        <v>627</v>
+        <v>578</v>
       </c>
       <c r="C608" s="4"/>
       <c r="D608" s="3"/>
@@ -12281,7 +12329,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="4" t="s">
-        <v>628</v>
+        <v>579</v>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="3"/>
@@ -12293,7 +12341,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="4" t="s">
-        <v>629</v>
+        <v>580</v>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="3"/>
@@ -12305,7 +12353,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="4" t="s">
-        <v>630</v>
+        <v>581</v>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="3"/>
@@ -12317,7 +12365,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="4" t="s">
-        <v>631</v>
+        <v>591</v>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="3"/>
@@ -12329,7 +12377,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="4" t="s">
-        <v>632</v>
+        <v>596</v>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="3"/>
@@ -12341,7 +12389,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="4" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="3"/>
@@ -12353,7 +12401,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="4" t="s">
-        <v>634</v>
+        <v>592</v>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="3"/>
@@ -12365,7 +12413,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="4" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="3"/>
@@ -12377,7 +12425,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="4" t="s">
-        <v>636</v>
+        <v>597</v>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="3"/>
@@ -12389,7 +12437,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="4" t="s">
-        <v>637</v>
+        <v>568</v>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="3"/>
@@ -12401,7 +12449,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="4" t="s">
-        <v>638</v>
+        <v>570</v>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="3"/>
@@ -12413,7 +12461,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="4" t="s">
-        <v>639</v>
+        <v>677</v>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="3"/>
@@ -12425,7 +12473,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="4" t="s">
-        <v>640</v>
+        <v>567</v>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="3"/>
@@ -12437,7 +12485,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="4" t="s">
-        <v>641</v>
+        <v>594</v>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="3"/>
@@ -12449,7 +12497,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="4" t="s">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="C623" s="4"/>
       <c r="D623" s="3"/>
@@ -12461,7 +12509,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="4" t="s">
-        <v>643</v>
+        <v>619</v>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="3"/>
@@ -12473,7 +12521,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="4" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="3"/>
@@ -12485,7 +12533,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="4" t="s">
-        <v>645</v>
+        <v>616</v>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="3"/>
@@ -12497,7 +12545,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="4" t="s">
-        <v>646</v>
+        <v>617</v>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="3"/>
@@ -12509,7 +12557,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="4" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="3"/>
@@ -12521,7 +12569,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="4" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="3"/>
@@ -12533,7 +12581,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="4" t="s">
-        <v>649</v>
+        <v>583</v>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="3"/>
@@ -12545,7 +12593,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="4" t="s">
-        <v>650</v>
+        <v>572</v>
       </c>
       <c r="C631" s="4"/>
       <c r="D631" s="3"/>
@@ -12557,7 +12605,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="4" t="s">
-        <v>651</v>
+        <v>602</v>
       </c>
       <c r="C632" s="4"/>
       <c r="D632" s="3"/>
@@ -12569,7 +12617,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="4" t="s">
-        <v>652</v>
+        <v>603</v>
       </c>
       <c r="C633" s="4"/>
       <c r="D633" s="3"/>
@@ -12581,7 +12629,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="4" t="s">
-        <v>653</v>
+        <v>600</v>
       </c>
       <c r="C634" s="4"/>
       <c r="D634" s="3"/>
@@ -12593,7 +12641,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="4" t="s">
-        <v>654</v>
+        <v>601</v>
       </c>
       <c r="C635" s="4"/>
       <c r="D635" s="3"/>
@@ -12605,7 +12653,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="4" t="s">
-        <v>655</v>
+        <v>598</v>
       </c>
       <c r="C636" s="4"/>
       <c r="D636" s="3"/>
@@ -12617,7 +12665,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="4" t="s">
-        <v>656</v>
+        <v>599</v>
       </c>
       <c r="C637" s="4"/>
       <c r="D637" s="3"/>
@@ -12629,7 +12677,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="4" t="s">
-        <v>657</v>
+        <v>605</v>
       </c>
       <c r="C638" s="4"/>
       <c r="D638" s="3"/>
@@ -12641,7 +12689,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="4" t="s">
-        <v>658</v>
+        <v>604</v>
       </c>
       <c r="C639" s="4"/>
       <c r="D639" s="3"/>
@@ -12653,7 +12701,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="4" t="s">
-        <v>659</v>
+        <v>610</v>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="3"/>
@@ -12665,7 +12713,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="4" t="s">
-        <v>660</v>
+        <v>573</v>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="3"/>
@@ -12677,7 +12725,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="4" t="s">
-        <v>661</v>
+        <v>609</v>
       </c>
       <c r="C642" s="4"/>
       <c r="D642" s="3"/>
@@ -12689,7 +12737,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="4" t="s">
-        <v>662</v>
+        <v>611</v>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="3"/>
@@ -12701,7 +12749,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="4" t="s">
-        <v>663</v>
+        <v>607</v>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="3"/>
@@ -12713,7 +12761,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="4" t="s">
-        <v>664</v>
+        <v>606</v>
       </c>
       <c r="C645" s="4"/>
       <c r="D645" s="3"/>
@@ -12725,7 +12773,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="4" t="s">
-        <v>665</v>
+        <v>608</v>
       </c>
       <c r="C646" s="4"/>
       <c r="D646" s="3"/>
@@ -12737,7 +12785,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="4" t="s">
-        <v>666</v>
+        <v>613</v>
       </c>
       <c r="C647" s="4"/>
       <c r="D647" s="3"/>
@@ -12749,7 +12797,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="4" t="s">
-        <v>667</v>
+        <v>612</v>
       </c>
       <c r="C648" s="4"/>
       <c r="D648" s="3"/>
@@ -12761,7 +12809,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="4" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="C649" s="4"/>
       <c r="D649" s="3"/>
@@ -12773,7 +12821,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="4" t="s">
-        <v>669</v>
+        <v>571</v>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="3"/>
@@ -12785,7 +12833,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="4" t="s">
-        <v>670</v>
+        <v>582</v>
       </c>
       <c r="C651" s="4"/>
       <c r="D651" s="3"/>
@@ -12797,7 +12845,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="4" t="s">
-        <v>671</v>
+        <v>587</v>
       </c>
       <c r="C652" s="4"/>
       <c r="D652" s="3"/>
@@ -12809,7 +12857,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>672</v>
+        <v>585</v>
       </c>
       <c r="C653" s="4"/>
       <c r="D653" s="3"/>
@@ -12821,7 +12869,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="4" t="s">
-        <v>673</v>
+        <v>584</v>
       </c>
       <c r="C654" s="4"/>
       <c r="D654" s="3"/>
@@ -12833,7 +12881,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="4" t="s">
-        <v>674</v>
+        <v>588</v>
       </c>
       <c r="C655" s="4"/>
       <c r="D655" s="3"/>
@@ -12845,7 +12893,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="4" t="s">
-        <v>675</v>
+        <v>589</v>
       </c>
       <c r="C656" s="4"/>
       <c r="D656" s="3"/>
@@ -12857,7 +12905,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="4" t="s">
-        <v>676</v>
+        <v>586</v>
       </c>
       <c r="C657" s="4"/>
       <c r="D657" s="3"/>
@@ -16306,6 +16354,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1001" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="B63">
     <cfRule type="duplicateValues" dxfId="12" priority="9"/>
   </conditionalFormatting>
